--- a/outputs/QLD_curtailment.xlsx
+++ b/outputs/QLD_curtailment.xlsx
@@ -639,7 +639,7 @@
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="5" t="inlineStr"/>
       <c r="K2" s="5" t="n">
-        <v>0.1085</v>
+        <v>0.1347</v>
       </c>
       <c r="L2" s="5" t="inlineStr"/>
       <c r="M2" s="5" t="inlineStr"/>
@@ -821,10 +821,10 @@
         <v>132</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>0.0221</v>
+        <v>0.0234</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>0.0123</v>
+        <v>0.0128</v>
       </c>
       <c r="L5" s="5" t="n">
         <v>0.233985863287972</v>
@@ -1016,10 +1016,10 @@
         <v>132</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>0.1154</v>
+        <v>0.1229</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>0.247</v>
+        <v>0.3065</v>
       </c>
       <c r="L8" s="5" t="n">
         <v>0.218738210926131</v>
@@ -1101,10 +1101,10 @@
         <v>132</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>0.1651</v>
+        <v>0.1872</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>0.246</v>
+        <v>0.3124</v>
       </c>
       <c r="L9" s="5" t="n">
         <v>0.219557634008624</v>
@@ -1186,10 +1186,10 @@
         <v>132</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>0.0201</v>
+        <v>0.0209</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>0.0699</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="L10" s="5" t="n">
         <v>0.22576156415161</v>
@@ -1274,7 +1274,7 @@
         <v>0.0057</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>0.0349</v>
+        <v>0.0354</v>
       </c>
       <c r="L11" s="5" t="n">
         <v>0.221997464026796</v>
@@ -1356,7 +1356,7 @@
         <v>132</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>0.0264</v>
+        <v>0.0277</v>
       </c>
       <c r="K12" s="5" t="n">
         <v>0.0025</v>
@@ -1441,10 +1441,10 @@
         <v>275</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>0.0107</v>
+        <v>0.0108</v>
       </c>
       <c r="L13" s="5" t="n">
         <v>0.224633904533977</v>
@@ -1526,10 +1526,10 @@
         <v>33</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>0.0375</v>
+        <v>0.0384</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>0.1631</v>
+        <v>0.2108</v>
       </c>
       <c r="L14" s="5" t="n">
         <v>0.221997464026796</v>
@@ -1611,10 +1611,10 @@
         <v>275</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>0.053</v>
+        <v>0.0583</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>0.1078</v>
+        <v>0.129</v>
       </c>
       <c r="L15" s="5" t="n">
         <v>0.224633904533977</v>
@@ -1765,10 +1765,10 @@
         <v>132</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>0.1852</v>
+        <v>0.1932</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>0.2878</v>
+        <v>0.35</v>
       </c>
       <c r="L17" s="5" t="n">
         <v>0.224633904533977</v>
@@ -1905,10 +1905,10 @@
         <v>33</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>0.0682</v>
+        <v>0.074</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>0.2172</v>
+        <v>0.2538</v>
       </c>
       <c r="L19" s="5" t="n">
         <v>0.221997464026796</v>
@@ -1990,10 +1990,10 @@
         <v>275</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>0.0743</v>
+        <v>0.0878</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>0.0356</v>
+        <v>0.0367</v>
       </c>
       <c r="L20" s="5" t="n">
         <v>0.219557634008624</v>
@@ -2075,10 +2075,10 @@
         <v>33</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>0.1862</v>
+        <v>0.2149</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>0.2762</v>
+        <v>0.3371</v>
       </c>
       <c r="L21" s="5" t="n">
         <v>0.221997464026796</v>
@@ -2225,10 +2225,10 @@
         <v>132</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>0.0888</v>
+        <v>0.0902</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>0.0722</v>
+        <v>0.0738</v>
       </c>
       <c r="L23" s="5" t="n">
         <v>0.219557634008624</v>
@@ -2310,10 +2310,10 @@
         <v>132</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>0.1948</v>
+        <v>0.2351</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>0.2924</v>
+        <v>0.3472</v>
       </c>
       <c r="L24" s="5" t="n">
         <v>0.219557634008624</v>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="J25" s="5" t="inlineStr"/>
       <c r="K25" s="5" t="n">
-        <v>0.1903</v>
+        <v>0.274</v>
       </c>
       <c r="L25" s="5" t="n">
         <v>0.233985863287972</v>
@@ -2462,10 +2462,10 @@
         <v>33</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>0.0726</v>
+        <v>0.1022</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>0.036</v>
+        <v>0.0369</v>
       </c>
       <c r="L26" s="5" t="n">
         <v>0.22576156415161</v>
@@ -2612,10 +2612,10 @@
         <v>110</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>0.1106</v>
+        <v>0.1165</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>0.3019</v>
+        <v>0.3673</v>
       </c>
       <c r="L28" s="5" t="n">
         <v>0.23150076097273</v>
@@ -2691,10 +2691,10 @@
       </c>
       <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="5" t="n">
-        <v>0.0506</v>
+        <v>0.0531</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>0.2329</v>
+        <v>0.2608</v>
       </c>
       <c r="L29" s="5" t="inlineStr"/>
       <c r="M29" s="5" t="inlineStr"/>
@@ -2756,10 +2756,10 @@
         <v>132</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>0.0236</v>
+        <v>0.0238</v>
       </c>
       <c r="L30" s="5" t="n">
         <v>0.216663358752891</v>
@@ -2896,10 +2896,10 @@
         <v>110</v>
       </c>
       <c r="J32" s="5" t="n">
-        <v>0.3056</v>
+        <v>0.3341</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>0.2647</v>
+        <v>0.362</v>
       </c>
       <c r="L32" s="5" t="n">
         <v>0.23150076097273</v>
@@ -2981,10 +2981,10 @@
         <v>110</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>0.0897</v>
+        <v>0.096</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>0.2016</v>
+        <v>0.2724</v>
       </c>
       <c r="L33" s="5" t="n">
         <v>0.23150076097273</v>
@@ -3066,10 +3066,10 @@
         <v>132</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>0.0113</v>
+        <v>0.0115</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>0.028</v>
+        <v>0.0282</v>
       </c>
       <c r="L34" s="5" t="n">
         <v>0.219557634008624</v>
@@ -3151,10 +3151,10 @@
         <v>132</v>
       </c>
       <c r="J35" s="5" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.0786</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>0.2026</v>
+        <v>0.229</v>
       </c>
       <c r="L35" s="5" t="n">
         <v>0.22576156415161</v>
@@ -3236,10 +3236,10 @@
         <v>132</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>0.0959</v>
+        <v>0.1003</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>0.1819</v>
+        <v>0.2386</v>
       </c>
       <c r="L36" s="5" t="n">
         <v>0.219325121104852</v>
@@ -3321,10 +3321,10 @@
         <v>132</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>0.1111</v>
+        <v>0.1189</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>0.2397</v>
+        <v>0.2939</v>
       </c>
       <c r="L37" s="5" t="n">
         <v>0.218738210926131</v>
@@ -3471,10 +3471,10 @@
         <v>275</v>
       </c>
       <c r="J39" s="5" t="n">
-        <v>0.1905</v>
+        <v>0.1975</v>
       </c>
       <c r="K39" s="5" t="n">
-        <v>0.3104</v>
+        <v>0.3758</v>
       </c>
       <c r="L39" s="5" t="n">
         <v>0.223370431255546</v>
@@ -3556,10 +3556,10 @@
         <v>110</v>
       </c>
       <c r="J40" s="5" t="n">
-        <v>0.3423</v>
+        <v>0.39</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>0.3946</v>
+        <v>0.5046</v>
       </c>
       <c r="L40" s="5" t="n">
         <v>0.23150076097273</v>
@@ -3641,10 +3641,10 @@
         <v>110</v>
       </c>
       <c r="J41" s="5" t="n">
-        <v>0.3471</v>
+        <v>0.394</v>
       </c>
       <c r="K41" s="5" t="n">
-        <v>0.3901</v>
+        <v>0.5084</v>
       </c>
       <c r="L41" s="5" t="n">
         <v>0.23150076097273</v>
@@ -3720,10 +3720,10 @@
       </c>
       <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="5" t="n">
-        <v>0.1226</v>
+        <v>0.1745</v>
       </c>
       <c r="K42" s="5" t="n">
-        <v>0.0295</v>
+        <v>0.0315</v>
       </c>
       <c r="L42" s="5" t="inlineStr"/>
       <c r="M42" s="5" t="inlineStr"/>
@@ -3785,10 +3785,10 @@
         <v>33</v>
       </c>
       <c r="J43" s="5" t="n">
-        <v>0.2744</v>
+        <v>0.3037</v>
       </c>
       <c r="K43" s="5" t="n">
-        <v>0.2787</v>
+        <v>0.3572</v>
       </c>
       <c r="L43" s="5" t="n">
         <v>0.221997464026796</v>
@@ -3870,10 +3870,10 @@
         <v>132</v>
       </c>
       <c r="J44" s="5" t="n">
-        <v>0.1592</v>
+        <v>0.2353</v>
       </c>
       <c r="K44" s="5" t="n">
-        <v>0.0599</v>
+        <v>0.0665</v>
       </c>
       <c r="L44" s="5" t="n">
         <v>0.23173278497921</v>
@@ -3955,10 +3955,10 @@
         <v>110</v>
       </c>
       <c r="J45" s="5" t="n">
-        <v>0.1286</v>
+        <v>0.1371</v>
       </c>
       <c r="K45" s="5" t="n">
-        <v>0.177</v>
+        <v>0.2328</v>
       </c>
       <c r="L45" s="5" t="n">
         <v>0.23150076097273</v>
@@ -4035,7 +4035,7 @@
       <c r="I46" s="2" t="inlineStr"/>
       <c r="J46" s="5" t="inlineStr"/>
       <c r="K46" s="5" t="n">
-        <v>0.0416</v>
+        <v>0.0425</v>
       </c>
       <c r="L46" s="5" t="inlineStr"/>
       <c r="M46" s="5" t="inlineStr"/>
@@ -4092,7 +4092,7 @@
       <c r="I47" s="2" t="inlineStr"/>
       <c r="J47" s="5" t="inlineStr"/>
       <c r="K47" s="5" t="n">
-        <v>0.0284</v>
+        <v>0.029</v>
       </c>
       <c r="L47" s="5" t="inlineStr"/>
       <c r="M47" s="5" t="inlineStr"/>
@@ -4148,10 +4148,10 @@
       </c>
       <c r="I48" s="2" t="inlineStr"/>
       <c r="J48" s="5" t="n">
-        <v>0.029</v>
+        <v>0.0306</v>
       </c>
       <c r="K48" s="5" t="n">
-        <v>0.0516</v>
+        <v>0.0532</v>
       </c>
       <c r="L48" s="5" t="inlineStr"/>
       <c r="M48" s="5" t="inlineStr"/>
@@ -4207,10 +4207,10 @@
       </c>
       <c r="I49" s="2" t="inlineStr"/>
       <c r="J49" s="5" t="n">
-        <v>0.0032</v>
+        <v>0.0033</v>
       </c>
       <c r="K49" s="5" t="n">
-        <v>0.0018</v>
+        <v>0.0011</v>
       </c>
       <c r="L49" s="5" t="inlineStr"/>
       <c r="M49" s="5" t="inlineStr"/>
@@ -4266,10 +4266,10 @@
       </c>
       <c r="I50" s="2" t="inlineStr"/>
       <c r="J50" s="5" t="n">
-        <v>0.0136</v>
+        <v>0.0141</v>
       </c>
       <c r="K50" s="5" t="n">
-        <v>0.0726</v>
+        <v>0.0766</v>
       </c>
       <c r="L50" s="5" t="inlineStr"/>
       <c r="M50" s="5" t="inlineStr"/>
@@ -4325,10 +4325,10 @@
       </c>
       <c r="I51" s="2" t="inlineStr"/>
       <c r="J51" s="5" t="n">
-        <v>0.0236</v>
+        <v>0.024</v>
       </c>
       <c r="K51" s="5" t="n">
-        <v>0.0135</v>
+        <v>0.0136</v>
       </c>
       <c r="L51" s="5" t="inlineStr"/>
       <c r="M51" s="5" t="inlineStr"/>
@@ -4441,10 +4441,10 @@
       </c>
       <c r="I53" s="2" t="inlineStr"/>
       <c r="J53" s="5" t="n">
-        <v>0.0396</v>
+        <v>0.0425</v>
       </c>
       <c r="K53" s="5" t="n">
-        <v>0.0188</v>
+        <v>0.0189</v>
       </c>
       <c r="L53" s="5" t="inlineStr"/>
       <c r="M53" s="5" t="inlineStr"/>
@@ -4501,7 +4501,7 @@
       <c r="I54" s="2" t="inlineStr"/>
       <c r="J54" s="5" t="inlineStr"/>
       <c r="K54" s="5" t="n">
-        <v>0.0038</v>
+        <v>0.0039</v>
       </c>
       <c r="L54" s="5" t="inlineStr"/>
       <c r="M54" s="5" t="inlineStr"/>
@@ -4795,7 +4795,7 @@
       </c>
       <c r="E2" s="5" t="inlineStr"/>
       <c r="F2" s="5" t="n">
-        <v>0.1085</v>
+        <v>0.1347</v>
       </c>
       <c r="G2" s="5" t="inlineStr"/>
       <c r="H2" s="5" t="inlineStr"/>
@@ -4980,10 +4980,10 @@
         <v>0.9459</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.0221</v>
+        <v>0.0234</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.0123</v>
+        <v>0.0128</v>
       </c>
       <c r="G5" s="5" t="n">
         <v>0.233985863287972</v>
@@ -5184,10 +5184,10 @@
         <v>0.9523</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.1154</v>
+        <v>0.1229</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0.247</v>
+        <v>0.3065</v>
       </c>
       <c r="G8" s="5" t="n">
         <v>0.218738210926131</v>
@@ -5268,10 +5268,10 @@
         <v>0.8572</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0.1651</v>
+        <v>0.1872</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.246</v>
+        <v>0.3124</v>
       </c>
       <c r="G9" s="5" t="n">
         <v>0.219557634008624</v>
@@ -5352,10 +5352,10 @@
         <v>0.8878</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0.0201</v>
+        <v>0.0209</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.0699</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="G10" s="5" t="n">
         <v>0.22576156415161</v>
@@ -5439,7 +5439,7 @@
         <v>0.0057</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.0349</v>
+        <v>0.0354</v>
       </c>
       <c r="G11" s="5" t="n">
         <v>0.221997464026796</v>
@@ -5520,7 +5520,7 @@
         <v>0.9831</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0.0264</v>
+        <v>0.0277</v>
       </c>
       <c r="F12" s="5" t="n">
         <v>0.0025</v>
@@ -5604,10 +5604,10 @@
         <v>0.981</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.0107</v>
+        <v>0.0108</v>
       </c>
       <c r="G13" s="5" t="n">
         <v>0.224633904533977</v>
@@ -5688,10 +5688,10 @@
         <v>0.8758</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0.0375</v>
+        <v>0.0384</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0.1631</v>
+        <v>0.2108</v>
       </c>
       <c r="G14" s="5" t="n">
         <v>0.221997464026796</v>
@@ -5772,10 +5772,10 @@
         <v>0.9797</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0.053</v>
+        <v>0.0583</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.1078</v>
+        <v>0.129</v>
       </c>
       <c r="G15" s="5" t="n">
         <v>0.224633904533977</v>
@@ -5924,10 +5924,10 @@
         <v>0.9918</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0.1852</v>
+        <v>0.1932</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0.2878</v>
+        <v>0.35</v>
       </c>
       <c r="G17" s="5" t="n">
         <v>0.224633904533977</v>
@@ -6068,10 +6068,10 @@
         <v>0.872</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0.0682</v>
+        <v>0.074</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>0.2172</v>
+        <v>0.2538</v>
       </c>
       <c r="G19" s="5" t="n">
         <v>0.221997464026796</v>
@@ -6152,10 +6152,10 @@
         <v>0.8766</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0.0743</v>
+        <v>0.0878</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0.0356</v>
+        <v>0.0367</v>
       </c>
       <c r="G20" s="5" t="n">
         <v>0.219557634008624</v>
@@ -6236,10 +6236,10 @@
         <v>0.8758</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>0.1862</v>
+        <v>0.2149</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0.2762</v>
+        <v>0.3371</v>
       </c>
       <c r="G21" s="5" t="n">
         <v>0.221997464026796</v>
@@ -6384,10 +6384,10 @@
         <v>0.9574</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>0.0888</v>
+        <v>0.0902</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>0.0722</v>
+        <v>0.0738</v>
       </c>
       <c r="G23" s="5" t="n">
         <v>0.219557634008624</v>
@@ -6468,10 +6468,10 @@
         <v>0.8832</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>0.1948</v>
+        <v>0.2351</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>0.2924</v>
+        <v>0.3472</v>
       </c>
       <c r="G24" s="5" t="n">
         <v>0.219557634008624</v>
@@ -6553,7 +6553,7 @@
       </c>
       <c r="E25" s="5" t="inlineStr"/>
       <c r="F25" s="5" t="n">
-        <v>0.1903</v>
+        <v>0.274</v>
       </c>
       <c r="G25" s="5" t="n">
         <v>0.233985863287972</v>
@@ -6618,10 +6618,10 @@
         <v>0.8824</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>0.0726</v>
+        <v>0.1022</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>0.036</v>
+        <v>0.0369</v>
       </c>
       <c r="G26" s="5" t="n">
         <v>0.22576156415161</v>
@@ -6766,10 +6766,10 @@
         <v>0.987</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>0.1106</v>
+        <v>0.1165</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>0.3019</v>
+        <v>0.3673</v>
       </c>
       <c r="G28" s="5" t="n">
         <v>0.23150076097273</v>
@@ -6850,10 +6850,10 @@
         <v>0.8854</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>0.0506</v>
+        <v>0.0531</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>0.2329</v>
+        <v>0.2608</v>
       </c>
       <c r="G29" s="5" t="inlineStr"/>
       <c r="H29" s="5" t="inlineStr"/>
@@ -6914,10 +6914,10 @@
         <v>0.885</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>0.0236</v>
+        <v>0.0238</v>
       </c>
       <c r="G30" s="5" t="n">
         <v>0.216663358752891</v>
@@ -7058,10 +7058,10 @@
         <v>0.9856</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>0.3056</v>
+        <v>0.3341</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>0.2647</v>
+        <v>0.362</v>
       </c>
       <c r="G32" s="5" t="n">
         <v>0.23150076097273</v>
@@ -7142,10 +7142,10 @@
         <v>0.9856</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>0.0897</v>
+        <v>0.096</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>0.2016</v>
+        <v>0.2724</v>
       </c>
       <c r="G33" s="5" t="n">
         <v>0.23150076097273</v>
@@ -7226,10 +7226,10 @@
         <v>0.8832</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>0.0113</v>
+        <v>0.0115</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>0.028</v>
+        <v>0.0282</v>
       </c>
       <c r="G34" s="5" t="n">
         <v>0.219557634008624</v>
@@ -7310,10 +7310,10 @@
         <v>0.8932</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.0786</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>0.2026</v>
+        <v>0.229</v>
       </c>
       <c r="G35" s="5" t="n">
         <v>0.22576156415161</v>
@@ -7394,10 +7394,10 @@
         <v>1.0179</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>0.0959</v>
+        <v>0.1003</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>0.1819</v>
+        <v>0.2386</v>
       </c>
       <c r="G36" s="5" t="n">
         <v>0.219325121104852</v>
@@ -7478,10 +7478,10 @@
         <v>0.9523</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>0.1111</v>
+        <v>0.1189</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>0.2397</v>
+        <v>0.2939</v>
       </c>
       <c r="G37" s="5" t="n">
         <v>0.218738210926131</v>
@@ -7626,10 +7626,10 @@
         <v>0.9903999999999999</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>0.1905</v>
+        <v>0.1975</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>0.3104</v>
+        <v>0.3758</v>
       </c>
       <c r="G39" s="5" t="n">
         <v>0.223370431255546</v>
@@ -7710,10 +7710,10 @@
         <v>0.987</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>0.3423</v>
+        <v>0.39</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>0.3946</v>
+        <v>0.5046</v>
       </c>
       <c r="G40" s="5" t="n">
         <v>0.23150076097273</v>
@@ -7794,10 +7794,10 @@
         <v>0.987</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>0.3471</v>
+        <v>0.394</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>0.3901</v>
+        <v>0.5084</v>
       </c>
       <c r="G41" s="5" t="n">
         <v>0.23150076097273</v>
@@ -7878,10 +7878,10 @@
         <v>0.9761</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>0.1226</v>
+        <v>0.1745</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>0.0295</v>
+        <v>0.0315</v>
       </c>
       <c r="G42" s="5" t="inlineStr"/>
       <c r="H42" s="5" t="inlineStr"/>
@@ -7942,10 +7942,10 @@
         <v>0.8736</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>0.2744</v>
+        <v>0.3037</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>0.2787</v>
+        <v>0.3572</v>
       </c>
       <c r="G43" s="5" t="n">
         <v>0.221997464026796</v>
@@ -8026,10 +8026,10 @@
         <v>0.9568</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>0.1592</v>
+        <v>0.2353</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>0.0599</v>
+        <v>0.0665</v>
       </c>
       <c r="G44" s="5" t="n">
         <v>0.23173278497921</v>
@@ -8110,10 +8110,10 @@
         <v>0.987</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>0.1286</v>
+        <v>0.1371</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>0.177</v>
+        <v>0.2328</v>
       </c>
       <c r="G45" s="5" t="n">
         <v>0.23150076097273</v>
@@ -8195,7 +8195,7 @@
       </c>
       <c r="E46" s="5" t="inlineStr"/>
       <c r="F46" s="5" t="n">
-        <v>0.0416</v>
+        <v>0.0425</v>
       </c>
       <c r="G46" s="5" t="inlineStr"/>
       <c r="H46" s="5" t="inlineStr"/>
@@ -8257,7 +8257,7 @@
       </c>
       <c r="E47" s="5" t="inlineStr"/>
       <c r="F47" s="5" t="n">
-        <v>0.0284</v>
+        <v>0.029</v>
       </c>
       <c r="G47" s="5" t="inlineStr"/>
       <c r="H47" s="5" t="inlineStr"/>
@@ -8318,10 +8318,10 @@
         <v>0.9704</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>0.029</v>
+        <v>0.0306</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>0.0516</v>
+        <v>0.0532</v>
       </c>
       <c r="G48" s="5" t="inlineStr"/>
       <c r="H48" s="5" t="inlineStr"/>
@@ -8382,10 +8382,10 @@
         <v>0.987</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>0.0032</v>
+        <v>0.0033</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>0.0018</v>
+        <v>0.0011</v>
       </c>
       <c r="G49" s="5" t="inlineStr"/>
       <c r="H49" s="5" t="inlineStr"/>
@@ -8446,10 +8446,10 @@
         <v>0.9442</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>0.0136</v>
+        <v>0.0141</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>0.0726</v>
+        <v>0.0766</v>
       </c>
       <c r="G50" s="5" t="inlineStr"/>
       <c r="H50" s="5" t="inlineStr"/>
@@ -8510,10 +8510,10 @@
         <v>0.9574</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>0.0236</v>
+        <v>0.024</v>
       </c>
       <c r="F51" s="5" t="n">
-        <v>0.0135</v>
+        <v>0.0136</v>
       </c>
       <c r="G51" s="5" t="inlineStr"/>
       <c r="H51" s="5" t="inlineStr"/>
@@ -8636,10 +8636,10 @@
         <v>0.9396</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>0.0396</v>
+        <v>0.0425</v>
       </c>
       <c r="F53" s="5" t="n">
-        <v>0.0188</v>
+        <v>0.0189</v>
       </c>
       <c r="G53" s="5" t="inlineStr"/>
       <c r="H53" s="5" t="inlineStr"/>
@@ -8701,7 +8701,7 @@
       </c>
       <c r="E54" s="5" t="inlineStr"/>
       <c r="F54" s="5" t="n">
-        <v>0.0038</v>
+        <v>0.0039</v>
       </c>
       <c r="G54" s="5" t="inlineStr"/>
       <c r="H54" s="5" t="inlineStr"/>

--- a/outputs/QLD_curtailment.xlsx
+++ b/outputs/QLD_curtailment.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W56"/>
+  <dimension ref="A1:Y57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -465,10 +465,10 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="5" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
@@ -482,6 +482,8 @@
     <col width="12" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -517,85 +519,95 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>REZ Source</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>State</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>MW</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>kV</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Actual FY24-25</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Actual FY25-26</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>ELI Near Term</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>ELI Med Term</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ELI Source</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>FY25-26</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>FY26-27</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Curt FY1</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Curt FY2</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Curt FY3</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Curt Avg</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Offl FY1</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Offl FY2</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Offl FY3</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Offl Avg</t>
         </is>
@@ -618,45 +630,39 @@
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="3" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>QLD</t>
         </is>
       </c>
-      <c r="H2" s="4" t="n">
+      <c r="I2" s="4" t="n">
         <v>535.213</v>
       </c>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="5" t="inlineStr"/>
-      <c r="K2" s="5" t="n">
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="5" t="inlineStr"/>
+      <c r="L2" s="5" t="n">
         <v>0.1347</v>
       </c>
-      <c r="L2" s="5" t="inlineStr"/>
       <c r="M2" s="5" t="inlineStr"/>
-      <c r="N2" s="5" t="n">
+      <c r="N2" s="5" t="inlineStr"/>
+      <c r="O2" s="2" t="inlineStr"/>
+      <c r="P2" s="5" t="n">
         <v>0.9318</v>
       </c>
-      <c r="O2" s="5" t="n">
+      <c r="Q2" s="5" t="n">
         <v>0.8948</v>
       </c>
-      <c r="P2" s="6" t="inlineStr"/>
-      <c r="Q2" s="6" t="inlineStr"/>
       <c r="R2" s="6" t="inlineStr"/>
       <c r="S2" s="6" t="inlineStr"/>
       <c r="T2" s="6" t="inlineStr"/>
       <c r="U2" s="6" t="inlineStr"/>
       <c r="V2" s="6" t="inlineStr"/>
       <c r="W2" s="6" t="inlineStr"/>
+      <c r="X2" s="6" t="inlineStr"/>
+      <c r="Y2" s="6" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -691,37 +697,47 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
           <t>QLD</t>
         </is>
       </c>
-      <c r="H3" s="4" t="n">
+      <c r="I3" s="4" t="n">
         <v>14.7</v>
       </c>
-      <c r="I3" s="2" t="n">
+      <c r="J3" s="2" t="n">
         <v>132</v>
       </c>
-      <c r="J3" s="5" t="inlineStr"/>
       <c r="K3" s="5" t="inlineStr"/>
-      <c r="L3" s="5" t="n">
+      <c r="L3" s="5" t="inlineStr"/>
+      <c r="M3" s="5" t="n">
         <v>0.233985863287972</v>
       </c>
-      <c r="M3" s="5" t="n">
+      <c r="N3" s="5" t="n">
         <v>0.0559828223482727</v>
       </c>
-      <c r="N3" s="5" t="n">
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>per-DUID</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="n">
         <v>0.9593</v>
       </c>
-      <c r="O3" s="5" t="n">
+      <c r="Q3" s="5" t="n">
         <v>0.9472</v>
       </c>
-      <c r="P3" s="6" t="inlineStr"/>
-      <c r="Q3" s="6" t="inlineStr"/>
       <c r="R3" s="6" t="inlineStr"/>
       <c r="S3" s="6" t="inlineStr"/>
       <c r="T3" s="6" t="inlineStr"/>
       <c r="U3" s="6" t="inlineStr"/>
       <c r="V3" s="6" t="inlineStr"/>
       <c r="W3" s="6" t="inlineStr"/>
+      <c r="X3" s="6" t="inlineStr"/>
+      <c r="Y3" s="6" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -740,43 +756,37 @@
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr"/>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="3" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>QLD</t>
         </is>
       </c>
-      <c r="H4" s="4" t="n">
+      <c r="I4" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="5" t="inlineStr"/>
       <c r="L4" s="5" t="inlineStr"/>
       <c r="M4" s="5" t="inlineStr"/>
-      <c r="N4" s="5" t="n">
+      <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="2" t="inlineStr"/>
+      <c r="P4" s="5" t="n">
         <v>0.9409999999999999</v>
       </c>
-      <c r="O4" s="5" t="n">
+      <c r="Q4" s="5" t="n">
         <v>0.8878</v>
       </c>
-      <c r="P4" s="6" t="inlineStr"/>
-      <c r="Q4" s="6" t="inlineStr"/>
       <c r="R4" s="6" t="inlineStr"/>
       <c r="S4" s="6" t="inlineStr"/>
       <c r="T4" s="6" t="inlineStr"/>
       <c r="U4" s="6" t="inlineStr"/>
       <c r="V4" s="6" t="inlineStr"/>
       <c r="W4" s="6" t="inlineStr"/>
+      <c r="X4" s="6" t="inlineStr"/>
+      <c r="Y4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -811,39 +821,43 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
           <t>QLD</t>
         </is>
       </c>
-      <c r="H5" s="4" t="n">
+      <c r="I5" s="4" t="n">
         <v>148</v>
       </c>
-      <c r="I5" s="2" t="n">
+      <c r="J5" s="2" t="n">
         <v>132</v>
       </c>
-      <c r="J5" s="5" t="n">
+      <c r="K5" s="5" t="n">
         <v>0.0234</v>
       </c>
-      <c r="K5" s="5" t="n">
+      <c r="L5" s="5" t="n">
         <v>0.0128</v>
       </c>
-      <c r="L5" s="5" t="n">
+      <c r="M5" s="5" t="n">
         <v>0.233985863287972</v>
       </c>
-      <c r="M5" s="5" t="n">
+      <c r="N5" s="5" t="n">
         <v>0.0559828223482727</v>
       </c>
-      <c r="N5" s="5" t="n">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>per-DUID</t>
+        </is>
+      </c>
+      <c r="P5" s="5" t="n">
         <v>0.9543</v>
       </c>
-      <c r="O5" s="5" t="n">
+      <c r="Q5" s="5" t="n">
         <v>0.9459</v>
       </c>
-      <c r="P5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" s="6" t="n">
         <v>0</v>
       </c>
@@ -851,15 +865,21 @@
         <v>0</v>
       </c>
       <c r="T5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="6" t="n">
         <v>0.01</v>
       </c>
-      <c r="U5" s="6" t="n">
+      <c r="W5" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="V5" s="6" t="n">
+      <c r="X5" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="W5" s="6" t="n">
+      <c r="Y5" s="6" t="n">
         <v>0.01666666666666667</v>
       </c>
     </row>
@@ -880,43 +900,37 @@
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr"/>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="3" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>QLD</t>
         </is>
       </c>
-      <c r="H6" s="4" t="n">
+      <c r="I6" s="4" t="n">
         <v>368</v>
       </c>
-      <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="5" t="inlineStr"/>
       <c r="L6" s="5" t="inlineStr"/>
       <c r="M6" s="5" t="inlineStr"/>
-      <c r="N6" s="5" t="n">
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="2" t="inlineStr"/>
+      <c r="P6" s="5" t="n">
         <v>0.929</v>
       </c>
-      <c r="O6" s="5" t="n">
+      <c r="Q6" s="5" t="n">
         <v>0.9247</v>
       </c>
-      <c r="P6" s="6" t="inlineStr"/>
-      <c r="Q6" s="6" t="inlineStr"/>
       <c r="R6" s="6" t="inlineStr"/>
       <c r="S6" s="6" t="inlineStr"/>
       <c r="T6" s="6" t="inlineStr"/>
       <c r="U6" s="6" t="inlineStr"/>
       <c r="V6" s="6" t="inlineStr"/>
       <c r="W6" s="6" t="inlineStr"/>
+      <c r="X6" s="6" t="inlineStr"/>
+      <c r="Y6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -935,43 +949,37 @@
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr"/>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>QLD</t>
         </is>
       </c>
-      <c r="H7" s="4" t="n">
+      <c r="I7" s="4" t="n">
         <v>101</v>
       </c>
-      <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="5" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="5" t="inlineStr"/>
       <c r="L7" s="5" t="inlineStr"/>
       <c r="M7" s="5" t="inlineStr"/>
-      <c r="N7" s="5" t="n">
+      <c r="N7" s="5" t="inlineStr"/>
+      <c r="O7" s="2" t="inlineStr"/>
+      <c r="P7" s="5" t="n">
         <v>0.9677</v>
       </c>
-      <c r="O7" s="5" t="n">
+      <c r="Q7" s="5" t="n">
         <v>0.9323</v>
       </c>
-      <c r="P7" s="6" t="inlineStr"/>
-      <c r="Q7" s="6" t="inlineStr"/>
       <c r="R7" s="6" t="inlineStr"/>
       <c r="S7" s="6" t="inlineStr"/>
       <c r="T7" s="6" t="inlineStr"/>
       <c r="U7" s="6" t="inlineStr"/>
       <c r="V7" s="6" t="inlineStr"/>
       <c r="W7" s="6" t="inlineStr"/>
+      <c r="X7" s="6" t="inlineStr"/>
+      <c r="Y7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1006,39 +1014,43 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
           <t>QLD</t>
         </is>
       </c>
-      <c r="H8" s="4" t="n">
+      <c r="I8" s="4" t="n">
         <v>64.38</v>
       </c>
-      <c r="I8" s="2" t="n">
+      <c r="J8" s="2" t="n">
         <v>132</v>
       </c>
-      <c r="J8" s="5" t="n">
+      <c r="K8" s="5" t="n">
         <v>0.1229</v>
       </c>
-      <c r="K8" s="5" t="n">
+      <c r="L8" s="5" t="n">
         <v>0.3065</v>
       </c>
-      <c r="L8" s="5" t="n">
+      <c r="M8" s="5" t="n">
         <v>0.218738210926131</v>
       </c>
-      <c r="M8" s="5" t="n">
+      <c r="N8" s="5" t="n">
         <v>0.0522010106762296</v>
       </c>
-      <c r="N8" s="5" t="n">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>per-DUID</t>
+        </is>
+      </c>
+      <c r="P8" s="5" t="n">
         <v>0.9772</v>
       </c>
-      <c r="O8" s="5" t="n">
+      <c r="Q8" s="5" t="n">
         <v>0.9523</v>
       </c>
-      <c r="P8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" s="6" t="n">
         <v>0</v>
       </c>
@@ -1046,15 +1058,21 @@
         <v>0</v>
       </c>
       <c r="T8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="U8" s="6" t="n">
+      <c r="W8" s="6" t="n">
         <v>0.05</v>
       </c>
-      <c r="V8" s="6" t="n">
+      <c r="X8" s="6" t="n">
         <v>0.06</v>
       </c>
-      <c r="W8" s="6" t="n">
+      <c r="Y8" s="6" t="n">
         <v>0.04666666666666667</v>
       </c>
     </row>
@@ -1091,39 +1109,43 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
           <t>QLD</t>
         </is>
       </c>
-      <c r="H9" s="4" t="n">
+      <c r="I9" s="4" t="n">
         <v>110.4</v>
       </c>
-      <c r="I9" s="2" t="n">
+      <c r="J9" s="2" t="n">
         <v>132</v>
       </c>
-      <c r="J9" s="5" t="n">
+      <c r="K9" s="5" t="n">
         <v>0.1872</v>
       </c>
-      <c r="K9" s="5" t="n">
+      <c r="L9" s="5" t="n">
         <v>0.3124</v>
       </c>
-      <c r="L9" s="5" t="n">
+      <c r="M9" s="5" t="n">
         <v>0.219557634008624</v>
       </c>
-      <c r="M9" s="5" t="n">
+      <c r="N9" s="5" t="n">
         <v>0.0510095644706063</v>
       </c>
-      <c r="N9" s="5" t="n">
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>per-DUID</t>
+        </is>
+      </c>
+      <c r="P9" s="5" t="n">
         <v>0.9363</v>
       </c>
-      <c r="O9" s="5" t="n">
+      <c r="Q9" s="5" t="n">
         <v>0.8572</v>
       </c>
-      <c r="P9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" s="6" t="n">
         <v>0</v>
       </c>
@@ -1131,15 +1153,21 @@
         <v>0</v>
       </c>
       <c r="T9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="6" t="n">
         <v>0.01</v>
       </c>
-      <c r="U9" s="6" t="n">
+      <c r="W9" s="6" t="n">
         <v>0.04</v>
       </c>
-      <c r="V9" s="6" t="n">
+      <c r="X9" s="6" t="n">
         <v>0.04</v>
       </c>
-      <c r="W9" s="6" t="n">
+      <c r="Y9" s="6" t="n">
         <v>0.03</v>
       </c>
     </row>
@@ -1176,39 +1204,43 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>QLD</t>
         </is>
       </c>
-      <c r="H10" s="4" t="n">
+      <c r="I10" s="4" t="n">
         <v>92.5</v>
       </c>
-      <c r="I10" s="2" t="n">
+      <c r="J10" s="2" t="n">
         <v>132</v>
       </c>
-      <c r="J10" s="5" t="n">
+      <c r="K10" s="5" t="n">
         <v>0.0209</v>
       </c>
-      <c r="K10" s="5" t="n">
+      <c r="L10" s="5" t="n">
         <v>0.07829999999999999</v>
       </c>
-      <c r="L10" s="5" t="n">
+      <c r="M10" s="5" t="n">
         <v>0.22576156415161</v>
       </c>
-      <c r="M10" s="5" t="n">
+      <c r="N10" s="5" t="n">
         <v>0.0531062553506225</v>
       </c>
-      <c r="N10" s="5" t="n">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>per-DUID</t>
+        </is>
+      </c>
+      <c r="P10" s="5" t="n">
         <v>0.9409999999999999</v>
       </c>
-      <c r="O10" s="5" t="n">
+      <c r="Q10" s="5" t="n">
         <v>0.8878</v>
       </c>
-      <c r="P10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" s="6" t="n">
         <v>0</v>
       </c>
@@ -1216,15 +1248,21 @@
         <v>0</v>
       </c>
       <c r="T10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="6" t="n">
         <v>0.01</v>
       </c>
-      <c r="U10" s="6" t="n">
+      <c r="W10" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="V10" s="6" t="n">
+      <c r="X10" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="W10" s="6" t="n">
+      <c r="Y10" s="6" t="n">
         <v>0.02333333333333333</v>
       </c>
     </row>
@@ -1261,39 +1299,43 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
           <t>QLD</t>
         </is>
       </c>
-      <c r="H11" s="4" t="n">
+      <c r="I11" s="4" t="n">
         <v>42.5</v>
       </c>
-      <c r="I11" s="2" t="n">
+      <c r="J11" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="J11" s="5" t="n">
+      <c r="K11" s="5" t="n">
         <v>0.0057</v>
       </c>
-      <c r="K11" s="5" t="n">
+      <c r="L11" s="5" t="n">
         <v>0.0354</v>
       </c>
-      <c r="L11" s="5" t="n">
+      <c r="M11" s="5" t="n">
         <v>0.221997464026796</v>
       </c>
-      <c r="M11" s="5" t="n">
+      <c r="N11" s="5" t="n">
         <v>0.0524178948511446</v>
       </c>
-      <c r="N11" s="5" t="n">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>per-DUID</t>
+        </is>
+      </c>
+      <c r="P11" s="5" t="n">
         <v>0.9413</v>
       </c>
-      <c r="O11" s="5" t="n">
+      <c r="Q11" s="5" t="n">
         <v>0.8731</v>
       </c>
-      <c r="P11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" s="6" t="n">
         <v>0</v>
       </c>
@@ -1301,15 +1343,21 @@
         <v>0</v>
       </c>
       <c r="T11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="6" t="n">
         <v>0.01</v>
       </c>
-      <c r="U11" s="6" t="n">
+      <c r="W11" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="V11" s="6" t="n">
+      <c r="X11" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="W11" s="6" t="n">
+      <c r="Y11" s="6" t="n">
         <v>0.02333333333333333</v>
       </c>
     </row>
@@ -1346,39 +1394,43 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
           <t>QLD</t>
         </is>
       </c>
-      <c r="H12" s="4" t="n">
+      <c r="I12" s="4" t="n">
         <v>217.25</v>
       </c>
-      <c r="I12" s="2" t="n">
+      <c r="J12" s="2" t="n">
         <v>132</v>
       </c>
-      <c r="J12" s="5" t="n">
+      <c r="K12" s="5" t="n">
         <v>0.0277</v>
       </c>
-      <c r="K12" s="5" t="n">
+      <c r="L12" s="5" t="n">
         <v>0.0025</v>
       </c>
-      <c r="L12" s="5" t="n">
+      <c r="M12" s="5" t="n">
         <v>0.223370431255546</v>
       </c>
-      <c r="M12" s="5" t="n">
+      <c r="N12" s="5" t="n">
         <v>0.0519780465459995</v>
       </c>
-      <c r="N12" s="5" t="n">
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>per-DUID</t>
+        </is>
+      </c>
+      <c r="P12" s="5" t="n">
         <v>0.9865</v>
       </c>
-      <c r="O12" s="5" t="n">
+      <c r="Q12" s="5" t="n">
         <v>0.9831</v>
       </c>
-      <c r="P12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" s="6" t="n">
         <v>0</v>
       </c>
@@ -1386,15 +1438,21 @@
         <v>0</v>
       </c>
       <c r="T12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="6" t="n">
         <v>0.01</v>
       </c>
-      <c r="U12" s="6" t="n">
+      <c r="W12" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="V12" s="6" t="n">
+      <c r="X12" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="W12" s="6" t="n">
+      <c r="Y12" s="6" t="n">
         <v>0.01666666666666667</v>
       </c>
     </row>
@@ -1431,39 +1489,43 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>QLD</t>
         </is>
       </c>
-      <c r="H13" s="4" t="n">
+      <c r="I13" s="4" t="n">
         <v>121</v>
       </c>
-      <c r="I13" s="2" t="n">
+      <c r="J13" s="2" t="n">
         <v>275</v>
       </c>
-      <c r="J13" s="5" t="n">
+      <c r="K13" s="5" t="n">
         <v>0.01</v>
       </c>
-      <c r="K13" s="5" t="n">
+      <c r="L13" s="5" t="n">
         <v>0.0108</v>
       </c>
-      <c r="L13" s="5" t="n">
+      <c r="M13" s="5" t="n">
         <v>0.224633904533977</v>
       </c>
-      <c r="M13" s="5" t="n">
+      <c r="N13" s="5" t="n">
         <v>0.0520360014057779</v>
       </c>
-      <c r="N13" s="5" t="n">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>per-DUID</t>
+        </is>
+      </c>
+      <c r="P13" s="5" t="n">
         <v>0.9849</v>
       </c>
-      <c r="O13" s="5" t="n">
+      <c r="Q13" s="5" t="n">
         <v>0.981</v>
       </c>
-      <c r="P13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" s="6" t="n">
         <v>0</v>
       </c>
@@ -1471,15 +1533,21 @@
         <v>0</v>
       </c>
       <c r="T13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="6" t="n">
         <v>0.01</v>
       </c>
-      <c r="U13" s="6" t="n">
+      <c r="W13" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="V13" s="6" t="n">
+      <c r="X13" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="W13" s="6" t="n">
+      <c r="Y13" s="6" t="n">
         <v>0.01666666666666667</v>
       </c>
     </row>
@@ -1516,39 +1584,43 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
           <t>QLD</t>
         </is>
       </c>
-      <c r="H14" s="4" t="n">
+      <c r="I14" s="4" t="n">
         <v>167.75</v>
       </c>
-      <c r="I14" s="2" t="n">
+      <c r="J14" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="J14" s="5" t="n">
+      <c r="K14" s="5" t="n">
         <v>0.0384</v>
       </c>
-      <c r="K14" s="5" t="n">
+      <c r="L14" s="5" t="n">
         <v>0.2108</v>
       </c>
-      <c r="L14" s="5" t="n">
+      <c r="M14" s="5" t="n">
         <v>0.221997464026796</v>
       </c>
-      <c r="M14" s="5" t="n">
+      <c r="N14" s="5" t="n">
         <v>0.0524178948511446</v>
       </c>
-      <c r="N14" s="5" t="n">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>per-DUID</t>
+        </is>
+      </c>
+      <c r="P14" s="5" t="n">
         <v>0.9396</v>
       </c>
-      <c r="O14" s="5" t="n">
+      <c r="Q14" s="5" t="n">
         <v>0.8758</v>
       </c>
-      <c r="P14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" s="6" t="n">
         <v>0</v>
       </c>
@@ -1556,15 +1628,21 @@
         <v>0</v>
       </c>
       <c r="T14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="6" t="n">
         <v>0.01</v>
       </c>
-      <c r="U14" s="6" t="n">
+      <c r="W14" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="V14" s="6" t="n">
+      <c r="X14" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="W14" s="6" t="n">
+      <c r="Y14" s="6" t="n">
         <v>0.02333333333333333</v>
       </c>
     </row>
@@ -1601,39 +1679,43 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
           <t>QLD</t>
         </is>
       </c>
-      <c r="H15" s="4" t="n">
+      <c r="I15" s="4" t="n">
         <v>180</v>
       </c>
-      <c r="I15" s="2" t="n">
+      <c r="J15" s="2" t="n">
         <v>275</v>
       </c>
-      <c r="J15" s="5" t="n">
+      <c r="K15" s="5" t="n">
         <v>0.0583</v>
       </c>
-      <c r="K15" s="5" t="n">
+      <c r="L15" s="5" t="n">
         <v>0.129</v>
       </c>
-      <c r="L15" s="5" t="n">
+      <c r="M15" s="5" t="n">
         <v>0.224633904533977</v>
       </c>
-      <c r="M15" s="5" t="n">
+      <c r="N15" s="5" t="n">
         <v>0.0520360014057779</v>
       </c>
-      <c r="N15" s="5" t="n">
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>per-DUID</t>
+        </is>
+      </c>
+      <c r="P15" s="5" t="n">
         <v>0.9823</v>
       </c>
-      <c r="O15" s="5" t="n">
+      <c r="Q15" s="5" t="n">
         <v>0.9797</v>
       </c>
-      <c r="P15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" s="6" t="n">
         <v>0</v>
       </c>
@@ -1641,15 +1723,21 @@
         <v>0</v>
       </c>
       <c r="T15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="6" t="n">
         <v>0.01</v>
       </c>
-      <c r="U15" s="6" t="n">
+      <c r="W15" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="V15" s="6" t="n">
+      <c r="X15" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="W15" s="6" t="n">
+      <c r="Y15" s="6" t="n">
         <v>0.01666666666666667</v>
       </c>
     </row>
@@ -1686,41 +1774,51 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>QLD</t>
         </is>
       </c>
-      <c r="H16" s="4" t="n">
+      <c r="I16" s="4" t="n">
         <v>72</v>
       </c>
-      <c r="I16" s="2" t="n">
+      <c r="J16" s="2" t="n">
         <v>66</v>
       </c>
-      <c r="J16" s="5" t="n">
+      <c r="K16" s="5" t="n">
         <v>0.004</v>
       </c>
-      <c r="K16" s="5" t="n">
+      <c r="L16" s="5" t="n">
         <v>0.0116</v>
       </c>
-      <c r="L16" s="5" t="n">
+      <c r="M16" s="5" t="n">
         <v>0.22576156415161</v>
       </c>
-      <c r="M16" s="5" t="n">
+      <c r="N16" s="5" t="n">
         <v>0.0531062553506225</v>
       </c>
-      <c r="N16" s="5" t="n">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>per-DUID</t>
+        </is>
+      </c>
+      <c r="P16" s="5" t="n">
         <v>0.9381</v>
       </c>
-      <c r="O16" s="5" t="n">
+      <c r="Q16" s="5" t="n">
         <v>0.8854</v>
       </c>
-      <c r="P16" s="6" t="inlineStr"/>
-      <c r="Q16" s="6" t="inlineStr"/>
       <c r="R16" s="6" t="inlineStr"/>
       <c r="S16" s="6" t="inlineStr"/>
       <c r="T16" s="6" t="inlineStr"/>
       <c r="U16" s="6" t="inlineStr"/>
       <c r="V16" s="6" t="inlineStr"/>
       <c r="W16" s="6" t="inlineStr"/>
+      <c r="X16" s="6" t="inlineStr"/>
+      <c r="Y16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1755,39 +1853,43 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
           <t>QLD</t>
         </is>
       </c>
-      <c r="H17" s="4" t="n">
+      <c r="I17" s="4" t="n">
         <v>162</v>
       </c>
-      <c r="I17" s="2" t="n">
+      <c r="J17" s="2" t="n">
         <v>132</v>
       </c>
-      <c r="J17" s="5" t="n">
+      <c r="K17" s="5" t="n">
         <v>0.1932</v>
       </c>
-      <c r="K17" s="5" t="n">
+      <c r="L17" s="5" t="n">
         <v>0.35</v>
       </c>
-      <c r="L17" s="5" t="n">
+      <c r="M17" s="5" t="n">
         <v>0.224633904533977</v>
       </c>
-      <c r="M17" s="5" t="n">
+      <c r="N17" s="5" t="n">
         <v>0.0520360014057779</v>
       </c>
-      <c r="N17" s="5" t="n">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>per-DUID</t>
+        </is>
+      </c>
+      <c r="P17" s="5" t="n">
         <v>0.9977</v>
       </c>
-      <c r="O17" s="5" t="n">
+      <c r="Q17" s="5" t="n">
         <v>0.9918</v>
       </c>
-      <c r="P17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" s="6" t="n">
         <v>0</v>
       </c>
@@ -1795,15 +1897,21 @@
         <v>0</v>
       </c>
       <c r="T17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="6" t="n">
         <v>0.01</v>
       </c>
-      <c r="U17" s="6" t="n">
+      <c r="W17" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="V17" s="6" t="n">
+      <c r="X17" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="W17" s="6" t="n">
+      <c r="Y17" s="6" t="n">
         <v>0.01666666666666667</v>
       </c>
     </row>
@@ -1824,43 +1932,37 @@
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr"/>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="3" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>QLD</t>
         </is>
       </c>
-      <c r="H18" s="4" t="n">
+      <c r="I18" s="4" t="n">
         <v>122.775</v>
       </c>
-      <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="5" t="inlineStr"/>
       <c r="L18" s="5" t="inlineStr"/>
       <c r="M18" s="5" t="inlineStr"/>
-      <c r="N18" s="5" t="n">
+      <c r="N18" s="5" t="inlineStr"/>
+      <c r="O18" s="2" t="inlineStr"/>
+      <c r="P18" s="5" t="n">
         <v>0.9836</v>
       </c>
-      <c r="O18" s="5" t="n">
+      <c r="Q18" s="5" t="n">
         <v>0.9827</v>
       </c>
-      <c r="P18" s="6" t="inlineStr"/>
-      <c r="Q18" s="6" t="inlineStr"/>
       <c r="R18" s="6" t="inlineStr"/>
       <c r="S18" s="6" t="inlineStr"/>
       <c r="T18" s="6" t="inlineStr"/>
       <c r="U18" s="6" t="inlineStr"/>
       <c r="V18" s="6" t="inlineStr"/>
       <c r="W18" s="6" t="inlineStr"/>
+      <c r="X18" s="6" t="inlineStr"/>
+      <c r="Y18" s="6" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1895,39 +1997,43 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
           <t>QLD</t>
         </is>
       </c>
-      <c r="H19" s="4" t="n">
+      <c r="I19" s="4" t="n">
         <v>57.5</v>
       </c>
-      <c r="I19" s="2" t="n">
+      <c r="J19" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="J19" s="5" t="n">
+      <c r="K19" s="5" t="n">
         <v>0.074</v>
       </c>
-      <c r="K19" s="5" t="n">
+      <c r="L19" s="5" t="n">
         <v>0.2538</v>
       </c>
-      <c r="L19" s="5" t="n">
+      <c r="M19" s="5" t="n">
         <v>0.221997464026796</v>
       </c>
-      <c r="M19" s="5" t="n">
+      <c r="N19" s="5" t="n">
         <v>0.0524178948511446</v>
       </c>
-      <c r="N19" s="5" t="n">
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>per-DUID</t>
+        </is>
+      </c>
+      <c r="P19" s="5" t="n">
         <v>0.9385</v>
       </c>
-      <c r="O19" s="5" t="n">
+      <c r="Q19" s="5" t="n">
         <v>0.872</v>
       </c>
-      <c r="P19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" s="6" t="n">
         <v>0</v>
       </c>
@@ -1935,15 +2041,21 @@
         <v>0</v>
       </c>
       <c r="T19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="6" t="n">
         <v>0.01</v>
       </c>
-      <c r="U19" s="6" t="n">
+      <c r="W19" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="V19" s="6" t="n">
+      <c r="X19" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="W19" s="6" t="n">
+      <c r="Y19" s="6" t="n">
         <v>0.02333333333333333</v>
       </c>
     </row>
@@ -1980,39 +2092,43 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
           <t>QLD</t>
         </is>
       </c>
-      <c r="H20" s="4" t="n">
+      <c r="I20" s="4" t="n">
         <v>132.6</v>
       </c>
-      <c r="I20" s="2" t="n">
+      <c r="J20" s="2" t="n">
         <v>275</v>
       </c>
-      <c r="J20" s="5" t="n">
+      <c r="K20" s="5" t="n">
         <v>0.0878</v>
       </c>
-      <c r="K20" s="5" t="n">
+      <c r="L20" s="5" t="n">
         <v>0.0367</v>
       </c>
-      <c r="L20" s="5" t="n">
+      <c r="M20" s="5" t="n">
         <v>0.219557634008624</v>
       </c>
-      <c r="M20" s="5" t="n">
+      <c r="N20" s="5" t="n">
         <v>0.0510095644706063</v>
       </c>
-      <c r="N20" s="5" t="n">
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>per-DUID</t>
+        </is>
+      </c>
+      <c r="P20" s="5" t="n">
         <v>0.9475</v>
       </c>
-      <c r="O20" s="5" t="n">
+      <c r="Q20" s="5" t="n">
         <v>0.8766</v>
       </c>
-      <c r="P20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" s="6" t="n">
         <v>0</v>
       </c>
@@ -2020,15 +2136,21 @@
         <v>0</v>
       </c>
       <c r="T20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="6" t="n">
         <v>0.01</v>
       </c>
-      <c r="U20" s="6" t="n">
+      <c r="W20" s="6" t="n">
         <v>0.04</v>
       </c>
-      <c r="V20" s="6" t="n">
+      <c r="X20" s="6" t="n">
         <v>0.04</v>
       </c>
-      <c r="W20" s="6" t="n">
+      <c r="Y20" s="6" t="n">
         <v>0.03</v>
       </c>
     </row>
@@ -2065,39 +2187,43 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
           <t>QLD</t>
         </is>
       </c>
-      <c r="H21" s="4" t="n">
+      <c r="I21" s="4" t="n">
         <v>57.75</v>
       </c>
-      <c r="I21" s="2" t="n">
+      <c r="J21" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="J21" s="5" t="n">
+      <c r="K21" s="5" t="n">
         <v>0.2149</v>
       </c>
-      <c r="K21" s="5" t="n">
+      <c r="L21" s="5" t="n">
         <v>0.3371</v>
       </c>
-      <c r="L21" s="5" t="n">
+      <c r="M21" s="5" t="n">
         <v>0.221997464026796</v>
       </c>
-      <c r="M21" s="5" t="n">
+      <c r="N21" s="5" t="n">
         <v>0.0524178948511446</v>
       </c>
-      <c r="N21" s="5" t="n">
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>per-DUID</t>
+        </is>
+      </c>
+      <c r="P21" s="5" t="n">
         <v>0.9396</v>
       </c>
-      <c r="O21" s="5" t="n">
+      <c r="Q21" s="5" t="n">
         <v>0.8758</v>
       </c>
-      <c r="P21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" s="6" t="n">
         <v>0</v>
       </c>
@@ -2105,15 +2231,21 @@
         <v>0</v>
       </c>
       <c r="T21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="6" t="n">
         <v>0.01</v>
       </c>
-      <c r="U21" s="6" t="n">
+      <c r="W21" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="V21" s="6" t="n">
+      <c r="X21" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="W21" s="6" t="n">
+      <c r="Y21" s="6" t="n">
         <v>0.02333333333333333</v>
       </c>
     </row>
@@ -2150,37 +2282,47 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
           <t>QLD</t>
         </is>
       </c>
-      <c r="H22" s="4" t="n">
+      <c r="I22" s="4" t="n">
         <v>20.97</v>
       </c>
-      <c r="I22" s="2" t="n">
+      <c r="J22" s="2" t="n">
         <v>132</v>
       </c>
-      <c r="J22" s="5" t="inlineStr"/>
       <c r="K22" s="5" t="inlineStr"/>
-      <c r="L22" s="5" t="n">
+      <c r="L22" s="5" t="inlineStr"/>
+      <c r="M22" s="5" t="n">
         <v>0.219557634008624</v>
       </c>
-      <c r="M22" s="5" t="n">
+      <c r="N22" s="5" t="n">
         <v>0.0510095644706063</v>
       </c>
-      <c r="N22" s="5" t="n">
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>per-DUID</t>
+        </is>
+      </c>
+      <c r="P22" s="5" t="n">
         <v>0.9516</v>
       </c>
-      <c r="O22" s="5" t="n">
+      <c r="Q22" s="5" t="n">
         <v>0.8832</v>
       </c>
-      <c r="P22" s="6" t="inlineStr"/>
-      <c r="Q22" s="6" t="inlineStr"/>
       <c r="R22" s="6" t="inlineStr"/>
       <c r="S22" s="6" t="inlineStr"/>
       <c r="T22" s="6" t="inlineStr"/>
       <c r="U22" s="6" t="inlineStr"/>
       <c r="V22" s="6" t="inlineStr"/>
       <c r="W22" s="6" t="inlineStr"/>
+      <c r="X22" s="6" t="inlineStr"/>
+      <c r="Y22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -2215,39 +2357,43 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
           <t>QLD</t>
         </is>
       </c>
-      <c r="H23" s="4" t="n">
+      <c r="I23" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="I23" s="2" t="n">
+      <c r="J23" s="2" t="n">
         <v>132</v>
       </c>
-      <c r="J23" s="5" t="n">
+      <c r="K23" s="5" t="n">
         <v>0.0902</v>
       </c>
-      <c r="K23" s="5" t="n">
+      <c r="L23" s="5" t="n">
         <v>0.0738</v>
       </c>
-      <c r="L23" s="5" t="n">
+      <c r="M23" s="5" t="n">
         <v>0.219557634008624</v>
       </c>
-      <c r="M23" s="5" t="n">
+      <c r="N23" s="5" t="n">
         <v>0.0510095644706063</v>
       </c>
-      <c r="N23" s="5" t="n">
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>per-DUID</t>
+        </is>
+      </c>
+      <c r="P23" s="5" t="n">
         <v>0.9813</v>
       </c>
-      <c r="O23" s="5" t="n">
+      <c r="Q23" s="5" t="n">
         <v>0.9574</v>
       </c>
-      <c r="P23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" s="6" t="n">
         <v>0</v>
       </c>
@@ -2255,15 +2401,21 @@
         <v>0</v>
       </c>
       <c r="T23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="U23" s="6" t="n">
+      <c r="W23" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="V23" s="6" t="n">
+      <c r="X23" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="W23" s="6" t="n">
+      <c r="Y23" s="6" t="n">
         <v>0.02666666666666667</v>
       </c>
     </row>
@@ -2300,39 +2452,43 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
           <t>QLD</t>
         </is>
       </c>
-      <c r="H24" s="4" t="n">
+      <c r="I24" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="I24" s="2" t="n">
+      <c r="J24" s="2" t="n">
         <v>132</v>
       </c>
-      <c r="J24" s="5" t="n">
+      <c r="K24" s="5" t="n">
         <v>0.2351</v>
       </c>
-      <c r="K24" s="5" t="n">
+      <c r="L24" s="5" t="n">
         <v>0.3472</v>
       </c>
-      <c r="L24" s="5" t="n">
+      <c r="M24" s="5" t="n">
         <v>0.219557634008624</v>
       </c>
-      <c r="M24" s="5" t="n">
+      <c r="N24" s="5" t="n">
         <v>0.0510095644706063</v>
       </c>
-      <c r="N24" s="5" t="n">
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>per-DUID</t>
+        </is>
+      </c>
+      <c r="P24" s="5" t="n">
         <v>0.9516</v>
       </c>
-      <c r="O24" s="5" t="n">
+      <c r="Q24" s="5" t="n">
         <v>0.8832</v>
       </c>
-      <c r="P24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" s="6" t="n">
         <v>0</v>
       </c>
@@ -2340,15 +2496,21 @@
         <v>0</v>
       </c>
       <c r="T24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="U24" s="6" t="n">
+      <c r="W24" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="V24" s="6" t="n">
+      <c r="X24" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="W24" s="6" t="n">
+      <c r="Y24" s="6" t="n">
         <v>0.02666666666666667</v>
       </c>
     </row>
@@ -2385,39 +2547,49 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
           <t>QLD</t>
         </is>
       </c>
-      <c r="H25" s="4" t="n">
+      <c r="I25" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="I25" s="2" t="n">
+      <c r="J25" s="2" t="n">
         <v>66</v>
       </c>
-      <c r="J25" s="5" t="inlineStr"/>
-      <c r="K25" s="5" t="n">
+      <c r="K25" s="5" t="inlineStr"/>
+      <c r="L25" s="5" t="n">
         <v>0.274</v>
       </c>
-      <c r="L25" s="5" t="n">
+      <c r="M25" s="5" t="n">
         <v>0.233985863287972</v>
       </c>
-      <c r="M25" s="5" t="n">
+      <c r="N25" s="5" t="n">
         <v>0.0559828223482727</v>
       </c>
-      <c r="N25" s="5" t="n">
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>per-DUID</t>
+        </is>
+      </c>
+      <c r="P25" s="5" t="n">
         <v>0.9795</v>
       </c>
-      <c r="O25" s="5" t="n">
+      <c r="Q25" s="5" t="n">
         <v>0.9791</v>
       </c>
-      <c r="P25" s="6" t="inlineStr"/>
-      <c r="Q25" s="6" t="inlineStr"/>
       <c r="R25" s="6" t="inlineStr"/>
       <c r="S25" s="6" t="inlineStr"/>
       <c r="T25" s="6" t="inlineStr"/>
       <c r="U25" s="6" t="inlineStr"/>
       <c r="V25" s="6" t="inlineStr"/>
       <c r="W25" s="6" t="inlineStr"/>
+      <c r="X25" s="6" t="inlineStr"/>
+      <c r="Y25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2452,39 +2624,43 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
           <t>QLD</t>
         </is>
       </c>
-      <c r="H26" s="4" t="n">
+      <c r="I26" s="4" t="n">
         <v>118.4</v>
       </c>
-      <c r="I26" s="2" t="n">
+      <c r="J26" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="J26" s="5" t="n">
+      <c r="K26" s="5" t="n">
         <v>0.1022</v>
       </c>
-      <c r="K26" s="5" t="n">
+      <c r="L26" s="5" t="n">
         <v>0.0369</v>
       </c>
-      <c r="L26" s="5" t="n">
+      <c r="M26" s="5" t="n">
         <v>0.22576156415161</v>
       </c>
-      <c r="M26" s="5" t="n">
+      <c r="N26" s="5" t="n">
         <v>0.0531062553506225</v>
       </c>
-      <c r="N26" s="5" t="n">
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>per-DUID</t>
+        </is>
+      </c>
+      <c r="P26" s="5" t="n">
         <v>0.9379</v>
       </c>
-      <c r="O26" s="5" t="n">
+      <c r="Q26" s="5" t="n">
         <v>0.8824</v>
       </c>
-      <c r="P26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" s="6" t="n">
         <v>0</v>
       </c>
@@ -2492,15 +2668,21 @@
         <v>0</v>
       </c>
       <c r="T26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="6" t="n">
         <v>0.01</v>
       </c>
-      <c r="U26" s="6" t="n">
+      <c r="W26" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="V26" s="6" t="n">
+      <c r="X26" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="W26" s="6" t="n">
+      <c r="Y26" s="6" t="n">
         <v>0.02333333333333333</v>
       </c>
     </row>
@@ -2537,37 +2719,47 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
           <t>QLD</t>
         </is>
       </c>
-      <c r="H27" s="4" t="n">
+      <c r="I27" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="I27" s="2" t="n">
+      <c r="J27" s="2" t="n">
         <v>132</v>
       </c>
-      <c r="J27" s="5" t="inlineStr"/>
       <c r="K27" s="5" t="inlineStr"/>
-      <c r="L27" s="5" t="n">
+      <c r="L27" s="5" t="inlineStr"/>
+      <c r="M27" s="5" t="n">
         <v>0.22576156415161</v>
       </c>
-      <c r="M27" s="5" t="n">
+      <c r="N27" s="5" t="n">
         <v>0.0531062553506225</v>
       </c>
-      <c r="N27" s="5" t="n">
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>per-DUID</t>
+        </is>
+      </c>
+      <c r="P27" s="5" t="n">
         <v>0.9409999999999999</v>
       </c>
-      <c r="O27" s="5" t="n">
+      <c r="Q27" s="5" t="n">
         <v>0.8878</v>
       </c>
-      <c r="P27" s="6" t="inlineStr"/>
-      <c r="Q27" s="6" t="inlineStr"/>
       <c r="R27" s="6" t="inlineStr"/>
       <c r="S27" s="6" t="inlineStr"/>
       <c r="T27" s="6" t="inlineStr"/>
       <c r="U27" s="6" t="inlineStr"/>
       <c r="V27" s="6" t="inlineStr"/>
       <c r="W27" s="6" t="inlineStr"/>
+      <c r="X27" s="6" t="inlineStr"/>
+      <c r="Y27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2602,39 +2794,43 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
           <t>QLD</t>
         </is>
       </c>
-      <c r="H28" s="4" t="n">
+      <c r="I28" s="4" t="n">
         <v>34.5</v>
       </c>
-      <c r="I28" s="2" t="n">
+      <c r="J28" s="2" t="n">
         <v>110</v>
       </c>
-      <c r="J28" s="5" t="n">
+      <c r="K28" s="5" t="n">
         <v>0.1165</v>
       </c>
-      <c r="K28" s="5" t="n">
+      <c r="L28" s="5" t="n">
         <v>0.3673</v>
       </c>
-      <c r="L28" s="5" t="n">
+      <c r="M28" s="5" t="n">
         <v>0.23150076097273</v>
       </c>
-      <c r="M28" s="5" t="n">
+      <c r="N28" s="5" t="n">
         <v>0.0544394673584698</v>
       </c>
-      <c r="N28" s="5" t="n">
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>per-DUID</t>
+        </is>
+      </c>
+      <c r="P28" s="5" t="n">
         <v>0.9888</v>
       </c>
-      <c r="O28" s="5" t="n">
+      <c r="Q28" s="5" t="n">
         <v>0.987</v>
       </c>
-      <c r="P28" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" s="6" t="n">
         <v>0</v>
       </c>
@@ -2642,15 +2838,21 @@
         <v>0</v>
       </c>
       <c r="T28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" s="6" t="n">
         <v>0.01</v>
       </c>
-      <c r="U28" s="6" t="n">
+      <c r="W28" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="V28" s="6" t="n">
+      <c r="X28" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="W28" s="6" t="n">
+      <c r="Y28" s="6" t="n">
         <v>0.01666666666666667</v>
       </c>
     </row>
@@ -2671,47 +2873,41 @@
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr"/>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr"/>
+      <c r="F29" s="3" t="inlineStr"/>
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>QLD</t>
         </is>
       </c>
-      <c r="H29" s="4" t="n">
+      <c r="I29" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="5" t="n">
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="5" t="n">
         <v>0.0531</v>
       </c>
-      <c r="K29" s="5" t="n">
+      <c r="L29" s="5" t="n">
         <v>0.2608</v>
       </c>
-      <c r="L29" s="5" t="inlineStr"/>
       <c r="M29" s="5" t="inlineStr"/>
-      <c r="N29" s="5" t="n">
+      <c r="N29" s="5" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr"/>
+      <c r="P29" s="5" t="n">
         <v>0.9381</v>
       </c>
-      <c r="O29" s="5" t="n">
+      <c r="Q29" s="5" t="n">
         <v>0.8854</v>
       </c>
-      <c r="P29" s="6" t="inlineStr"/>
-      <c r="Q29" s="6" t="inlineStr"/>
       <c r="R29" s="6" t="inlineStr"/>
       <c r="S29" s="6" t="inlineStr"/>
       <c r="T29" s="6" t="inlineStr"/>
       <c r="U29" s="6" t="inlineStr"/>
       <c r="V29" s="6" t="inlineStr"/>
       <c r="W29" s="6" t="inlineStr"/>
+      <c r="X29" s="6" t="inlineStr"/>
+      <c r="Y29" s="6" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2746,39 +2942,43 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
           <t>QLD</t>
         </is>
       </c>
-      <c r="H30" s="4" t="n">
+      <c r="I30" s="4" t="n">
         <v>99</v>
       </c>
-      <c r="I30" s="2" t="n">
+      <c r="J30" s="2" t="n">
         <v>132</v>
       </c>
-      <c r="J30" s="5" t="n">
+      <c r="K30" s="5" t="n">
         <v>0.008200000000000001</v>
       </c>
-      <c r="K30" s="5" t="n">
+      <c r="L30" s="5" t="n">
         <v>0.0238</v>
       </c>
-      <c r="L30" s="5" t="n">
+      <c r="M30" s="5" t="n">
         <v>0.216663358752891</v>
       </c>
-      <c r="M30" s="5" t="n">
+      <c r="N30" s="5" t="n">
         <v>0.0509815379375577</v>
       </c>
-      <c r="N30" s="5" t="n">
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>per-DUID</t>
+        </is>
+      </c>
+      <c r="P30" s="5" t="n">
         <v>0.9328</v>
       </c>
-      <c r="O30" s="5" t="n">
+      <c r="Q30" s="5" t="n">
         <v>0.885</v>
       </c>
-      <c r="P30" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" s="6" t="n">
         <v>0</v>
       </c>
@@ -2786,15 +2986,21 @@
         <v>0</v>
       </c>
       <c r="T30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" s="6" t="n">
         <v>0.01</v>
       </c>
-      <c r="U30" s="6" t="n">
+      <c r="W30" s="6" t="n">
         <v>0.04</v>
       </c>
-      <c r="V30" s="6" t="n">
+      <c r="X30" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="W30" s="6" t="n">
+      <c r="Y30" s="6" t="n">
         <v>0.02333333333333333</v>
       </c>
     </row>
@@ -2815,43 +3021,37 @@
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr"/>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr"/>
+      <c r="F31" s="3" t="inlineStr"/>
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>QLD</t>
         </is>
       </c>
-      <c r="H31" s="4" t="n">
+      <c r="I31" s="4" t="n">
         <v>154</v>
       </c>
-      <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="5" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="5" t="inlineStr"/>
       <c r="L31" s="5" t="inlineStr"/>
       <c r="M31" s="5" t="inlineStr"/>
-      <c r="N31" s="5" t="n">
+      <c r="N31" s="5" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr"/>
+      <c r="P31" s="5" t="n">
         <v>0.9759</v>
       </c>
-      <c r="O31" s="5" t="n">
+      <c r="Q31" s="5" t="n">
         <v>0.9579</v>
       </c>
-      <c r="P31" s="6" t="inlineStr"/>
-      <c r="Q31" s="6" t="inlineStr"/>
       <c r="R31" s="6" t="inlineStr"/>
       <c r="S31" s="6" t="inlineStr"/>
       <c r="T31" s="6" t="inlineStr"/>
       <c r="U31" s="6" t="inlineStr"/>
       <c r="V31" s="6" t="inlineStr"/>
       <c r="W31" s="6" t="inlineStr"/>
+      <c r="X31" s="6" t="inlineStr"/>
+      <c r="Y31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2886,39 +3086,43 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
           <t>QLD</t>
         </is>
       </c>
-      <c r="H32" s="4" t="n">
+      <c r="I32" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="I32" s="2" t="n">
+      <c r="J32" s="2" t="n">
         <v>110</v>
       </c>
-      <c r="J32" s="5" t="n">
+      <c r="K32" s="5" t="n">
         <v>0.3341</v>
       </c>
-      <c r="K32" s="5" t="n">
+      <c r="L32" s="5" t="n">
         <v>0.362</v>
       </c>
-      <c r="L32" s="5" t="n">
+      <c r="M32" s="5" t="n">
         <v>0.23150076097273</v>
       </c>
-      <c r="M32" s="5" t="n">
+      <c r="N32" s="5" t="n">
         <v>0.0544394673584698</v>
       </c>
-      <c r="N32" s="5" t="n">
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>per-DUID</t>
+        </is>
+      </c>
+      <c r="P32" s="5" t="n">
         <v>0.9852</v>
       </c>
-      <c r="O32" s="5" t="n">
+      <c r="Q32" s="5" t="n">
         <v>0.9856</v>
       </c>
-      <c r="P32" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" s="6" t="n">
         <v>0</v>
       </c>
@@ -2926,15 +3130,21 @@
         <v>0</v>
       </c>
       <c r="T32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" s="6" t="n">
         <v>0.01</v>
       </c>
-      <c r="U32" s="6" t="n">
+      <c r="W32" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="V32" s="6" t="n">
+      <c r="X32" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="W32" s="6" t="n">
+      <c r="Y32" s="6" t="n">
         <v>0.01666666666666667</v>
       </c>
     </row>
@@ -2971,39 +3181,43 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
           <t>QLD</t>
         </is>
       </c>
-      <c r="H33" s="4" t="n">
+      <c r="I33" s="4" t="n">
         <v>55.64</v>
       </c>
-      <c r="I33" s="2" t="n">
+      <c r="J33" s="2" t="n">
         <v>110</v>
       </c>
-      <c r="J33" s="5" t="n">
+      <c r="K33" s="5" t="n">
         <v>0.096</v>
       </c>
-      <c r="K33" s="5" t="n">
+      <c r="L33" s="5" t="n">
         <v>0.2724</v>
       </c>
-      <c r="L33" s="5" t="n">
+      <c r="M33" s="5" t="n">
         <v>0.23150076097273</v>
       </c>
-      <c r="M33" s="5" t="n">
+      <c r="N33" s="5" t="n">
         <v>0.0544394673584698</v>
       </c>
-      <c r="N33" s="5" t="n">
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>per-DUID</t>
+        </is>
+      </c>
+      <c r="P33" s="5" t="n">
         <v>0.9852</v>
       </c>
-      <c r="O33" s="5" t="n">
+      <c r="Q33" s="5" t="n">
         <v>0.9856</v>
       </c>
-      <c r="P33" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" s="6" t="n">
         <v>0</v>
       </c>
@@ -3011,15 +3225,21 @@
         <v>0</v>
       </c>
       <c r="T33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" s="6" t="n">
         <v>0.01</v>
       </c>
-      <c r="U33" s="6" t="n">
+      <c r="W33" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="V33" s="6" t="n">
+      <c r="X33" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="W33" s="6" t="n">
+      <c r="Y33" s="6" t="n">
         <v>0.01666666666666667</v>
       </c>
     </row>
@@ -3056,39 +3276,43 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
           <t>QLD</t>
         </is>
       </c>
-      <c r="H34" s="4" t="n">
+      <c r="I34" s="4" t="n">
         <v>128</v>
       </c>
-      <c r="I34" s="2" t="n">
+      <c r="J34" s="2" t="n">
         <v>132</v>
       </c>
-      <c r="J34" s="5" t="n">
+      <c r="K34" s="5" t="n">
         <v>0.0115</v>
       </c>
-      <c r="K34" s="5" t="n">
+      <c r="L34" s="5" t="n">
         <v>0.0282</v>
       </c>
-      <c r="L34" s="5" t="n">
+      <c r="M34" s="5" t="n">
         <v>0.219557634008624</v>
       </c>
-      <c r="M34" s="5" t="n">
+      <c r="N34" s="5" t="n">
         <v>0.0510095644706063</v>
       </c>
-      <c r="N34" s="5" t="n">
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>per-DUID</t>
+        </is>
+      </c>
+      <c r="P34" s="5" t="n">
         <v>0.9516</v>
       </c>
-      <c r="O34" s="5" t="n">
+      <c r="Q34" s="5" t="n">
         <v>0.8832</v>
       </c>
-      <c r="P34" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" s="6" t="n">
         <v>0</v>
       </c>
@@ -3096,15 +3320,21 @@
         <v>0</v>
       </c>
       <c r="T34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" s="6" t="n">
         <v>0.01</v>
       </c>
-      <c r="U34" s="6" t="n">
+      <c r="W34" s="6" t="n">
         <v>0.04</v>
       </c>
-      <c r="V34" s="6" t="n">
+      <c r="X34" s="6" t="n">
         <v>0.04</v>
       </c>
-      <c r="W34" s="6" t="n">
+      <c r="Y34" s="6" t="n">
         <v>0.03</v>
       </c>
     </row>
@@ -3141,39 +3371,43 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
           <t>QLD</t>
         </is>
       </c>
-      <c r="H35" s="4" t="n">
+      <c r="I35" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="I35" s="2" t="n">
+      <c r="J35" s="2" t="n">
         <v>132</v>
       </c>
-      <c r="J35" s="5" t="n">
+      <c r="K35" s="5" t="n">
         <v>0.0786</v>
       </c>
-      <c r="K35" s="5" t="n">
+      <c r="L35" s="5" t="n">
         <v>0.229</v>
       </c>
-      <c r="L35" s="5" t="n">
+      <c r="M35" s="5" t="n">
         <v>0.22576156415161</v>
       </c>
-      <c r="M35" s="5" t="n">
+      <c r="N35" s="5" t="n">
         <v>0.0531062553506225</v>
       </c>
-      <c r="N35" s="5" t="n">
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>per-DUID</t>
+        </is>
+      </c>
+      <c r="P35" s="5" t="n">
         <v>0.9463</v>
       </c>
-      <c r="O35" s="5" t="n">
+      <c r="Q35" s="5" t="n">
         <v>0.8932</v>
       </c>
-      <c r="P35" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" s="6" t="n">
         <v>0</v>
       </c>
@@ -3181,15 +3415,21 @@
         <v>0</v>
       </c>
       <c r="T35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" s="6" t="n">
         <v>0.01</v>
       </c>
-      <c r="U35" s="6" t="n">
+      <c r="W35" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="V35" s="6" t="n">
+      <c r="X35" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="W35" s="6" t="n">
+      <c r="Y35" s="6" t="n">
         <v>0.02333333333333333</v>
       </c>
     </row>
@@ -3226,39 +3466,43 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
           <t>QLD</t>
         </is>
       </c>
-      <c r="H36" s="4" t="n">
+      <c r="I36" s="4" t="n">
         <v>143</v>
       </c>
-      <c r="I36" s="2" t="n">
+      <c r="J36" s="2" t="n">
         <v>132</v>
       </c>
-      <c r="J36" s="5" t="n">
+      <c r="K36" s="5" t="n">
         <v>0.1003</v>
       </c>
-      <c r="K36" s="5" t="n">
+      <c r="L36" s="5" t="n">
         <v>0.2386</v>
       </c>
-      <c r="L36" s="5" t="n">
+      <c r="M36" s="5" t="n">
         <v>0.219325121104852</v>
       </c>
-      <c r="M36" s="5" t="n">
+      <c r="N36" s="5" t="n">
         <v>0.0509806543175163</v>
       </c>
-      <c r="N36" s="5" t="n">
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>per-DUID</t>
+        </is>
+      </c>
+      <c r="P36" s="5" t="n">
         <v>1.0151</v>
       </c>
-      <c r="O36" s="5" t="n">
+      <c r="Q36" s="5" t="n">
         <v>1.0179</v>
       </c>
-      <c r="P36" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" s="6" t="n">
         <v>0</v>
       </c>
@@ -3266,15 +3510,21 @@
         <v>0</v>
       </c>
       <c r="T36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" s="6" t="n">
         <v>0.01</v>
       </c>
-      <c r="U36" s="6" t="n">
+      <c r="W36" s="6" t="n">
         <v>0.04</v>
       </c>
-      <c r="V36" s="6" t="n">
+      <c r="X36" s="6" t="n">
         <v>0.04</v>
       </c>
-      <c r="W36" s="6" t="n">
+      <c r="Y36" s="6" t="n">
         <v>0.03</v>
       </c>
     </row>
@@ -3311,39 +3561,43 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
           <t>QLD</t>
         </is>
       </c>
-      <c r="H37" s="4" t="n">
+      <c r="I37" s="4" t="n">
         <v>85.26000000000001</v>
       </c>
-      <c r="I37" s="2" t="n">
+      <c r="J37" s="2" t="n">
         <v>132</v>
       </c>
-      <c r="J37" s="5" t="n">
+      <c r="K37" s="5" t="n">
         <v>0.1189</v>
       </c>
-      <c r="K37" s="5" t="n">
+      <c r="L37" s="5" t="n">
         <v>0.2939</v>
       </c>
-      <c r="L37" s="5" t="n">
+      <c r="M37" s="5" t="n">
         <v>0.218738210926131</v>
       </c>
-      <c r="M37" s="5" t="n">
+      <c r="N37" s="5" t="n">
         <v>0.0522010106762296</v>
       </c>
-      <c r="N37" s="5" t="n">
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>per-DUID</t>
+        </is>
+      </c>
+      <c r="P37" s="5" t="n">
         <v>0.9772</v>
       </c>
-      <c r="O37" s="5" t="n">
+      <c r="Q37" s="5" t="n">
         <v>0.9523</v>
       </c>
-      <c r="P37" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" s="6" t="n">
         <v>0</v>
       </c>
@@ -3351,15 +3605,21 @@
         <v>0</v>
       </c>
       <c r="T37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="U37" s="6" t="n">
+      <c r="W37" s="6" t="n">
         <v>0.05</v>
       </c>
-      <c r="V37" s="6" t="n">
+      <c r="X37" s="6" t="n">
         <v>0.06</v>
       </c>
-      <c r="W37" s="6" t="n">
+      <c r="Y37" s="6" t="n">
         <v>0.04666666666666667</v>
       </c>
     </row>
@@ -3396,37 +3656,47 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
           <t>QLD</t>
         </is>
       </c>
-      <c r="H38" s="4" t="n">
+      <c r="I38" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="I38" s="2" t="n">
+      <c r="J38" s="2" t="n">
         <v>132</v>
       </c>
-      <c r="J38" s="5" t="inlineStr"/>
       <c r="K38" s="5" t="inlineStr"/>
-      <c r="L38" s="5" t="n">
+      <c r="L38" s="5" t="inlineStr"/>
+      <c r="M38" s="5" t="n">
         <v>0.240575567460725</v>
       </c>
-      <c r="M38" s="5" t="n">
+      <c r="N38" s="5" t="n">
         <v>0.0593284659737539</v>
       </c>
-      <c r="N38" s="5" t="n">
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>per-DUID</t>
+        </is>
+      </c>
+      <c r="P38" s="5" t="n">
         <v>1.0144</v>
       </c>
-      <c r="O38" s="5" t="n">
+      <c r="Q38" s="5" t="n">
         <v>1.0132</v>
       </c>
-      <c r="P38" s="6" t="inlineStr"/>
-      <c r="Q38" s="6" t="inlineStr"/>
       <c r="R38" s="6" t="inlineStr"/>
       <c r="S38" s="6" t="inlineStr"/>
       <c r="T38" s="6" t="inlineStr"/>
       <c r="U38" s="6" t="inlineStr"/>
       <c r="V38" s="6" t="inlineStr"/>
       <c r="W38" s="6" t="inlineStr"/>
+      <c r="X38" s="6" t="inlineStr"/>
+      <c r="Y38" s="6" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -3436,7 +3706,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Wandoan Solar Farm 1</t>
+          <t>Wandoan Solar Farm</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3461,38 +3731,42 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
           <t>QLD</t>
         </is>
       </c>
-      <c r="H39" s="4" t="n">
+      <c r="I39" s="4" t="n">
         <v>160</v>
       </c>
-      <c r="I39" s="2" t="n">
+      <c r="J39" s="2" t="n">
         <v>275</v>
       </c>
-      <c r="J39" s="5" t="n">
+      <c r="K39" s="5" t="n">
         <v>0.1975</v>
       </c>
-      <c r="K39" s="5" t="n">
+      <c r="L39" s="5" t="n">
         <v>0.3758</v>
       </c>
-      <c r="L39" s="5" t="n">
+      <c r="M39" s="5" t="n">
         <v>0.223370431255546</v>
       </c>
-      <c r="M39" s="5" t="n">
+      <c r="N39" s="5" t="n">
         <v>0.0519780465459995</v>
       </c>
-      <c r="N39" s="5" t="n">
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>per-DUID</t>
+        </is>
+      </c>
+      <c r="P39" s="5" t="n">
         <v>0.9975000000000001</v>
       </c>
-      <c r="O39" s="5" t="n">
-        <v>0.9903999999999999</v>
-      </c>
-      <c r="P39" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" s="6" t="n">
-        <v>0</v>
+      <c r="Q39" s="5" t="n">
+        <v>0.985</v>
       </c>
       <c r="R39" s="6" t="n">
         <v>0</v>
@@ -3501,27 +3775,33 @@
         <v>0</v>
       </c>
       <c r="T39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" s="6" t="n">
         <v>0.01</v>
       </c>
-      <c r="U39" s="6" t="n">
+      <c r="W39" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="V39" s="6" t="n">
+      <c r="X39" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="W39" s="6" t="n">
+      <c r="Y39" s="6" t="n">
         <v>0.01666666666666667</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>WARWSF1</t>
+          <t>WANDSF2</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Warwick Solar Farm 1 </t>
+          <t>Wandoan Solar Farm</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3529,84 +3809,48 @@
           <t>Solar</t>
         </is>
       </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>Middle Ridge</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F40" s="3" t="inlineStr">
-        <is>
-          <t>Darling Downs</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="D40" s="3" t="inlineStr"/>
+      <c r="E40" s="2" t="inlineStr"/>
+      <c r="F40" s="3" t="inlineStr"/>
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>QLD</t>
         </is>
       </c>
-      <c r="H40" s="4" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="I40" s="2" t="n">
-        <v>110</v>
-      </c>
-      <c r="J40" s="5" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="K40" s="5" t="n">
-        <v>0.5046</v>
-      </c>
-      <c r="L40" s="5" t="n">
-        <v>0.23150076097273</v>
-      </c>
-      <c r="M40" s="5" t="n">
-        <v>0.0544394673584698</v>
-      </c>
-      <c r="N40" s="5" t="n">
-        <v>0.9888</v>
-      </c>
-      <c r="O40" s="5" t="n">
-        <v>0.987</v>
-      </c>
-      <c r="P40" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="U40" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="V40" s="6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="W40" s="6" t="n">
-        <v>0.01666666666666667</v>
-      </c>
+      <c r="I40" s="4" t="n">
+        <v>310</v>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="5" t="inlineStr"/>
+      <c r="L40" s="5" t="inlineStr"/>
+      <c r="M40" s="5" t="inlineStr"/>
+      <c r="N40" s="5" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr"/>
+      <c r="P40" s="5" t="n">
+        <v>0.9975000000000001</v>
+      </c>
+      <c r="Q40" s="5" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="R40" s="6" t="inlineStr"/>
+      <c r="S40" s="6" t="inlineStr"/>
+      <c r="T40" s="6" t="inlineStr"/>
+      <c r="U40" s="6" t="inlineStr"/>
+      <c r="V40" s="6" t="inlineStr"/>
+      <c r="W40" s="6" t="inlineStr"/>
+      <c r="X40" s="6" t="inlineStr"/>
+      <c r="Y40" s="6" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>WARWSF2</t>
+          <t>WARWSF1</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Warwick Solar Farm 2</t>
+          <t xml:space="preserve">Warwick Solar Farm 1 </t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3631,39 +3875,43 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
           <t>QLD</t>
         </is>
       </c>
-      <c r="H41" s="4" t="n">
+      <c r="I41" s="4" t="n">
         <v>32.1</v>
       </c>
-      <c r="I41" s="2" t="n">
+      <c r="J41" s="2" t="n">
         <v>110</v>
       </c>
-      <c r="J41" s="5" t="n">
-        <v>0.394</v>
-      </c>
       <c r="K41" s="5" t="n">
-        <v>0.5084</v>
+        <v>0.39</v>
       </c>
       <c r="L41" s="5" t="n">
+        <v>0.5046</v>
+      </c>
+      <c r="M41" s="5" t="n">
         <v>0.23150076097273</v>
       </c>
-      <c r="M41" s="5" t="n">
+      <c r="N41" s="5" t="n">
         <v>0.0544394673584698</v>
       </c>
-      <c r="N41" s="5" t="n">
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>per-DUID</t>
+        </is>
+      </c>
+      <c r="P41" s="5" t="n">
         <v>0.9888</v>
       </c>
-      <c r="O41" s="5" t="n">
+      <c r="Q41" s="5" t="n">
         <v>0.987</v>
       </c>
-      <c r="P41" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q41" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" s="6" t="n">
         <v>0</v>
       </c>
@@ -3671,27 +3919,33 @@
         <v>0</v>
       </c>
       <c r="T41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" s="6" t="n">
         <v>0.01</v>
       </c>
-      <c r="U41" s="6" t="n">
+      <c r="W41" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="V41" s="6" t="n">
+      <c r="X41" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="W41" s="6" t="n">
+      <c r="Y41" s="6" t="n">
         <v>0.01666666666666667</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>WDGPH1</t>
+          <t>WARWSF2</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Western Downs GPH</t>
+          <t>Warwick Solar Farm 2</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3699,58 +3953,94 @@
           <t>Solar</t>
         </is>
       </c>
-      <c r="D42" s="3" t="inlineStr"/>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Middle Ridge</t>
+        </is>
+      </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>Non-REZ</t>
+          <t>Darling Downs</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
           <t>QLD</t>
         </is>
       </c>
-      <c r="H42" s="4" t="n">
-        <v>501</v>
-      </c>
-      <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="5" t="n">
-        <v>0.1745</v>
+      <c r="I42" s="4" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="J42" s="2" t="n">
+        <v>110</v>
       </c>
       <c r="K42" s="5" t="n">
-        <v>0.0315</v>
-      </c>
-      <c r="L42" s="5" t="inlineStr"/>
-      <c r="M42" s="5" t="inlineStr"/>
+        <v>0.394</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>0.5084</v>
+      </c>
+      <c r="M42" s="5" t="n">
+        <v>0.23150076097273</v>
+      </c>
       <c r="N42" s="5" t="n">
-        <v>0.9767</v>
-      </c>
-      <c r="O42" s="5" t="n">
-        <v>0.9761</v>
-      </c>
-      <c r="P42" s="6" t="inlineStr"/>
-      <c r="Q42" s="6" t="inlineStr"/>
-      <c r="R42" s="6" t="inlineStr"/>
-      <c r="S42" s="6" t="inlineStr"/>
-      <c r="T42" s="6" t="inlineStr"/>
-      <c r="U42" s="6" t="inlineStr"/>
-      <c r="V42" s="6" t="inlineStr"/>
-      <c r="W42" s="6" t="inlineStr"/>
+        <v>0.0544394673584698</v>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>per-DUID</t>
+        </is>
+      </c>
+      <c r="P42" s="5" t="n">
+        <v>0.9888</v>
+      </c>
+      <c r="Q42" s="5" t="n">
+        <v>0.987</v>
+      </c>
+      <c r="R42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="W42" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="X42" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Y42" s="6" t="n">
+        <v>0.01666666666666667</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>WHITSF1</t>
+          <t>WDGPH1</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Whitsunday Solar Farm</t>
+          <t>Western Downs GPH</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3758,84 +4048,52 @@
           <t>Solar</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>Strathmore</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t>Isaac</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="D43" s="3" t="inlineStr"/>
+      <c r="E43" s="2" t="inlineStr"/>
+      <c r="F43" s="3" t="inlineStr"/>
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>QLD</t>
         </is>
       </c>
-      <c r="H43" s="4" t="n">
-        <v>57.5</v>
-      </c>
-      <c r="I43" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J43" s="5" t="n">
-        <v>0.3037</v>
-      </c>
+      <c r="I43" s="4" t="n">
+        <v>501</v>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="5" t="n">
-        <v>0.3572</v>
+        <v>0.1745</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>0.221997464026796</v>
-      </c>
-      <c r="M43" s="5" t="n">
-        <v>0.0524178948511446</v>
-      </c>
-      <c r="N43" s="5" t="n">
-        <v>0.9398</v>
-      </c>
-      <c r="O43" s="5" t="n">
-        <v>0.8736</v>
-      </c>
-      <c r="P43" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R43" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S43" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="U43" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="V43" s="6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="W43" s="6" t="n">
-        <v>0.02333333333333333</v>
-      </c>
+        <v>0.0315</v>
+      </c>
+      <c r="M43" s="5" t="inlineStr"/>
+      <c r="N43" s="5" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr"/>
+      <c r="P43" s="5" t="n">
+        <v>0.9767</v>
+      </c>
+      <c r="Q43" s="5" t="n">
+        <v>0.9761</v>
+      </c>
+      <c r="R43" s="6" t="inlineStr"/>
+      <c r="S43" s="6" t="inlineStr"/>
+      <c r="T43" s="6" t="inlineStr"/>
+      <c r="U43" s="6" t="inlineStr"/>
+      <c r="V43" s="6" t="inlineStr"/>
+      <c r="W43" s="6" t="inlineStr"/>
+      <c r="X43" s="6" t="inlineStr"/>
+      <c r="Y43" s="6" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>WOOLGSF1</t>
+          <t>WHITSF1</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Woolooga Solar Farm</t>
+          <t>Whitsunday Solar Farm</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3845,7 +4103,7 @@
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Woolooga</t>
+          <t>Strathmore</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -3855,43 +4113,47 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>Wide Bay</t>
+          <t>Isaac</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
           <t>QLD</t>
         </is>
       </c>
-      <c r="H44" s="4" t="n">
-        <v>222.5</v>
-      </c>
-      <c r="I44" s="2" t="n">
-        <v>132</v>
-      </c>
-      <c r="J44" s="5" t="n">
-        <v>0.2353</v>
+      <c r="I44" s="4" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="J44" s="2" t="n">
+        <v>33</v>
       </c>
       <c r="K44" s="5" t="n">
-        <v>0.0665</v>
+        <v>0.3037</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>0.23173278497921</v>
+        <v>0.3572</v>
       </c>
       <c r="M44" s="5" t="n">
-        <v>0.0558256772551647</v>
+        <v>0.221997464026796</v>
       </c>
       <c r="N44" s="5" t="n">
-        <v>0.9787</v>
-      </c>
-      <c r="O44" s="5" t="n">
-        <v>0.9568</v>
-      </c>
-      <c r="P44" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q44" s="6" t="n">
-        <v>0</v>
+        <v>0.0524178948511446</v>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>per-DUID</t>
+        </is>
+      </c>
+      <c r="P44" s="5" t="n">
+        <v>0.9398</v>
+      </c>
+      <c r="Q44" s="5" t="n">
+        <v>0.8736</v>
       </c>
       <c r="R44" s="6" t="n">
         <v>0</v>
@@ -3900,27 +4162,33 @@
         <v>0</v>
       </c>
       <c r="T44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="W44" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="U44" s="6" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="V44" s="6" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="W44" s="6" t="n">
-        <v>0.04666666666666667</v>
+      <c r="X44" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Y44" s="6" t="n">
+        <v>0.02333333333333333</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>YARANSF1</t>
+          <t>WOOLGSF1</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Yarranlea Solar Farm</t>
+          <t>Woolooga Solar Farm</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3930,7 +4198,7 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Middle Ridge</t>
+          <t>Woolooga</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -3940,43 +4208,47 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>Darling Downs</t>
+          <t>Wide Bay</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
           <t>QLD</t>
         </is>
       </c>
-      <c r="H45" s="4" t="n">
-        <v>121</v>
-      </c>
-      <c r="I45" s="2" t="n">
-        <v>110</v>
-      </c>
-      <c r="J45" s="5" t="n">
-        <v>0.1371</v>
+      <c r="I45" s="4" t="n">
+        <v>222.5</v>
+      </c>
+      <c r="J45" s="2" t="n">
+        <v>132</v>
       </c>
       <c r="K45" s="5" t="n">
-        <v>0.2328</v>
+        <v>0.2353</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>0.23150076097273</v>
+        <v>0.0665</v>
       </c>
       <c r="M45" s="5" t="n">
-        <v>0.0544394673584698</v>
+        <v>0.23173278497921</v>
       </c>
       <c r="N45" s="5" t="n">
-        <v>0.9888</v>
-      </c>
-      <c r="O45" s="5" t="n">
-        <v>0.987</v>
-      </c>
-      <c r="P45" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" s="6" t="n">
-        <v>0</v>
+        <v>0.0558256772551647</v>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>per-DUID</t>
+        </is>
+      </c>
+      <c r="P45" s="5" t="n">
+        <v>0.9787</v>
+      </c>
+      <c r="Q45" s="5" t="n">
+        <v>0.9568</v>
       </c>
       <c r="R45" s="6" t="n">
         <v>0</v>
@@ -3985,79 +4257,123 @@
         <v>0</v>
       </c>
       <c r="T45" s="6" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="U45" s="6" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="V45" s="6" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="W45" s="6" t="n">
-        <v>0.01666666666666667</v>
+        <v>0.05</v>
+      </c>
+      <c r="X45" s="6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="Y45" s="6" t="n">
+        <v>0.04666666666666667</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>CLRKCWF1</t>
+          <t>YARANSF1</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Clarke Creek Wind Farm</t>
+          <t>Yarranlea Solar Farm</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Wind</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="inlineStr"/>
+          <t>Solar</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Middle Ridge</t>
+        </is>
+      </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>Non-REZ</t>
+          <t>Darling Downs</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
           <t>QLD</t>
         </is>
       </c>
-      <c r="H46" s="4" t="n">
-        <v>345.5</v>
-      </c>
-      <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="5" t="inlineStr"/>
+      <c r="I46" s="4" t="n">
+        <v>121</v>
+      </c>
+      <c r="J46" s="2" t="n">
+        <v>110</v>
+      </c>
       <c r="K46" s="5" t="n">
-        <v>0.0425</v>
-      </c>
-      <c r="L46" s="5" t="inlineStr"/>
-      <c r="M46" s="5" t="inlineStr"/>
+        <v>0.1371</v>
+      </c>
+      <c r="L46" s="5" t="n">
+        <v>0.2328</v>
+      </c>
+      <c r="M46" s="5" t="n">
+        <v>0.23150076097273</v>
+      </c>
       <c r="N46" s="5" t="n">
-        <v>0.9429999999999999</v>
-      </c>
-      <c r="O46" s="5" t="n">
-        <v>0.9313</v>
-      </c>
-      <c r="P46" s="6" t="inlineStr"/>
-      <c r="Q46" s="6" t="inlineStr"/>
-      <c r="R46" s="6" t="inlineStr"/>
-      <c r="S46" s="6" t="inlineStr"/>
-      <c r="T46" s="6" t="inlineStr"/>
-      <c r="U46" s="6" t="inlineStr"/>
-      <c r="V46" s="6" t="inlineStr"/>
-      <c r="W46" s="6" t="inlineStr"/>
+        <v>0.0544394673584698</v>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>per-DUID</t>
+        </is>
+      </c>
+      <c r="P46" s="5" t="n">
+        <v>0.9888</v>
+      </c>
+      <c r="Q46" s="5" t="n">
+        <v>0.987</v>
+      </c>
+      <c r="R46" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="W46" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="X46" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Y46" s="6" t="n">
+        <v>0.01666666666666667</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>CLRKCWF2</t>
+          <t>CLRKCWF1</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -4071,55 +4387,49 @@
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr"/>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F47" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr"/>
+      <c r="F47" s="3" t="inlineStr"/>
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>QLD</t>
         </is>
       </c>
-      <c r="H47" s="4" t="n">
-        <v>103.5</v>
-      </c>
-      <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="5" t="inlineStr"/>
-      <c r="K47" s="5" t="n">
-        <v>0.029</v>
-      </c>
-      <c r="L47" s="5" t="inlineStr"/>
+      <c r="I47" s="4" t="n">
+        <v>345.5</v>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="5" t="inlineStr"/>
+      <c r="L47" s="5" t="n">
+        <v>0.0425</v>
+      </c>
       <c r="M47" s="5" t="inlineStr"/>
-      <c r="N47" s="5" t="n">
+      <c r="N47" s="5" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr"/>
+      <c r="P47" s="5" t="n">
         <v>0.9429999999999999</v>
       </c>
-      <c r="O47" s="5" t="n">
+      <c r="Q47" s="5" t="n">
         <v>0.9313</v>
       </c>
-      <c r="P47" s="6" t="inlineStr"/>
-      <c r="Q47" s="6" t="inlineStr"/>
       <c r="R47" s="6" t="inlineStr"/>
       <c r="S47" s="6" t="inlineStr"/>
       <c r="T47" s="6" t="inlineStr"/>
       <c r="U47" s="6" t="inlineStr"/>
       <c r="V47" s="6" t="inlineStr"/>
       <c r="W47" s="6" t="inlineStr"/>
+      <c r="X47" s="6" t="inlineStr"/>
+      <c r="Y47" s="6" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>COOPGWF1</t>
+          <t>CLRKCWF2</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Coopers Gap Wind Farm</t>
+          <t>Clarke Creek Wind Farm</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4128,57 +4438,49 @@
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr"/>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F48" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr"/>
+      <c r="F48" s="3" t="inlineStr"/>
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>QLD</t>
         </is>
       </c>
-      <c r="H48" s="4" t="n">
-        <v>452</v>
-      </c>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="5" t="n">
-        <v>0.0306</v>
-      </c>
-      <c r="K48" s="5" t="n">
-        <v>0.0532</v>
-      </c>
-      <c r="L48" s="5" t="inlineStr"/>
+      <c r="I48" s="4" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="5" t="inlineStr"/>
+      <c r="L48" s="5" t="n">
+        <v>0.029</v>
+      </c>
       <c r="M48" s="5" t="inlineStr"/>
-      <c r="N48" s="5" t="n">
-        <v>0.9691</v>
-      </c>
-      <c r="O48" s="5" t="n">
-        <v>0.9704</v>
-      </c>
-      <c r="P48" s="6" t="inlineStr"/>
-      <c r="Q48" s="6" t="inlineStr"/>
+      <c r="N48" s="5" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr"/>
+      <c r="P48" s="5" t="n">
+        <v>0.9429999999999999</v>
+      </c>
+      <c r="Q48" s="5" t="n">
+        <v>0.9313</v>
+      </c>
       <c r="R48" s="6" t="inlineStr"/>
       <c r="S48" s="6" t="inlineStr"/>
       <c r="T48" s="6" t="inlineStr"/>
       <c r="U48" s="6" t="inlineStr"/>
       <c r="V48" s="6" t="inlineStr"/>
       <c r="W48" s="6" t="inlineStr"/>
+      <c r="X48" s="6" t="inlineStr"/>
+      <c r="Y48" s="6" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>DULAWF1</t>
+          <t>COOPGWF1</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Dulacca Wind Farm</t>
+          <t>Coopers Gap Wind Farm</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4187,57 +4489,51 @@
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr"/>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F49" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr"/>
+      <c r="F49" s="3" t="inlineStr"/>
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>QLD</t>
         </is>
       </c>
-      <c r="H49" s="4" t="n">
-        <v>180</v>
-      </c>
-      <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="5" t="n">
-        <v>0.0033</v>
-      </c>
+      <c r="I49" s="4" t="n">
+        <v>452</v>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="5" t="n">
-        <v>0.0011</v>
-      </c>
-      <c r="L49" s="5" t="inlineStr"/>
+        <v>0.0306</v>
+      </c>
+      <c r="L49" s="5" t="n">
+        <v>0.0532</v>
+      </c>
       <c r="M49" s="5" t="inlineStr"/>
-      <c r="N49" s="5" t="n">
-        <v>0.9853</v>
-      </c>
-      <c r="O49" s="5" t="n">
-        <v>0.987</v>
-      </c>
-      <c r="P49" s="6" t="inlineStr"/>
-      <c r="Q49" s="6" t="inlineStr"/>
+      <c r="N49" s="5" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr"/>
+      <c r="P49" s="5" t="n">
+        <v>0.9691</v>
+      </c>
+      <c r="Q49" s="5" t="n">
+        <v>0.9704</v>
+      </c>
       <c r="R49" s="6" t="inlineStr"/>
       <c r="S49" s="6" t="inlineStr"/>
       <c r="T49" s="6" t="inlineStr"/>
       <c r="U49" s="6" t="inlineStr"/>
       <c r="V49" s="6" t="inlineStr"/>
       <c r="W49" s="6" t="inlineStr"/>
+      <c r="X49" s="6" t="inlineStr"/>
+      <c r="Y49" s="6" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>KABANWF1</t>
+          <t>DULAWF1</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Kaban Wind Farm</t>
+          <t>Dulacca Wind Farm</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4246,57 +4542,51 @@
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr"/>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F50" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr"/>
+      <c r="F50" s="3" t="inlineStr"/>
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>QLD</t>
         </is>
       </c>
-      <c r="H50" s="4" t="n">
-        <v>156</v>
-      </c>
-      <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="5" t="n">
-        <v>0.0141</v>
-      </c>
+      <c r="I50" s="4" t="n">
+        <v>180</v>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="5" t="n">
-        <v>0.0766</v>
-      </c>
-      <c r="L50" s="5" t="inlineStr"/>
+        <v>0.0033</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>0.0011</v>
+      </c>
       <c r="M50" s="5" t="inlineStr"/>
-      <c r="N50" s="5" t="n">
-        <v>0.9696</v>
-      </c>
-      <c r="O50" s="5" t="n">
-        <v>0.9442</v>
-      </c>
-      <c r="P50" s="6" t="inlineStr"/>
-      <c r="Q50" s="6" t="inlineStr"/>
+      <c r="N50" s="5" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr"/>
+      <c r="P50" s="5" t="n">
+        <v>0.9853</v>
+      </c>
+      <c r="Q50" s="5" t="n">
+        <v>0.987</v>
+      </c>
       <c r="R50" s="6" t="inlineStr"/>
       <c r="S50" s="6" t="inlineStr"/>
       <c r="T50" s="6" t="inlineStr"/>
       <c r="U50" s="6" t="inlineStr"/>
       <c r="V50" s="6" t="inlineStr"/>
       <c r="W50" s="6" t="inlineStr"/>
+      <c r="X50" s="6" t="inlineStr"/>
+      <c r="Y50" s="6" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>KEPWF1</t>
+          <t>KABANWF1</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Kennedy Energy Park</t>
+          <t>Kaban Wind Farm</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4305,57 +4595,51 @@
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr"/>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F51" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr"/>
+      <c r="F51" s="3" t="inlineStr"/>
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>QLD</t>
         </is>
       </c>
-      <c r="H51" s="4" t="n">
-        <v>43</v>
-      </c>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="5" t="n">
-        <v>0.024</v>
-      </c>
+      <c r="I51" s="4" t="n">
+        <v>156</v>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="5" t="n">
-        <v>0.0136</v>
-      </c>
-      <c r="L51" s="5" t="inlineStr"/>
+        <v>0.0141</v>
+      </c>
+      <c r="L51" s="5" t="n">
+        <v>0.0766</v>
+      </c>
       <c r="M51" s="5" t="inlineStr"/>
-      <c r="N51" s="5" t="n">
-        <v>0.9813</v>
-      </c>
-      <c r="O51" s="5" t="n">
-        <v>0.9574</v>
-      </c>
-      <c r="P51" s="6" t="inlineStr"/>
-      <c r="Q51" s="6" t="inlineStr"/>
+      <c r="N51" s="5" t="inlineStr"/>
+      <c r="O51" s="2" t="inlineStr"/>
+      <c r="P51" s="5" t="n">
+        <v>0.9696</v>
+      </c>
+      <c r="Q51" s="5" t="n">
+        <v>0.9442</v>
+      </c>
       <c r="R51" s="6" t="inlineStr"/>
       <c r="S51" s="6" t="inlineStr"/>
       <c r="T51" s="6" t="inlineStr"/>
       <c r="U51" s="6" t="inlineStr"/>
       <c r="V51" s="6" t="inlineStr"/>
       <c r="W51" s="6" t="inlineStr"/>
+      <c r="X51" s="6" t="inlineStr"/>
+      <c r="Y51" s="6" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>MCINTYR1</t>
+          <t>KEPWF1</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>MacIntyre Wind Farm</t>
+          <t>Kennedy Energy Park</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4364,55 +4648,51 @@
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr"/>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F52" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr"/>
+      <c r="F52" s="3" t="inlineStr"/>
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>QLD</t>
         </is>
       </c>
-      <c r="H52" s="4" t="n">
-        <v>923</v>
-      </c>
-      <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="5" t="inlineStr"/>
+      <c r="I52" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="5" t="n">
-        <v>0.0035</v>
-      </c>
-      <c r="L52" s="5" t="inlineStr"/>
+        <v>0.024</v>
+      </c>
+      <c r="L52" s="5" t="n">
+        <v>0.0136</v>
+      </c>
       <c r="M52" s="5" t="inlineStr"/>
-      <c r="N52" s="5" t="n">
-        <v>0.9723000000000001</v>
-      </c>
-      <c r="O52" s="5" t="n">
-        <v>0.9729</v>
-      </c>
-      <c r="P52" s="6" t="inlineStr"/>
-      <c r="Q52" s="6" t="inlineStr"/>
+      <c r="N52" s="5" t="inlineStr"/>
+      <c r="O52" s="2" t="inlineStr"/>
+      <c r="P52" s="5" t="n">
+        <v>0.9813</v>
+      </c>
+      <c r="Q52" s="5" t="n">
+        <v>0.9574</v>
+      </c>
       <c r="R52" s="6" t="inlineStr"/>
       <c r="S52" s="6" t="inlineStr"/>
       <c r="T52" s="6" t="inlineStr"/>
       <c r="U52" s="6" t="inlineStr"/>
       <c r="V52" s="6" t="inlineStr"/>
       <c r="W52" s="6" t="inlineStr"/>
+      <c r="X52" s="6" t="inlineStr"/>
+      <c r="Y52" s="6" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>MEWF1</t>
+          <t>MCINTYR1</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Mount Emerald Wind Farm</t>
+          <t>MacIntyre Wind Farm</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4421,57 +4701,49 @@
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr"/>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F53" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr"/>
+      <c r="F53" s="3" t="inlineStr"/>
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>QLD</t>
         </is>
       </c>
-      <c r="H53" s="4" t="n">
-        <v>180</v>
-      </c>
-      <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="5" t="n">
-        <v>0.0425</v>
-      </c>
-      <c r="K53" s="5" t="n">
-        <v>0.0189</v>
-      </c>
-      <c r="L53" s="5" t="inlineStr"/>
+      <c r="I53" s="4" t="n">
+        <v>923</v>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="5" t="inlineStr"/>
+      <c r="L53" s="5" t="n">
+        <v>0.0035</v>
+      </c>
       <c r="M53" s="5" t="inlineStr"/>
-      <c r="N53" s="5" t="n">
-        <v>0.9649</v>
-      </c>
-      <c r="O53" s="5" t="n">
-        <v>0.9396</v>
-      </c>
-      <c r="P53" s="6" t="inlineStr"/>
-      <c r="Q53" s="6" t="inlineStr"/>
+      <c r="N53" s="5" t="inlineStr"/>
+      <c r="O53" s="2" t="inlineStr"/>
+      <c r="P53" s="5" t="n">
+        <v>0.9723000000000001</v>
+      </c>
+      <c r="Q53" s="5" t="n">
+        <v>0.9729</v>
+      </c>
       <c r="R53" s="6" t="inlineStr"/>
       <c r="S53" s="6" t="inlineStr"/>
       <c r="T53" s="6" t="inlineStr"/>
       <c r="U53" s="6" t="inlineStr"/>
       <c r="V53" s="6" t="inlineStr"/>
       <c r="W53" s="6" t="inlineStr"/>
+      <c r="X53" s="6" t="inlineStr"/>
+      <c r="Y53" s="6" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>WAMBOWF1</t>
+          <t>MEWF1</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Wambo Wind Farm 1</t>
+          <t>Mount Emerald Wind Farm</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4480,55 +4752,51 @@
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr"/>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F54" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr"/>
+      <c r="F54" s="3" t="inlineStr"/>
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>QLD</t>
         </is>
       </c>
-      <c r="H54" s="4" t="n">
-        <v>252</v>
-      </c>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="5" t="inlineStr"/>
+      <c r="I54" s="4" t="n">
+        <v>180</v>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="5" t="n">
-        <v>0.0039</v>
-      </c>
-      <c r="L54" s="5" t="inlineStr"/>
+        <v>0.0425</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>0.0189</v>
+      </c>
       <c r="M54" s="5" t="inlineStr"/>
-      <c r="N54" s="5" t="n">
-        <v>0.967</v>
-      </c>
-      <c r="O54" s="5" t="n">
-        <v>0.9701</v>
-      </c>
-      <c r="P54" s="6" t="inlineStr"/>
-      <c r="Q54" s="6" t="inlineStr"/>
+      <c r="N54" s="5" t="inlineStr"/>
+      <c r="O54" s="2" t="inlineStr"/>
+      <c r="P54" s="5" t="n">
+        <v>0.9649</v>
+      </c>
+      <c r="Q54" s="5" t="n">
+        <v>0.9396</v>
+      </c>
       <c r="R54" s="6" t="inlineStr"/>
       <c r="S54" s="6" t="inlineStr"/>
       <c r="T54" s="6" t="inlineStr"/>
       <c r="U54" s="6" t="inlineStr"/>
       <c r="V54" s="6" t="inlineStr"/>
       <c r="W54" s="6" t="inlineStr"/>
+      <c r="X54" s="6" t="inlineStr"/>
+      <c r="Y54" s="6" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>WAMBOWF2</t>
+          <t>WAMBOWF1</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Wambo Wind Farm 2</t>
+          <t>Wambo Wind Farm 1</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4537,49 +4805,49 @@
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr"/>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F55" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr"/>
+      <c r="F55" s="3" t="inlineStr"/>
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>QLD</t>
         </is>
       </c>
-      <c r="H55" s="4" t="n">
-        <v>254</v>
-      </c>
-      <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" s="5" t="inlineStr"/>
+      <c r="I55" s="4" t="n">
+        <v>252</v>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="5" t="inlineStr"/>
-      <c r="L55" s="5" t="inlineStr"/>
+      <c r="L55" s="5" t="n">
+        <v>0.0039</v>
+      </c>
       <c r="M55" s="5" t="inlineStr"/>
       <c r="N55" s="5" t="inlineStr"/>
-      <c r="O55" s="5" t="inlineStr"/>
-      <c r="P55" s="6" t="inlineStr"/>
-      <c r="Q55" s="6" t="inlineStr"/>
+      <c r="O55" s="2" t="inlineStr"/>
+      <c r="P55" s="5" t="n">
+        <v>0.967</v>
+      </c>
+      <c r="Q55" s="5" t="n">
+        <v>0.9701</v>
+      </c>
       <c r="R55" s="6" t="inlineStr"/>
       <c r="S55" s="6" t="inlineStr"/>
       <c r="T55" s="6" t="inlineStr"/>
       <c r="U55" s="6" t="inlineStr"/>
       <c r="V55" s="6" t="inlineStr"/>
       <c r="W55" s="6" t="inlineStr"/>
+      <c r="X55" s="6" t="inlineStr"/>
+      <c r="Y55" s="6" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>WHILL1</t>
+          <t>WAMBOWF2</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Windy Hill Wind Farm</t>
+          <t>Wambo Wind Farm 2</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4588,43 +4856,86 @@
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr"/>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F56" s="3" t="inlineStr">
-        <is>
-          <t>Non-REZ</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr"/>
+      <c r="F56" s="3" t="inlineStr"/>
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>QLD</t>
         </is>
       </c>
-      <c r="H56" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="5" t="inlineStr"/>
+      <c r="I56" s="4" t="n">
+        <v>254</v>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="5" t="inlineStr"/>
       <c r="L56" s="5" t="inlineStr"/>
       <c r="M56" s="5" t="inlineStr"/>
-      <c r="N56" s="5" t="n">
-        <v>1.0128</v>
-      </c>
-      <c r="O56" s="5" t="n">
-        <v>1.013</v>
-      </c>
-      <c r="P56" s="6" t="inlineStr"/>
-      <c r="Q56" s="6" t="inlineStr"/>
+      <c r="N56" s="5" t="inlineStr"/>
+      <c r="O56" s="2" t="inlineStr"/>
+      <c r="P56" s="5" t="n">
+        <v>0.9671999999999999</v>
+      </c>
+      <c r="Q56" s="5" t="n">
+        <v>0.9685</v>
+      </c>
       <c r="R56" s="6" t="inlineStr"/>
       <c r="S56" s="6" t="inlineStr"/>
       <c r="T56" s="6" t="inlineStr"/>
       <c r="U56" s="6" t="inlineStr"/>
       <c r="V56" s="6" t="inlineStr"/>
       <c r="W56" s="6" t="inlineStr"/>
+      <c r="X56" s="6" t="inlineStr"/>
+      <c r="Y56" s="6" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>WHILL1</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>Windy Hill Wind Farm</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr"/>
+      <c r="E57" s="2" t="inlineStr"/>
+      <c r="F57" s="3" t="inlineStr"/>
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>QLD</t>
+        </is>
+      </c>
+      <c r="I57" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="5" t="inlineStr"/>
+      <c r="L57" s="5" t="inlineStr"/>
+      <c r="M57" s="5" t="inlineStr"/>
+      <c r="N57" s="5" t="inlineStr"/>
+      <c r="O57" s="2" t="inlineStr"/>
+      <c r="P57" s="5" t="n">
+        <v>1.0128</v>
+      </c>
+      <c r="Q57" s="5" t="n">
+        <v>1.013</v>
+      </c>
+      <c r="R57" s="6" t="inlineStr"/>
+      <c r="S57" s="6" t="inlineStr"/>
+      <c r="T57" s="6" t="inlineStr"/>
+      <c r="U57" s="6" t="inlineStr"/>
+      <c r="V57" s="6" t="inlineStr"/>
+      <c r="W57" s="6" t="inlineStr"/>
+      <c r="X57" s="6" t="inlineStr"/>
+      <c r="Y57" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4637,7 +4948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V56"/>
+  <dimension ref="A1:V57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4800,42 +5111,18 @@
       <c r="G2" s="5" t="inlineStr"/>
       <c r="H2" s="5" t="inlineStr"/>
       <c r="I2" s="5" t="inlineStr"/>
-      <c r="J2" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J2" s="5" t="inlineStr"/>
       <c r="K2" s="5" t="inlineStr"/>
-      <c r="L2" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L2" s="5" t="inlineStr"/>
       <c r="M2" s="5" t="inlineStr"/>
-      <c r="N2" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N2" s="5" t="inlineStr"/>
       <c r="O2" s="5" t="inlineStr"/>
       <c r="P2" s="5" t="inlineStr"/>
-      <c r="Q2" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q2" s="5" t="inlineStr"/>
       <c r="R2" s="5" t="inlineStr"/>
-      <c r="S2" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S2" s="5" t="inlineStr"/>
       <c r="T2" s="5" t="inlineStr"/>
-      <c r="U2" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U2" s="5" t="inlineStr"/>
       <c r="V2" s="5" t="inlineStr"/>
     </row>
     <row r="3">
@@ -4924,42 +5211,18 @@
       <c r="G4" s="5" t="inlineStr"/>
       <c r="H4" s="5" t="inlineStr"/>
       <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J4" s="5" t="inlineStr"/>
       <c r="K4" s="5" t="inlineStr"/>
-      <c r="L4" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L4" s="5" t="inlineStr"/>
       <c r="M4" s="5" t="inlineStr"/>
-      <c r="N4" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N4" s="5" t="inlineStr"/>
       <c r="O4" s="5" t="inlineStr"/>
       <c r="P4" s="5" t="inlineStr"/>
-      <c r="Q4" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q4" s="5" t="inlineStr"/>
       <c r="R4" s="5" t="inlineStr"/>
-      <c r="S4" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S4" s="5" t="inlineStr"/>
       <c r="T4" s="5" t="inlineStr"/>
-      <c r="U4" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U4" s="5" t="inlineStr"/>
       <c r="V4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
@@ -5068,42 +5331,18 @@
       <c r="G6" s="5" t="inlineStr"/>
       <c r="H6" s="5" t="inlineStr"/>
       <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J6" s="5" t="inlineStr"/>
       <c r="K6" s="5" t="inlineStr"/>
-      <c r="L6" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L6" s="5" t="inlineStr"/>
       <c r="M6" s="5" t="inlineStr"/>
-      <c r="N6" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N6" s="5" t="inlineStr"/>
       <c r="O6" s="5" t="inlineStr"/>
       <c r="P6" s="5" t="inlineStr"/>
-      <c r="Q6" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q6" s="5" t="inlineStr"/>
       <c r="R6" s="5" t="inlineStr"/>
-      <c r="S6" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S6" s="5" t="inlineStr"/>
       <c r="T6" s="5" t="inlineStr"/>
-      <c r="U6" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U6" s="5" t="inlineStr"/>
       <c r="V6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
@@ -5128,42 +5367,18 @@
       <c r="G7" s="5" t="inlineStr"/>
       <c r="H7" s="5" t="inlineStr"/>
       <c r="I7" s="5" t="inlineStr"/>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J7" s="5" t="inlineStr"/>
       <c r="K7" s="5" t="inlineStr"/>
-      <c r="L7" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L7" s="5" t="inlineStr"/>
       <c r="M7" s="5" t="inlineStr"/>
-      <c r="N7" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N7" s="5" t="inlineStr"/>
       <c r="O7" s="5" t="inlineStr"/>
       <c r="P7" s="5" t="inlineStr"/>
-      <c r="Q7" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q7" s="5" t="inlineStr"/>
       <c r="R7" s="5" t="inlineStr"/>
-      <c r="S7" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S7" s="5" t="inlineStr"/>
       <c r="T7" s="5" t="inlineStr"/>
-      <c r="U7" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U7" s="5" t="inlineStr"/>
       <c r="V7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
@@ -6012,42 +6227,18 @@
       <c r="G18" s="5" t="inlineStr"/>
       <c r="H18" s="5" t="inlineStr"/>
       <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J18" s="5" t="inlineStr"/>
       <c r="K18" s="5" t="inlineStr"/>
-      <c r="L18" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L18" s="5" t="inlineStr"/>
       <c r="M18" s="5" t="inlineStr"/>
-      <c r="N18" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N18" s="5" t="inlineStr"/>
       <c r="O18" s="5" t="inlineStr"/>
       <c r="P18" s="5" t="inlineStr"/>
-      <c r="Q18" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q18" s="5" t="inlineStr"/>
       <c r="R18" s="5" t="inlineStr"/>
-      <c r="S18" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S18" s="5" t="inlineStr"/>
       <c r="T18" s="5" t="inlineStr"/>
-      <c r="U18" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U18" s="5" t="inlineStr"/>
       <c r="V18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
@@ -6858,42 +7049,18 @@
       <c r="G29" s="5" t="inlineStr"/>
       <c r="H29" s="5" t="inlineStr"/>
       <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J29" s="5" t="inlineStr"/>
       <c r="K29" s="5" t="inlineStr"/>
-      <c r="L29" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L29" s="5" t="inlineStr"/>
       <c r="M29" s="5" t="inlineStr"/>
-      <c r="N29" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N29" s="5" t="inlineStr"/>
       <c r="O29" s="5" t="inlineStr"/>
       <c r="P29" s="5" t="inlineStr"/>
-      <c r="Q29" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q29" s="5" t="inlineStr"/>
       <c r="R29" s="5" t="inlineStr"/>
-      <c r="S29" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S29" s="5" t="inlineStr"/>
       <c r="T29" s="5" t="inlineStr"/>
-      <c r="U29" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U29" s="5" t="inlineStr"/>
       <c r="V29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
@@ -7002,42 +7169,18 @@
       <c r="G31" s="5" t="inlineStr"/>
       <c r="H31" s="5" t="inlineStr"/>
       <c r="I31" s="5" t="inlineStr"/>
-      <c r="J31" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J31" s="5" t="inlineStr"/>
       <c r="K31" s="5" t="inlineStr"/>
-      <c r="L31" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L31" s="5" t="inlineStr"/>
       <c r="M31" s="5" t="inlineStr"/>
-      <c r="N31" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N31" s="5" t="inlineStr"/>
       <c r="O31" s="5" t="inlineStr"/>
       <c r="P31" s="5" t="inlineStr"/>
-      <c r="Q31" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q31" s="5" t="inlineStr"/>
       <c r="R31" s="5" t="inlineStr"/>
-      <c r="S31" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S31" s="5" t="inlineStr"/>
       <c r="T31" s="5" t="inlineStr"/>
-      <c r="U31" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U31" s="5" t="inlineStr"/>
       <c r="V31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
@@ -7623,7 +7766,7 @@
         <v>0.9975000000000001</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>0.9903999999999999</v>
+        <v>0.985</v>
       </c>
       <c r="E39" s="5" t="n">
         <v>0.1975</v>
@@ -7695,7 +7838,7 @@
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>WARWSF1</t>
+          <t>WANDSF2</t>
         </is>
       </c>
       <c r="B40" s="8" t="inlineStr">
@@ -7704,82 +7847,34 @@
         </is>
       </c>
       <c r="C40" s="5" t="n">
-        <v>0.9888</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>0.987</v>
-      </c>
-      <c r="E40" s="5" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="F40" s="5" t="n">
-        <v>0.5046</v>
-      </c>
-      <c r="G40" s="5" t="n">
-        <v>0.23150076097273</v>
-      </c>
-      <c r="H40" s="5" t="n">
-        <v>0.0544394673584698</v>
-      </c>
-      <c r="I40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="Q40" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R40" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="S40" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T40" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="U40" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V40" s="5" t="n">
-        <v>0.01666666666666667</v>
-      </c>
+        <v>0.985</v>
+      </c>
+      <c r="E40" s="5" t="inlineStr"/>
+      <c r="F40" s="5" t="inlineStr"/>
+      <c r="G40" s="5" t="inlineStr"/>
+      <c r="H40" s="5" t="inlineStr"/>
+      <c r="I40" s="5" t="inlineStr"/>
+      <c r="J40" s="5" t="inlineStr"/>
+      <c r="K40" s="5" t="inlineStr"/>
+      <c r="L40" s="5" t="inlineStr"/>
+      <c r="M40" s="5" t="inlineStr"/>
+      <c r="N40" s="5" t="inlineStr"/>
+      <c r="O40" s="5" t="inlineStr"/>
+      <c r="P40" s="5" t="inlineStr"/>
+      <c r="Q40" s="5" t="inlineStr"/>
+      <c r="R40" s="5" t="inlineStr"/>
+      <c r="S40" s="5" t="inlineStr"/>
+      <c r="T40" s="5" t="inlineStr"/>
+      <c r="U40" s="5" t="inlineStr"/>
+      <c r="V40" s="5" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>WARWSF2</t>
+          <t>WARWSF1</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
@@ -7794,10 +7889,10 @@
         <v>0.987</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>0.394</v>
+        <v>0.39</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>0.5084</v>
+        <v>0.5046</v>
       </c>
       <c r="G41" s="5" t="n">
         <v>0.23150076097273</v>
@@ -7863,7 +7958,7 @@
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>WDGPH1</t>
+          <t>WARWSF2</t>
         </is>
       </c>
       <c r="B42" s="8" t="inlineStr">
@@ -7872,62 +7967,82 @@
         </is>
       </c>
       <c r="C42" s="5" t="n">
-        <v>0.9767</v>
+        <v>0.9888</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>0.9761</v>
+        <v>0.987</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>0.1745</v>
+        <v>0.394</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>0.0315</v>
-      </c>
-      <c r="G42" s="5" t="inlineStr"/>
-      <c r="H42" s="5" t="inlineStr"/>
-      <c r="I42" s="5" t="inlineStr"/>
+        <v>0.5084</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>0.23150076097273</v>
+      </c>
+      <c r="H42" s="5" t="n">
+        <v>0.0544394673584698</v>
+      </c>
+      <c r="I42" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
           <t>25-26</t>
         </is>
       </c>
-      <c r="K42" s="5" t="inlineStr"/>
+      <c r="K42" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="L42" s="5" t="inlineStr">
         <is>
           <t>26-27</t>
         </is>
       </c>
-      <c r="M42" s="5" t="inlineStr"/>
+      <c r="M42" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="N42" s="5" t="inlineStr">
         <is>
           <t>27-28</t>
         </is>
       </c>
-      <c r="O42" s="5" t="inlineStr"/>
-      <c r="P42" s="5" t="inlineStr"/>
+      <c r="O42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" s="5" t="n">
+        <v>0.01</v>
+      </c>
       <c r="Q42" s="5" t="inlineStr">
         <is>
           <t>25-26</t>
         </is>
       </c>
-      <c r="R42" s="5" t="inlineStr"/>
+      <c r="R42" s="5" t="n">
+        <v>0.02</v>
+      </c>
       <c r="S42" s="5" t="inlineStr">
         <is>
           <t>26-27</t>
         </is>
       </c>
-      <c r="T42" s="5" t="inlineStr"/>
+      <c r="T42" s="5" t="n">
+        <v>0.02</v>
+      </c>
       <c r="U42" s="5" t="inlineStr">
         <is>
           <t>27-28</t>
         </is>
       </c>
-      <c r="V42" s="5" t="inlineStr"/>
+      <c r="V42" s="5" t="n">
+        <v>0.01666666666666667</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>WHITSF1</t>
+          <t>WDGPH1</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
@@ -7936,82 +8051,38 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>0.9398</v>
+        <v>0.9767</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>0.8736</v>
+        <v>0.9761</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>0.3037</v>
+        <v>0.1745</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>0.3572</v>
-      </c>
-      <c r="G43" s="5" t="n">
-        <v>0.221997464026796</v>
-      </c>
-      <c r="H43" s="5" t="n">
-        <v>0.0524178948511446</v>
-      </c>
-      <c r="I43" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="K43" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="M43" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="O43" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="Q43" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R43" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="S43" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
-      <c r="T43" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="U43" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
-      <c r="V43" s="5" t="n">
-        <v>0.02333333333333333</v>
-      </c>
+        <v>0.0315</v>
+      </c>
+      <c r="G43" s="5" t="inlineStr"/>
+      <c r="H43" s="5" t="inlineStr"/>
+      <c r="I43" s="5" t="inlineStr"/>
+      <c r="J43" s="5" t="inlineStr"/>
+      <c r="K43" s="5" t="inlineStr"/>
+      <c r="L43" s="5" t="inlineStr"/>
+      <c r="M43" s="5" t="inlineStr"/>
+      <c r="N43" s="5" t="inlineStr"/>
+      <c r="O43" s="5" t="inlineStr"/>
+      <c r="P43" s="5" t="inlineStr"/>
+      <c r="Q43" s="5" t="inlineStr"/>
+      <c r="R43" s="5" t="inlineStr"/>
+      <c r="S43" s="5" t="inlineStr"/>
+      <c r="T43" s="5" t="inlineStr"/>
+      <c r="U43" s="5" t="inlineStr"/>
+      <c r="V43" s="5" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>WOOLGSF1</t>
+          <t>WHITSF1</t>
         </is>
       </c>
       <c r="B44" s="8" t="inlineStr">
@@ -8020,22 +8091,22 @@
         </is>
       </c>
       <c r="C44" s="5" t="n">
-        <v>0.9787</v>
+        <v>0.9398</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>0.9568</v>
+        <v>0.8736</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>0.2353</v>
+        <v>0.3037</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>0.0665</v>
+        <v>0.3572</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.23173278497921</v>
+        <v>0.221997464026796</v>
       </c>
       <c r="H44" s="5" t="n">
-        <v>0.0558256772551647</v>
+        <v>0.0524178948511446</v>
       </c>
       <c r="I44" s="5" t="n">
         <v>0</v>
@@ -8065,23 +8136,23 @@
         <v>0</v>
       </c>
       <c r="P44" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q44" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R44" s="5" t="n">
         <v>0.03</v>
       </c>
-      <c r="Q44" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="R44" s="5" t="n">
-        <v>0.05</v>
-      </c>
       <c r="S44" s="5" t="inlineStr">
         <is>
           <t>26-27</t>
         </is>
       </c>
       <c r="T44" s="5" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="U44" s="5" t="inlineStr">
         <is>
@@ -8089,13 +8160,13 @@
         </is>
       </c>
       <c r="V44" s="5" t="n">
-        <v>0.04666666666666667</v>
+        <v>0.02333333333333333</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>YARANSF1</t>
+          <t>WOOLGSF1</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
@@ -8104,22 +8175,22 @@
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>0.9888</v>
+        <v>0.9787</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>0.987</v>
+        <v>0.9568</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>0.1371</v>
+        <v>0.2353</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>0.2328</v>
+        <v>0.0665</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.23150076097273</v>
+        <v>0.23173278497921</v>
       </c>
       <c r="H45" s="5" t="n">
-        <v>0.0544394673584698</v>
+        <v>0.0558256772551647</v>
       </c>
       <c r="I45" s="5" t="n">
         <v>0</v>
@@ -8149,7 +8220,7 @@
         <v>0</v>
       </c>
       <c r="P45" s="5" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="Q45" s="5" t="inlineStr">
         <is>
@@ -8157,7 +8228,7 @@
         </is>
       </c>
       <c r="R45" s="5" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="S45" s="5" t="inlineStr">
         <is>
@@ -8165,7 +8236,7 @@
         </is>
       </c>
       <c r="T45" s="5" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="U45" s="5" t="inlineStr">
         <is>
@@ -8173,75 +8244,97 @@
         </is>
       </c>
       <c r="V45" s="5" t="n">
-        <v>0.01666666666666667</v>
+        <v>0.04666666666666667</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t>CLRKCWF1</t>
+          <t>YARANSF1</t>
         </is>
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>Wind</t>
+          <t>Solar</t>
         </is>
       </c>
       <c r="C46" s="5" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.9888</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>0.9313</v>
-      </c>
-      <c r="E46" s="5" t="inlineStr"/>
+        <v>0.987</v>
+      </c>
+      <c r="E46" s="5" t="n">
+        <v>0.1371</v>
+      </c>
       <c r="F46" s="5" t="n">
-        <v>0.0425</v>
-      </c>
-      <c r="G46" s="5" t="inlineStr"/>
-      <c r="H46" s="5" t="inlineStr"/>
-      <c r="I46" s="5" t="inlineStr"/>
+        <v>0.2328</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>0.23150076097273</v>
+      </c>
+      <c r="H46" s="5" t="n">
+        <v>0.0544394673584698</v>
+      </c>
+      <c r="I46" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
           <t>25-26</t>
         </is>
       </c>
-      <c r="K46" s="5" t="inlineStr"/>
+      <c r="K46" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="L46" s="5" t="inlineStr">
         <is>
           <t>26-27</t>
         </is>
       </c>
-      <c r="M46" s="5" t="inlineStr"/>
+      <c r="M46" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="N46" s="5" t="inlineStr">
         <is>
           <t>27-28</t>
         </is>
       </c>
-      <c r="O46" s="5" t="inlineStr"/>
-      <c r="P46" s="5" t="inlineStr"/>
+      <c r="O46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" s="5" t="n">
+        <v>0.01</v>
+      </c>
       <c r="Q46" s="5" t="inlineStr">
         <is>
           <t>25-26</t>
         </is>
       </c>
-      <c r="R46" s="5" t="inlineStr"/>
+      <c r="R46" s="5" t="n">
+        <v>0.02</v>
+      </c>
       <c r="S46" s="5" t="inlineStr">
         <is>
           <t>26-27</t>
         </is>
       </c>
-      <c r="T46" s="5" t="inlineStr"/>
+      <c r="T46" s="5" t="n">
+        <v>0.02</v>
+      </c>
       <c r="U46" s="5" t="inlineStr">
         <is>
           <t>27-28</t>
         </is>
       </c>
-      <c r="V46" s="5" t="inlineStr"/>
+      <c r="V46" s="5" t="n">
+        <v>0.01666666666666667</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>CLRKCWF2</t>
+          <t>CLRKCWF1</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
@@ -8257,53 +8350,29 @@
       </c>
       <c r="E47" s="5" t="inlineStr"/>
       <c r="F47" s="5" t="n">
-        <v>0.029</v>
+        <v>0.0425</v>
       </c>
       <c r="G47" s="5" t="inlineStr"/>
       <c r="H47" s="5" t="inlineStr"/>
       <c r="I47" s="5" t="inlineStr"/>
-      <c r="J47" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J47" s="5" t="inlineStr"/>
       <c r="K47" s="5" t="inlineStr"/>
-      <c r="L47" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L47" s="5" t="inlineStr"/>
       <c r="M47" s="5" t="inlineStr"/>
-      <c r="N47" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N47" s="5" t="inlineStr"/>
       <c r="O47" s="5" t="inlineStr"/>
       <c r="P47" s="5" t="inlineStr"/>
-      <c r="Q47" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q47" s="5" t="inlineStr"/>
       <c r="R47" s="5" t="inlineStr"/>
-      <c r="S47" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S47" s="5" t="inlineStr"/>
       <c r="T47" s="5" t="inlineStr"/>
-      <c r="U47" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U47" s="5" t="inlineStr"/>
       <c r="V47" s="5" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>COOPGWF1</t>
+          <t>CLRKCWF2</t>
         </is>
       </c>
       <c r="B48" s="8" t="inlineStr">
@@ -8312,62 +8381,36 @@
         </is>
       </c>
       <c r="C48" s="5" t="n">
-        <v>0.9691</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>0.9704</v>
-      </c>
-      <c r="E48" s="5" t="n">
-        <v>0.0306</v>
-      </c>
+        <v>0.9313</v>
+      </c>
+      <c r="E48" s="5" t="inlineStr"/>
       <c r="F48" s="5" t="n">
-        <v>0.0532</v>
+        <v>0.029</v>
       </c>
       <c r="G48" s="5" t="inlineStr"/>
       <c r="H48" s="5" t="inlineStr"/>
       <c r="I48" s="5" t="inlineStr"/>
-      <c r="J48" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J48" s="5" t="inlineStr"/>
       <c r="K48" s="5" t="inlineStr"/>
-      <c r="L48" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L48" s="5" t="inlineStr"/>
       <c r="M48" s="5" t="inlineStr"/>
-      <c r="N48" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N48" s="5" t="inlineStr"/>
       <c r="O48" s="5" t="inlineStr"/>
       <c r="P48" s="5" t="inlineStr"/>
-      <c r="Q48" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q48" s="5" t="inlineStr"/>
       <c r="R48" s="5" t="inlineStr"/>
-      <c r="S48" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S48" s="5" t="inlineStr"/>
       <c r="T48" s="5" t="inlineStr"/>
-      <c r="U48" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U48" s="5" t="inlineStr"/>
       <c r="V48" s="5" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>DULAWF1</t>
+          <t>COOPGWF1</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
@@ -8376,62 +8419,38 @@
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>0.9853</v>
+        <v>0.9691</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>0.987</v>
+        <v>0.9704</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.0306</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>0.0011</v>
+        <v>0.0532</v>
       </c>
       <c r="G49" s="5" t="inlineStr"/>
       <c r="H49" s="5" t="inlineStr"/>
       <c r="I49" s="5" t="inlineStr"/>
-      <c r="J49" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J49" s="5" t="inlineStr"/>
       <c r="K49" s="5" t="inlineStr"/>
-      <c r="L49" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L49" s="5" t="inlineStr"/>
       <c r="M49" s="5" t="inlineStr"/>
-      <c r="N49" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N49" s="5" t="inlineStr"/>
       <c r="O49" s="5" t="inlineStr"/>
       <c r="P49" s="5" t="inlineStr"/>
-      <c r="Q49" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q49" s="5" t="inlineStr"/>
       <c r="R49" s="5" t="inlineStr"/>
-      <c r="S49" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S49" s="5" t="inlineStr"/>
       <c r="T49" s="5" t="inlineStr"/>
-      <c r="U49" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U49" s="5" t="inlineStr"/>
       <c r="V49" s="5" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>KABANWF1</t>
+          <t>DULAWF1</t>
         </is>
       </c>
       <c r="B50" s="8" t="inlineStr">
@@ -8440,62 +8459,38 @@
         </is>
       </c>
       <c r="C50" s="5" t="n">
-        <v>0.9696</v>
+        <v>0.9853</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>0.9442</v>
+        <v>0.987</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>0.0141</v>
+        <v>0.0033</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>0.0766</v>
+        <v>0.0011</v>
       </c>
       <c r="G50" s="5" t="inlineStr"/>
       <c r="H50" s="5" t="inlineStr"/>
       <c r="I50" s="5" t="inlineStr"/>
-      <c r="J50" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J50" s="5" t="inlineStr"/>
       <c r="K50" s="5" t="inlineStr"/>
-      <c r="L50" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L50" s="5" t="inlineStr"/>
       <c r="M50" s="5" t="inlineStr"/>
-      <c r="N50" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N50" s="5" t="inlineStr"/>
       <c r="O50" s="5" t="inlineStr"/>
       <c r="P50" s="5" t="inlineStr"/>
-      <c r="Q50" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q50" s="5" t="inlineStr"/>
       <c r="R50" s="5" t="inlineStr"/>
-      <c r="S50" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S50" s="5" t="inlineStr"/>
       <c r="T50" s="5" t="inlineStr"/>
-      <c r="U50" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U50" s="5" t="inlineStr"/>
       <c r="V50" s="5" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>KEPWF1</t>
+          <t>KABANWF1</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
@@ -8504,62 +8499,38 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>0.9813</v>
+        <v>0.9696</v>
       </c>
       <c r="D51" s="5" t="n">
-        <v>0.9574</v>
+        <v>0.9442</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>0.024</v>
+        <v>0.0141</v>
       </c>
       <c r="F51" s="5" t="n">
-        <v>0.0136</v>
+        <v>0.0766</v>
       </c>
       <c r="G51" s="5" t="inlineStr"/>
       <c r="H51" s="5" t="inlineStr"/>
       <c r="I51" s="5" t="inlineStr"/>
-      <c r="J51" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J51" s="5" t="inlineStr"/>
       <c r="K51" s="5" t="inlineStr"/>
-      <c r="L51" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L51" s="5" t="inlineStr"/>
       <c r="M51" s="5" t="inlineStr"/>
-      <c r="N51" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N51" s="5" t="inlineStr"/>
       <c r="O51" s="5" t="inlineStr"/>
       <c r="P51" s="5" t="inlineStr"/>
-      <c r="Q51" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q51" s="5" t="inlineStr"/>
       <c r="R51" s="5" t="inlineStr"/>
-      <c r="S51" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S51" s="5" t="inlineStr"/>
       <c r="T51" s="5" t="inlineStr"/>
-      <c r="U51" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U51" s="5" t="inlineStr"/>
       <c r="V51" s="5" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
         <is>
-          <t>MCINTYR1</t>
+          <t>KEPWF1</t>
         </is>
       </c>
       <c r="B52" s="8" t="inlineStr">
@@ -8568,60 +8539,38 @@
         </is>
       </c>
       <c r="C52" s="5" t="n">
-        <v>0.9723000000000001</v>
+        <v>0.9813</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>0.9729</v>
-      </c>
-      <c r="E52" s="5" t="inlineStr"/>
+        <v>0.9574</v>
+      </c>
+      <c r="E52" s="5" t="n">
+        <v>0.024</v>
+      </c>
       <c r="F52" s="5" t="n">
-        <v>0.0035</v>
+        <v>0.0136</v>
       </c>
       <c r="G52" s="5" t="inlineStr"/>
       <c r="H52" s="5" t="inlineStr"/>
       <c r="I52" s="5" t="inlineStr"/>
-      <c r="J52" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J52" s="5" t="inlineStr"/>
       <c r="K52" s="5" t="inlineStr"/>
-      <c r="L52" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L52" s="5" t="inlineStr"/>
       <c r="M52" s="5" t="inlineStr"/>
-      <c r="N52" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N52" s="5" t="inlineStr"/>
       <c r="O52" s="5" t="inlineStr"/>
       <c r="P52" s="5" t="inlineStr"/>
-      <c r="Q52" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q52" s="5" t="inlineStr"/>
       <c r="R52" s="5" t="inlineStr"/>
-      <c r="S52" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S52" s="5" t="inlineStr"/>
       <c r="T52" s="5" t="inlineStr"/>
-      <c r="U52" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U52" s="5" t="inlineStr"/>
       <c r="V52" s="5" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>MEWF1</t>
+          <t>MCINTYR1</t>
         </is>
       </c>
       <c r="B53" s="8" t="inlineStr">
@@ -8630,62 +8579,36 @@
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>0.9649</v>
+        <v>0.9723000000000001</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>0.9396</v>
-      </c>
-      <c r="E53" s="5" t="n">
-        <v>0.0425</v>
-      </c>
+        <v>0.9729</v>
+      </c>
+      <c r="E53" s="5" t="inlineStr"/>
       <c r="F53" s="5" t="n">
-        <v>0.0189</v>
+        <v>0.0035</v>
       </c>
       <c r="G53" s="5" t="inlineStr"/>
       <c r="H53" s="5" t="inlineStr"/>
       <c r="I53" s="5" t="inlineStr"/>
-      <c r="J53" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J53" s="5" t="inlineStr"/>
       <c r="K53" s="5" t="inlineStr"/>
-      <c r="L53" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L53" s="5" t="inlineStr"/>
       <c r="M53" s="5" t="inlineStr"/>
-      <c r="N53" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N53" s="5" t="inlineStr"/>
       <c r="O53" s="5" t="inlineStr"/>
       <c r="P53" s="5" t="inlineStr"/>
-      <c r="Q53" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q53" s="5" t="inlineStr"/>
       <c r="R53" s="5" t="inlineStr"/>
-      <c r="S53" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S53" s="5" t="inlineStr"/>
       <c r="T53" s="5" t="inlineStr"/>
-      <c r="U53" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U53" s="5" t="inlineStr"/>
       <c r="V53" s="5" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
         <is>
-          <t>WAMBOWF1</t>
+          <t>MEWF1</t>
         </is>
       </c>
       <c r="B54" s="8" t="inlineStr">
@@ -8694,60 +8617,38 @@
         </is>
       </c>
       <c r="C54" s="5" t="n">
-        <v>0.967</v>
+        <v>0.9649</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>0.9701</v>
-      </c>
-      <c r="E54" s="5" t="inlineStr"/>
+        <v>0.9396</v>
+      </c>
+      <c r="E54" s="5" t="n">
+        <v>0.0425</v>
+      </c>
       <c r="F54" s="5" t="n">
-        <v>0.0039</v>
+        <v>0.0189</v>
       </c>
       <c r="G54" s="5" t="inlineStr"/>
       <c r="H54" s="5" t="inlineStr"/>
       <c r="I54" s="5" t="inlineStr"/>
-      <c r="J54" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J54" s="5" t="inlineStr"/>
       <c r="K54" s="5" t="inlineStr"/>
-      <c r="L54" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L54" s="5" t="inlineStr"/>
       <c r="M54" s="5" t="inlineStr"/>
-      <c r="N54" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N54" s="5" t="inlineStr"/>
       <c r="O54" s="5" t="inlineStr"/>
       <c r="P54" s="5" t="inlineStr"/>
-      <c r="Q54" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q54" s="5" t="inlineStr"/>
       <c r="R54" s="5" t="inlineStr"/>
-      <c r="S54" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S54" s="5" t="inlineStr"/>
       <c r="T54" s="5" t="inlineStr"/>
-      <c r="U54" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U54" s="5" t="inlineStr"/>
       <c r="V54" s="5" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>WAMBOWF2</t>
+          <t>WAMBOWF1</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
@@ -8755,55 +8656,37 @@
           <t>Wind</t>
         </is>
       </c>
-      <c r="C55" s="5" t="inlineStr"/>
-      <c r="D55" s="5" t="inlineStr"/>
+      <c r="C55" s="5" t="n">
+        <v>0.967</v>
+      </c>
+      <c r="D55" s="5" t="n">
+        <v>0.9701</v>
+      </c>
       <c r="E55" s="5" t="inlineStr"/>
-      <c r="F55" s="5" t="inlineStr"/>
+      <c r="F55" s="5" t="n">
+        <v>0.0039</v>
+      </c>
       <c r="G55" s="5" t="inlineStr"/>
       <c r="H55" s="5" t="inlineStr"/>
       <c r="I55" s="5" t="inlineStr"/>
-      <c r="J55" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J55" s="5" t="inlineStr"/>
       <c r="K55" s="5" t="inlineStr"/>
-      <c r="L55" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L55" s="5" t="inlineStr"/>
       <c r="M55" s="5" t="inlineStr"/>
-      <c r="N55" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N55" s="5" t="inlineStr"/>
       <c r="O55" s="5" t="inlineStr"/>
       <c r="P55" s="5" t="inlineStr"/>
-      <c r="Q55" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q55" s="5" t="inlineStr"/>
       <c r="R55" s="5" t="inlineStr"/>
-      <c r="S55" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S55" s="5" t="inlineStr"/>
       <c r="T55" s="5" t="inlineStr"/>
-      <c r="U55" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U55" s="5" t="inlineStr"/>
       <c r="V55" s="5" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
         <is>
-          <t>WHILL1</t>
+          <t>WAMBOWF2</t>
         </is>
       </c>
       <c r="B56" s="8" t="inlineStr">
@@ -8812,56 +8695,68 @@
         </is>
       </c>
       <c r="C56" s="5" t="n">
-        <v>1.0128</v>
+        <v>0.9671999999999999</v>
       </c>
       <c r="D56" s="5" t="n">
-        <v>1.013</v>
+        <v>0.9685</v>
       </c>
       <c r="E56" s="5" t="inlineStr"/>
       <c r="F56" s="5" t="inlineStr"/>
       <c r="G56" s="5" t="inlineStr"/>
       <c r="H56" s="5" t="inlineStr"/>
       <c r="I56" s="5" t="inlineStr"/>
-      <c r="J56" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J56" s="5" t="inlineStr"/>
       <c r="K56" s="5" t="inlineStr"/>
-      <c r="L56" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L56" s="5" t="inlineStr"/>
       <c r="M56" s="5" t="inlineStr"/>
-      <c r="N56" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N56" s="5" t="inlineStr"/>
       <c r="O56" s="5" t="inlineStr"/>
       <c r="P56" s="5" t="inlineStr"/>
-      <c r="Q56" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q56" s="5" t="inlineStr"/>
       <c r="R56" s="5" t="inlineStr"/>
-      <c r="S56" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S56" s="5" t="inlineStr"/>
       <c r="T56" s="5" t="inlineStr"/>
-      <c r="U56" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U56" s="5" t="inlineStr"/>
       <c r="V56" s="5" t="inlineStr"/>
     </row>
+    <row r="57">
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>WHILL1</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>Wind</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="n">
+        <v>1.0128</v>
+      </c>
+      <c r="D57" s="5" t="n">
+        <v>1.013</v>
+      </c>
+      <c r="E57" s="5" t="inlineStr"/>
+      <c r="F57" s="5" t="inlineStr"/>
+      <c r="G57" s="5" t="inlineStr"/>
+      <c r="H57" s="5" t="inlineStr"/>
+      <c r="I57" s="5" t="inlineStr"/>
+      <c r="J57" s="5" t="inlineStr"/>
+      <c r="K57" s="5" t="inlineStr"/>
+      <c r="L57" s="5" t="inlineStr"/>
+      <c r="M57" s="5" t="inlineStr"/>
+      <c r="N57" s="5" t="inlineStr"/>
+      <c r="O57" s="5" t="inlineStr"/>
+      <c r="P57" s="5" t="inlineStr"/>
+      <c r="Q57" s="5" t="inlineStr"/>
+      <c r="R57" s="5" t="inlineStr"/>
+      <c r="S57" s="5" t="inlineStr"/>
+      <c r="T57" s="5" t="inlineStr"/>
+      <c r="U57" s="5" t="inlineStr"/>
+      <c r="V57" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C56">
+  <conditionalFormatting sqref="C2:C57">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -8873,7 +8768,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D56">
+  <conditionalFormatting sqref="D2:D57">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -8885,7 +8780,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E56">
+  <conditionalFormatting sqref="E2:E57">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -8897,7 +8792,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F56">
+  <conditionalFormatting sqref="F2:F57">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -8909,7 +8804,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G56">
+  <conditionalFormatting sqref="G2:G57">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -8921,7 +8816,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H56">
+  <conditionalFormatting sqref="H2:H57">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -8933,7 +8828,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I56">
+  <conditionalFormatting sqref="I2:I57">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -8945,7 +8840,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J56">
+  <conditionalFormatting sqref="J2:J57">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -8957,7 +8852,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K56">
+  <conditionalFormatting sqref="K2:K57">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -8969,7 +8864,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L56">
+  <conditionalFormatting sqref="L2:L57">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
@@ -8981,7 +8876,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M56">
+  <conditionalFormatting sqref="M2:M57">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
@@ -8993,7 +8888,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N56">
+  <conditionalFormatting sqref="N2:N57">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
@@ -9005,7 +8900,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O56">
+  <conditionalFormatting sqref="O2:O57">
     <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
@@ -9017,7 +8912,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P56">
+  <conditionalFormatting sqref="P2:P57">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="min"/>
@@ -9029,7 +8924,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q56">
+  <conditionalFormatting sqref="Q2:Q57">
     <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="min"/>
@@ -9041,7 +8936,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R56">
+  <conditionalFormatting sqref="R2:R57">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="min"/>
@@ -9053,7 +8948,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S56">
+  <conditionalFormatting sqref="S2:S57">
     <cfRule type="colorScale" priority="17">
       <colorScale>
         <cfvo type="min"/>
@@ -9065,7 +8960,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T2:T56">
+  <conditionalFormatting sqref="T2:T57">
     <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="min"/>
@@ -9077,7 +8972,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U2:U56">
+  <conditionalFormatting sqref="U2:U57">
     <cfRule type="colorScale" priority="19">
       <colorScale>
         <cfvo type="min"/>
@@ -9089,7 +8984,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V2:V56">
+  <conditionalFormatting sqref="V2:V57">
     <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="min"/>

--- a/outputs/QLD_curtailment.xlsx
+++ b/outputs/QLD_curtailment.xlsx
@@ -549,12 +549,12 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>ELI Near Term</t>
+          <t>ELI Near Term (2026-28)</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>ELI Med Term</t>
+          <t>ELI Med Term (2030-35)</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
@@ -644,7 +644,7 @@
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="5" t="inlineStr"/>
       <c r="L2" s="5" t="n">
-        <v>0.1347</v>
+        <v>0.1335</v>
       </c>
       <c r="M2" s="5" t="inlineStr"/>
       <c r="N2" s="5" t="inlineStr"/>
@@ -821,7 +821,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>eli</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -836,7 +836,7 @@
         <v>132</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>0.0234</v>
+        <v>0.0232</v>
       </c>
       <c r="L5" s="5" t="n">
         <v>0.0128</v>
@@ -914,9 +914,17 @@
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="5" t="inlineStr"/>
       <c r="L6" s="5" t="inlineStr"/>
-      <c r="M6" s="5" t="inlineStr"/>
-      <c r="N6" s="5" t="inlineStr"/>
-      <c r="O6" s="2" t="inlineStr"/>
+      <c r="M6" s="5" t="n">
+        <v>0.225748318520862</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>0.054098481062334</v>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>location-name</t>
+        </is>
+      </c>
       <c r="P6" s="5" t="n">
         <v>0.929</v>
       </c>
@@ -963,9 +971,17 @@
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="5" t="inlineStr"/>
       <c r="L7" s="5" t="inlineStr"/>
-      <c r="M7" s="5" t="inlineStr"/>
-      <c r="N7" s="5" t="inlineStr"/>
-      <c r="O7" s="2" t="inlineStr"/>
+      <c r="M7" s="5" t="n">
+        <v>0.218738210926131</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>0.0522010106762296</v>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>location-name</t>
+        </is>
+      </c>
       <c r="P7" s="5" t="n">
         <v>0.9677</v>
       </c>
@@ -1014,7 +1030,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>eli</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1032,7 +1048,7 @@
         <v>0.1229</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>0.3065</v>
+        <v>0.3046</v>
       </c>
       <c r="M8" s="5" t="n">
         <v>0.218738210926131</v>
@@ -1109,7 +1125,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>eli</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1127,7 +1143,7 @@
         <v>0.1872</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>0.3124</v>
+        <v>0.31</v>
       </c>
       <c r="M9" s="5" t="n">
         <v>0.219557634008624</v>
@@ -1204,7 +1220,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>eli</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1219,10 +1235,10 @@
         <v>132</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>0.0209</v>
+        <v>0.0158</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>0.07829999999999999</v>
+        <v>0.0764</v>
       </c>
       <c r="M10" s="5" t="n">
         <v>0.22576156415161</v>
@@ -1299,7 +1315,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>eli</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1314,7 +1330,7 @@
         <v>33</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>0.0057</v>
+        <v>0.0018</v>
       </c>
       <c r="L11" s="5" t="n">
         <v>0.0354</v>
@@ -1394,7 +1410,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>eli</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1489,7 +1505,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>eli</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1584,7 +1600,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>eli</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1599,10 +1615,10 @@
         <v>33</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>0.0384</v>
+        <v>0.0376</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>0.2108</v>
+        <v>0.2096</v>
       </c>
       <c r="M14" s="5" t="n">
         <v>0.221997464026796</v>
@@ -1679,7 +1695,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>eli</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1694,10 +1710,10 @@
         <v>275</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>0.0583</v>
+        <v>0.0581</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>0.129</v>
+        <v>0.1269</v>
       </c>
       <c r="M15" s="5" t="n">
         <v>0.224633904533977</v>
@@ -1774,7 +1790,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>eli</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1789,10 +1805,10 @@
         <v>66</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>0.0116</v>
+        <v>0.0114</v>
       </c>
       <c r="M16" s="5" t="n">
         <v>0.22576156415161</v>
@@ -1853,7 +1869,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>eli</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1868,10 +1884,10 @@
         <v>132</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>0.1932</v>
+        <v>0.1929</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>0.35</v>
+        <v>0.3486</v>
       </c>
       <c r="M17" s="5" t="n">
         <v>0.224633904533977</v>
@@ -1997,7 +2013,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>eli</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2012,10 +2028,10 @@
         <v>33</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>0.074</v>
+        <v>0.07389999999999999</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>0.2538</v>
+        <v>0.2526</v>
       </c>
       <c r="M19" s="5" t="n">
         <v>0.221997464026796</v>
@@ -2092,7 +2108,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>eli</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2107,7 +2123,7 @@
         <v>275</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>0.0878</v>
+        <v>0.0871</v>
       </c>
       <c r="L20" s="5" t="n">
         <v>0.0367</v>
@@ -2187,7 +2203,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>eli</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2205,7 +2221,7 @@
         <v>0.2149</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>0.3371</v>
+        <v>0.3349</v>
       </c>
       <c r="M21" s="5" t="n">
         <v>0.221997464026796</v>
@@ -2357,7 +2373,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>eli</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2452,7 +2468,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>eli</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2470,7 +2486,7 @@
         <v>0.2351</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>0.3472</v>
+        <v>0.3459</v>
       </c>
       <c r="M24" s="5" t="n">
         <v>0.219557634008624</v>
@@ -2547,7 +2563,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>eli</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2563,7 +2579,7 @@
       </c>
       <c r="K25" s="5" t="inlineStr"/>
       <c r="L25" s="5" t="n">
-        <v>0.274</v>
+        <v>0.2694</v>
       </c>
       <c r="M25" s="5" t="n">
         <v>0.233985863287972</v>
@@ -2624,7 +2640,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>eli</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2794,7 +2810,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>eli</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2809,10 +2825,10 @@
         <v>110</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>0.1165</v>
+        <v>0.1155</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>0.3673</v>
+        <v>0.3663</v>
       </c>
       <c r="M28" s="5" t="n">
         <v>0.23150076097273</v>
@@ -2873,9 +2889,21 @@
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr"/>
-      <c r="E29" s="2" t="inlineStr"/>
-      <c r="F29" s="3" t="inlineStr"/>
-      <c r="G29" s="2" t="inlineStr"/>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Isaac</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
           <t>QLD</t>
@@ -2886,10 +2914,10 @@
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="5" t="n">
-        <v>0.0531</v>
+        <v>0.02</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>0.2608</v>
+        <v>0.259</v>
       </c>
       <c r="M29" s="5" t="inlineStr"/>
       <c r="N29" s="5" t="inlineStr"/>
@@ -2900,14 +2928,30 @@
       <c r="Q29" s="5" t="n">
         <v>0.8854</v>
       </c>
-      <c r="R29" s="6" t="inlineStr"/>
-      <c r="S29" s="6" t="inlineStr"/>
-      <c r="T29" s="6" t="inlineStr"/>
-      <c r="U29" s="6" t="inlineStr"/>
-      <c r="V29" s="6" t="inlineStr"/>
-      <c r="W29" s="6" t="inlineStr"/>
-      <c r="X29" s="6" t="inlineStr"/>
-      <c r="Y29" s="6" t="inlineStr"/>
+      <c r="R29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="W29" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="X29" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Y29" s="6" t="n">
+        <v>0.02333333333333333</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2942,7 +2986,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>eli</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2957,7 +3001,7 @@
         <v>132</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.0042</v>
       </c>
       <c r="L30" s="5" t="n">
         <v>0.0238</v>
@@ -3086,7 +3130,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>eli</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -3104,7 +3148,7 @@
         <v>0.3341</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>0.362</v>
+        <v>0.3606</v>
       </c>
       <c r="M32" s="5" t="n">
         <v>0.23150076097273</v>
@@ -3181,7 +3225,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>eli</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -3196,10 +3240,10 @@
         <v>110</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>0.096</v>
+        <v>0.0953</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>0.2724</v>
+        <v>0.2702</v>
       </c>
       <c r="M33" s="5" t="n">
         <v>0.23150076097273</v>
@@ -3276,7 +3320,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>eli</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -3291,7 +3335,7 @@
         <v>132</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>0.0115</v>
+        <v>0.0109</v>
       </c>
       <c r="L34" s="5" t="n">
         <v>0.0282</v>
@@ -3371,7 +3415,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>eli</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -3389,7 +3433,7 @@
         <v>0.0786</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>0.229</v>
+        <v>0.2287</v>
       </c>
       <c r="M35" s="5" t="n">
         <v>0.22576156415161</v>
@@ -3466,7 +3510,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>eli</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3484,7 +3528,7 @@
         <v>0.1003</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>0.2386</v>
+        <v>0.2371</v>
       </c>
       <c r="M36" s="5" t="n">
         <v>0.219325121104852</v>
@@ -3561,7 +3605,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>eli</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3579,7 +3623,7 @@
         <v>0.1189</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>0.2939</v>
+        <v>0.2924</v>
       </c>
       <c r="M37" s="5" t="n">
         <v>0.218738210926131</v>
@@ -3731,7 +3775,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>eli</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3746,10 +3790,10 @@
         <v>275</v>
       </c>
       <c r="K39" s="5" t="n">
-        <v>0.1975</v>
+        <v>0.1974</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>0.3758</v>
+        <v>0.3746</v>
       </c>
       <c r="M39" s="5" t="n">
         <v>0.223370431255546</v>
@@ -3810,9 +3854,21 @@
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr"/>
-      <c r="E40" s="2" t="inlineStr"/>
-      <c r="F40" s="3" t="inlineStr"/>
-      <c r="G40" s="2" t="inlineStr"/>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Darling Downs</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>eli-station</t>
+        </is>
+      </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
           <t>QLD</t>
@@ -3833,14 +3889,30 @@
       <c r="Q40" s="5" t="n">
         <v>0.985</v>
       </c>
-      <c r="R40" s="6" t="inlineStr"/>
-      <c r="S40" s="6" t="inlineStr"/>
-      <c r="T40" s="6" t="inlineStr"/>
-      <c r="U40" s="6" t="inlineStr"/>
-      <c r="V40" s="6" t="inlineStr"/>
-      <c r="W40" s="6" t="inlineStr"/>
-      <c r="X40" s="6" t="inlineStr"/>
-      <c r="Y40" s="6" t="inlineStr"/>
+      <c r="R40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="W40" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="X40" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Y40" s="6" t="n">
+        <v>0.01666666666666667</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -3875,7 +3947,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>eli</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3893,7 +3965,7 @@
         <v>0.39</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>0.5046</v>
+        <v>0.5008</v>
       </c>
       <c r="M41" s="5" t="n">
         <v>0.23150076097273</v>
@@ -3970,7 +4042,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>eli</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3988,7 +4060,7 @@
         <v>0.394</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>0.5084</v>
+        <v>0.5044</v>
       </c>
       <c r="M42" s="5" t="n">
         <v>0.23150076097273</v>
@@ -4049,9 +4121,21 @@
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr"/>
-      <c r="E43" s="2" t="inlineStr"/>
-      <c r="F43" s="3" t="inlineStr"/>
-      <c r="G43" s="2" t="inlineStr"/>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>Darling Downs</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
           <t>QLD</t>
@@ -4065,25 +4149,49 @@
         <v>0.1745</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>0.0315</v>
-      </c>
-      <c r="M43" s="5" t="inlineStr"/>
-      <c r="N43" s="5" t="inlineStr"/>
-      <c r="O43" s="2" t="inlineStr"/>
+        <v>0.0309</v>
+      </c>
+      <c r="M43" s="5" t="n">
+        <v>0.224633904533977</v>
+      </c>
+      <c r="N43" s="5" t="n">
+        <v>0.0520360014057779</v>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>location-name</t>
+        </is>
+      </c>
       <c r="P43" s="5" t="n">
         <v>0.9767</v>
       </c>
       <c r="Q43" s="5" t="n">
         <v>0.9761</v>
       </c>
-      <c r="R43" s="6" t="inlineStr"/>
-      <c r="S43" s="6" t="inlineStr"/>
-      <c r="T43" s="6" t="inlineStr"/>
-      <c r="U43" s="6" t="inlineStr"/>
-      <c r="V43" s="6" t="inlineStr"/>
-      <c r="W43" s="6" t="inlineStr"/>
-      <c r="X43" s="6" t="inlineStr"/>
-      <c r="Y43" s="6" t="inlineStr"/>
+      <c r="R43" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="W43" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="X43" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Y43" s="6" t="n">
+        <v>0.01666666666666667</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -4118,7 +4226,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>eli</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -4136,7 +4244,7 @@
         <v>0.3037</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>0.3572</v>
+        <v>0.3556</v>
       </c>
       <c r="M44" s="5" t="n">
         <v>0.221997464026796</v>
@@ -4213,7 +4321,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>eli</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -4231,7 +4339,7 @@
         <v>0.2353</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>0.0665</v>
+        <v>0.0663</v>
       </c>
       <c r="M45" s="5" t="n">
         <v>0.23173278497921</v>
@@ -4308,7 +4416,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>eli</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -4326,7 +4434,7 @@
         <v>0.1371</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>0.2328</v>
+        <v>0.2322</v>
       </c>
       <c r="M46" s="5" t="n">
         <v>0.23150076097273</v>
@@ -4387,9 +4495,21 @@
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr"/>
-      <c r="E47" s="2" t="inlineStr"/>
-      <c r="F47" s="3" t="inlineStr"/>
-      <c r="G47" s="2" t="inlineStr"/>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>Isaac</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
           <t>QLD</t>
@@ -4401,7 +4521,7 @@
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="5" t="inlineStr"/>
       <c r="L47" s="5" t="n">
-        <v>0.0425</v>
+        <v>0.0423</v>
       </c>
       <c r="M47" s="5" t="inlineStr"/>
       <c r="N47" s="5" t="inlineStr"/>
@@ -4412,14 +4532,30 @@
       <c r="Q47" s="5" t="n">
         <v>0.9313</v>
       </c>
-      <c r="R47" s="6" t="inlineStr"/>
-      <c r="S47" s="6" t="inlineStr"/>
-      <c r="T47" s="6" t="inlineStr"/>
-      <c r="U47" s="6" t="inlineStr"/>
-      <c r="V47" s="6" t="inlineStr"/>
-      <c r="W47" s="6" t="inlineStr"/>
-      <c r="X47" s="6" t="inlineStr"/>
-      <c r="Y47" s="6" t="inlineStr"/>
+      <c r="R47" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="W47" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="X47" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Y47" s="6" t="n">
+        <v>0.02333333333333333</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -4438,9 +4574,21 @@
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr"/>
-      <c r="E48" s="2" t="inlineStr"/>
-      <c r="F48" s="3" t="inlineStr"/>
-      <c r="G48" s="2" t="inlineStr"/>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Isaac</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>eli-station</t>
+        </is>
+      </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
           <t>QLD</t>
@@ -4452,7 +4600,7 @@
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="5" t="inlineStr"/>
       <c r="L48" s="5" t="n">
-        <v>0.029</v>
+        <v>0.0289</v>
       </c>
       <c r="M48" s="5" t="inlineStr"/>
       <c r="N48" s="5" t="inlineStr"/>
@@ -4463,14 +4611,30 @@
       <c r="Q48" s="5" t="n">
         <v>0.9313</v>
       </c>
-      <c r="R48" s="6" t="inlineStr"/>
-      <c r="S48" s="6" t="inlineStr"/>
-      <c r="T48" s="6" t="inlineStr"/>
-      <c r="U48" s="6" t="inlineStr"/>
-      <c r="V48" s="6" t="inlineStr"/>
-      <c r="W48" s="6" t="inlineStr"/>
-      <c r="X48" s="6" t="inlineStr"/>
-      <c r="Y48" s="6" t="inlineStr"/>
+      <c r="R48" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="W48" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="X48" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Y48" s="6" t="n">
+        <v>0.02333333333333333</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -4489,9 +4653,21 @@
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr"/>
-      <c r="E49" s="2" t="inlineStr"/>
-      <c r="F49" s="3" t="inlineStr"/>
-      <c r="G49" s="2" t="inlineStr"/>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>Darling Downs</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
           <t>QLD</t>
@@ -4502,10 +4678,10 @@
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="5" t="n">
-        <v>0.0306</v>
+        <v>0.0298</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>0.0532</v>
+        <v>0.0529</v>
       </c>
       <c r="M49" s="5" t="inlineStr"/>
       <c r="N49" s="5" t="inlineStr"/>
@@ -4516,14 +4692,30 @@
       <c r="Q49" s="5" t="n">
         <v>0.9704</v>
       </c>
-      <c r="R49" s="6" t="inlineStr"/>
-      <c r="S49" s="6" t="inlineStr"/>
-      <c r="T49" s="6" t="inlineStr"/>
-      <c r="U49" s="6" t="inlineStr"/>
-      <c r="V49" s="6" t="inlineStr"/>
-      <c r="W49" s="6" t="inlineStr"/>
-      <c r="X49" s="6" t="inlineStr"/>
-      <c r="Y49" s="6" t="inlineStr"/>
+      <c r="R49" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="W49" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="X49" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Y49" s="6" t="n">
+        <v>0.01666666666666667</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -4542,9 +4734,21 @@
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr"/>
-      <c r="E50" s="2" t="inlineStr"/>
-      <c r="F50" s="3" t="inlineStr"/>
-      <c r="G50" s="2" t="inlineStr"/>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Darling Downs</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
           <t>QLD</t>
@@ -4555,10 +4759,10 @@
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.0024</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>0.0011</v>
+        <v>0</v>
       </c>
       <c r="M50" s="5" t="inlineStr"/>
       <c r="N50" s="5" t="inlineStr"/>
@@ -4569,14 +4773,30 @@
       <c r="Q50" s="5" t="n">
         <v>0.987</v>
       </c>
-      <c r="R50" s="6" t="inlineStr"/>
-      <c r="S50" s="6" t="inlineStr"/>
-      <c r="T50" s="6" t="inlineStr"/>
-      <c r="U50" s="6" t="inlineStr"/>
-      <c r="V50" s="6" t="inlineStr"/>
-      <c r="W50" s="6" t="inlineStr"/>
-      <c r="X50" s="6" t="inlineStr"/>
-      <c r="Y50" s="6" t="inlineStr"/>
+      <c r="R50" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="W50" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="X50" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Y50" s="6" t="n">
+        <v>0.01666666666666667</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -4595,9 +4815,21 @@
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr"/>
-      <c r="E51" s="2" t="inlineStr"/>
-      <c r="F51" s="3" t="inlineStr"/>
-      <c r="G51" s="2" t="inlineStr"/>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>Far North Queensland</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
           <t>QLD</t>
@@ -4608,10 +4840,10 @@
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="5" t="n">
-        <v>0.0141</v>
+        <v>0.0114</v>
       </c>
       <c r="L51" s="5" t="n">
-        <v>0.0766</v>
+        <v>0.07630000000000001</v>
       </c>
       <c r="M51" s="5" t="inlineStr"/>
       <c r="N51" s="5" t="inlineStr"/>
@@ -4622,14 +4854,30 @@
       <c r="Q51" s="5" t="n">
         <v>0.9442</v>
       </c>
-      <c r="R51" s="6" t="inlineStr"/>
-      <c r="S51" s="6" t="inlineStr"/>
-      <c r="T51" s="6" t="inlineStr"/>
-      <c r="U51" s="6" t="inlineStr"/>
-      <c r="V51" s="6" t="inlineStr"/>
-      <c r="W51" s="6" t="inlineStr"/>
-      <c r="X51" s="6" t="inlineStr"/>
-      <c r="Y51" s="6" t="inlineStr"/>
+      <c r="R51" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="W51" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="X51" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Y51" s="6" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -4648,9 +4896,21 @@
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr"/>
-      <c r="E52" s="2" t="inlineStr"/>
-      <c r="F52" s="3" t="inlineStr"/>
-      <c r="G52" s="2" t="inlineStr"/>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>North Queensland Clean Energy Hub</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
           <t>QLD</t>
@@ -4675,14 +4935,30 @@
       <c r="Q52" s="5" t="n">
         <v>0.9574</v>
       </c>
-      <c r="R52" s="6" t="inlineStr"/>
-      <c r="S52" s="6" t="inlineStr"/>
-      <c r="T52" s="6" t="inlineStr"/>
-      <c r="U52" s="6" t="inlineStr"/>
-      <c r="V52" s="6" t="inlineStr"/>
-      <c r="W52" s="6" t="inlineStr"/>
-      <c r="X52" s="6" t="inlineStr"/>
-      <c r="Y52" s="6" t="inlineStr"/>
+      <c r="R52" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="W52" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="X52" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Y52" s="6" t="n">
+        <v>0.02666666666666667</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -4701,9 +4977,21 @@
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr"/>
-      <c r="E53" s="2" t="inlineStr"/>
-      <c r="F53" s="3" t="inlineStr"/>
-      <c r="G53" s="2" t="inlineStr"/>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>Non-REZ</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
           <t>QLD</t>
@@ -4752,9 +5040,21 @@
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr"/>
-      <c r="E54" s="2" t="inlineStr"/>
-      <c r="F54" s="3" t="inlineStr"/>
-      <c r="G54" s="2" t="inlineStr"/>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>Far North Queensland</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>eli</t>
+        </is>
+      </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
           <t>QLD</t>
@@ -4765,7 +5065,7 @@
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="5" t="n">
-        <v>0.0425</v>
+        <v>0.0395</v>
       </c>
       <c r="L54" s="5" t="n">
         <v>0.0189</v>
@@ -4779,14 +5079,30 @@
       <c r="Q54" s="5" t="n">
         <v>0.9396</v>
       </c>
-      <c r="R54" s="6" t="inlineStr"/>
-      <c r="S54" s="6" t="inlineStr"/>
-      <c r="T54" s="6" t="inlineStr"/>
-      <c r="U54" s="6" t="inlineStr"/>
-      <c r="V54" s="6" t="inlineStr"/>
-      <c r="W54" s="6" t="inlineStr"/>
-      <c r="X54" s="6" t="inlineStr"/>
-      <c r="Y54" s="6" t="inlineStr"/>
+      <c r="R54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="W54" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="X54" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Y54" s="6" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -4819,7 +5135,7 @@
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="5" t="inlineStr"/>
       <c r="L55" s="5" t="n">
-        <v>0.0039</v>
+        <v>0.0038</v>
       </c>
       <c r="M55" s="5" t="inlineStr"/>
       <c r="N55" s="5" t="inlineStr"/>
@@ -5106,7 +5422,7 @@
       </c>
       <c r="E2" s="5" t="inlineStr"/>
       <c r="F2" s="5" t="n">
-        <v>0.1347</v>
+        <v>0.1335</v>
       </c>
       <c r="G2" s="5" t="inlineStr"/>
       <c r="H2" s="5" t="inlineStr"/>
@@ -5151,42 +5467,18 @@
         <v>0.0559828223482727</v>
       </c>
       <c r="I3" s="5" t="inlineStr"/>
-      <c r="J3" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J3" s="5" t="inlineStr"/>
       <c r="K3" s="5" t="inlineStr"/>
-      <c r="L3" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L3" s="5" t="inlineStr"/>
       <c r="M3" s="5" t="inlineStr"/>
-      <c r="N3" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N3" s="5" t="inlineStr"/>
       <c r="O3" s="5" t="inlineStr"/>
       <c r="P3" s="5" t="inlineStr"/>
-      <c r="Q3" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q3" s="5" t="inlineStr"/>
       <c r="R3" s="5" t="inlineStr"/>
-      <c r="S3" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S3" s="5" t="inlineStr"/>
       <c r="T3" s="5" t="inlineStr"/>
-      <c r="U3" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U3" s="5" t="inlineStr"/>
       <c r="V3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
@@ -5243,7 +5535,7 @@
         <v>0.9459</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.0234</v>
+        <v>0.0232</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0.0128</v>
@@ -5328,8 +5620,12 @@
       </c>
       <c r="E6" s="5" t="inlineStr"/>
       <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="n">
+        <v>0.225748318520862</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>0.054098481062334</v>
+      </c>
       <c r="I6" s="5" t="inlineStr"/>
       <c r="J6" s="5" t="inlineStr"/>
       <c r="K6" s="5" t="inlineStr"/>
@@ -5364,8 +5660,12 @@
       </c>
       <c r="E7" s="5" t="inlineStr"/>
       <c r="F7" s="5" t="inlineStr"/>
-      <c r="G7" s="5" t="inlineStr"/>
-      <c r="H7" s="5" t="inlineStr"/>
+      <c r="G7" s="5" t="n">
+        <v>0.218738210926131</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>0.0522010106762296</v>
+      </c>
       <c r="I7" s="5" t="inlineStr"/>
       <c r="J7" s="5" t="inlineStr"/>
       <c r="K7" s="5" t="inlineStr"/>
@@ -5402,7 +5702,7 @@
         <v>0.1229</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0.3065</v>
+        <v>0.3046</v>
       </c>
       <c r="G8" s="5" t="n">
         <v>0.218738210926131</v>
@@ -5486,7 +5786,7 @@
         <v>0.1872</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.3124</v>
+        <v>0.31</v>
       </c>
       <c r="G9" s="5" t="n">
         <v>0.219557634008624</v>
@@ -5567,10 +5867,10 @@
         <v>0.8878</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0.0209</v>
+        <v>0.0158</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.07829999999999999</v>
+        <v>0.0764</v>
       </c>
       <c r="G10" s="5" t="n">
         <v>0.22576156415161</v>
@@ -5651,7 +5951,7 @@
         <v>0.8731</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0.0057</v>
+        <v>0.0018</v>
       </c>
       <c r="F11" s="5" t="n">
         <v>0.0354</v>
@@ -5903,10 +6203,10 @@
         <v>0.8758</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0.0384</v>
+        <v>0.0376</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0.2108</v>
+        <v>0.2096</v>
       </c>
       <c r="G14" s="5" t="n">
         <v>0.221997464026796</v>
@@ -5987,10 +6287,10 @@
         <v>0.9797</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0.0583</v>
+        <v>0.0581</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.129</v>
+        <v>0.1269</v>
       </c>
       <c r="G15" s="5" t="n">
         <v>0.224633904533977</v>
@@ -6071,10 +6371,10 @@
         <v>0.8854</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0.0116</v>
+        <v>0.0114</v>
       </c>
       <c r="G16" s="5" t="n">
         <v>0.22576156415161</v>
@@ -6083,42 +6383,18 @@
         <v>0.0531062553506225</v>
       </c>
       <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J16" s="5" t="inlineStr"/>
       <c r="K16" s="5" t="inlineStr"/>
-      <c r="L16" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L16" s="5" t="inlineStr"/>
       <c r="M16" s="5" t="inlineStr"/>
-      <c r="N16" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N16" s="5" t="inlineStr"/>
       <c r="O16" s="5" t="inlineStr"/>
       <c r="P16" s="5" t="inlineStr"/>
-      <c r="Q16" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q16" s="5" t="inlineStr"/>
       <c r="R16" s="5" t="inlineStr"/>
-      <c r="S16" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S16" s="5" t="inlineStr"/>
       <c r="T16" s="5" t="inlineStr"/>
-      <c r="U16" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U16" s="5" t="inlineStr"/>
       <c r="V16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
@@ -6139,10 +6415,10 @@
         <v>0.9918</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0.1932</v>
+        <v>0.1929</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0.35</v>
+        <v>0.3486</v>
       </c>
       <c r="G17" s="5" t="n">
         <v>0.224633904533977</v>
@@ -6259,10 +6535,10 @@
         <v>0.872</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0.074</v>
+        <v>0.07389999999999999</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>0.2538</v>
+        <v>0.2526</v>
       </c>
       <c r="G19" s="5" t="n">
         <v>0.221997464026796</v>
@@ -6343,7 +6619,7 @@
         <v>0.8766</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0.0878</v>
+        <v>0.0871</v>
       </c>
       <c r="F20" s="5" t="n">
         <v>0.0367</v>
@@ -6430,7 +6706,7 @@
         <v>0.2149</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0.3371</v>
+        <v>0.3349</v>
       </c>
       <c r="G21" s="5" t="n">
         <v>0.221997464026796</v>
@@ -6519,42 +6795,18 @@
         <v>0.0510095644706063</v>
       </c>
       <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J22" s="5" t="inlineStr"/>
       <c r="K22" s="5" t="inlineStr"/>
-      <c r="L22" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L22" s="5" t="inlineStr"/>
       <c r="M22" s="5" t="inlineStr"/>
-      <c r="N22" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N22" s="5" t="inlineStr"/>
       <c r="O22" s="5" t="inlineStr"/>
       <c r="P22" s="5" t="inlineStr"/>
-      <c r="Q22" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q22" s="5" t="inlineStr"/>
       <c r="R22" s="5" t="inlineStr"/>
-      <c r="S22" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S22" s="5" t="inlineStr"/>
       <c r="T22" s="5" t="inlineStr"/>
-      <c r="U22" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U22" s="5" t="inlineStr"/>
       <c r="V22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
@@ -6662,7 +6914,7 @@
         <v>0.2351</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>0.3472</v>
+        <v>0.3459</v>
       </c>
       <c r="G24" s="5" t="n">
         <v>0.219557634008624</v>
@@ -6744,7 +6996,7 @@
       </c>
       <c r="E25" s="5" t="inlineStr"/>
       <c r="F25" s="5" t="n">
-        <v>0.274</v>
+        <v>0.2694</v>
       </c>
       <c r="G25" s="5" t="n">
         <v>0.233985863287972</v>
@@ -6753,42 +7005,18 @@
         <v>0.0559828223482727</v>
       </c>
       <c r="I25" s="5" t="inlineStr"/>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J25" s="5" t="inlineStr"/>
       <c r="K25" s="5" t="inlineStr"/>
-      <c r="L25" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L25" s="5" t="inlineStr"/>
       <c r="M25" s="5" t="inlineStr"/>
-      <c r="N25" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N25" s="5" t="inlineStr"/>
       <c r="O25" s="5" t="inlineStr"/>
       <c r="P25" s="5" t="inlineStr"/>
-      <c r="Q25" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q25" s="5" t="inlineStr"/>
       <c r="R25" s="5" t="inlineStr"/>
-      <c r="S25" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S25" s="5" t="inlineStr"/>
       <c r="T25" s="5" t="inlineStr"/>
-      <c r="U25" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U25" s="5" t="inlineStr"/>
       <c r="V25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
@@ -6901,42 +7129,18 @@
         <v>0.0531062553506225</v>
       </c>
       <c r="I27" s="5" t="inlineStr"/>
-      <c r="J27" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J27" s="5" t="inlineStr"/>
       <c r="K27" s="5" t="inlineStr"/>
-      <c r="L27" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L27" s="5" t="inlineStr"/>
       <c r="M27" s="5" t="inlineStr"/>
-      <c r="N27" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N27" s="5" t="inlineStr"/>
       <c r="O27" s="5" t="inlineStr"/>
       <c r="P27" s="5" t="inlineStr"/>
-      <c r="Q27" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q27" s="5" t="inlineStr"/>
       <c r="R27" s="5" t="inlineStr"/>
-      <c r="S27" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S27" s="5" t="inlineStr"/>
       <c r="T27" s="5" t="inlineStr"/>
-      <c r="U27" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U27" s="5" t="inlineStr"/>
       <c r="V27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
@@ -6957,10 +7161,10 @@
         <v>0.987</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>0.1165</v>
+        <v>0.1155</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>0.3673</v>
+        <v>0.3663</v>
       </c>
       <c r="G28" s="5" t="n">
         <v>0.23150076097273</v>
@@ -7041,27 +7245,67 @@
         <v>0.8854</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>0.0531</v>
+        <v>0.02</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>0.2608</v>
+        <v>0.259</v>
       </c>
       <c r="G29" s="5" t="inlineStr"/>
       <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr"/>
-      <c r="L29" s="5" t="inlineStr"/>
-      <c r="M29" s="5" t="inlineStr"/>
-      <c r="N29" s="5" t="inlineStr"/>
-      <c r="O29" s="5" t="inlineStr"/>
-      <c r="P29" s="5" t="inlineStr"/>
-      <c r="Q29" s="5" t="inlineStr"/>
-      <c r="R29" s="5" t="inlineStr"/>
-      <c r="S29" s="5" t="inlineStr"/>
-      <c r="T29" s="5" t="inlineStr"/>
-      <c r="U29" s="5" t="inlineStr"/>
-      <c r="V29" s="5" t="inlineStr"/>
+      <c r="I29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q29" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R29" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="S29" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T29" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="U29" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V29" s="5" t="n">
+        <v>0.02333333333333333</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
@@ -7081,7 +7325,7 @@
         <v>0.885</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.0042</v>
       </c>
       <c r="F30" s="5" t="n">
         <v>0.0238</v>
@@ -7204,7 +7448,7 @@
         <v>0.3341</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>0.362</v>
+        <v>0.3606</v>
       </c>
       <c r="G32" s="5" t="n">
         <v>0.23150076097273</v>
@@ -7285,10 +7529,10 @@
         <v>0.9856</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>0.096</v>
+        <v>0.0953</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>0.2724</v>
+        <v>0.2702</v>
       </c>
       <c r="G33" s="5" t="n">
         <v>0.23150076097273</v>
@@ -7369,7 +7613,7 @@
         <v>0.8832</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>0.0115</v>
+        <v>0.0109</v>
       </c>
       <c r="F34" s="5" t="n">
         <v>0.0282</v>
@@ -7456,7 +7700,7 @@
         <v>0.0786</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>0.229</v>
+        <v>0.2287</v>
       </c>
       <c r="G35" s="5" t="n">
         <v>0.22576156415161</v>
@@ -7540,7 +7784,7 @@
         <v>0.1003</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>0.2386</v>
+        <v>0.2371</v>
       </c>
       <c r="G36" s="5" t="n">
         <v>0.219325121104852</v>
@@ -7624,7 +7868,7 @@
         <v>0.1189</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>0.2939</v>
+        <v>0.2924</v>
       </c>
       <c r="G37" s="5" t="n">
         <v>0.218738210926131</v>
@@ -7713,42 +7957,18 @@
         <v>0.0593284659737539</v>
       </c>
       <c r="I38" s="5" t="inlineStr"/>
-      <c r="J38" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="J38" s="5" t="inlineStr"/>
       <c r="K38" s="5" t="inlineStr"/>
-      <c r="L38" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="L38" s="5" t="inlineStr"/>
       <c r="M38" s="5" t="inlineStr"/>
-      <c r="N38" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="N38" s="5" t="inlineStr"/>
       <c r="O38" s="5" t="inlineStr"/>
       <c r="P38" s="5" t="inlineStr"/>
-      <c r="Q38" s="5" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
+      <c r="Q38" s="5" t="inlineStr"/>
       <c r="R38" s="5" t="inlineStr"/>
-      <c r="S38" s="5" t="inlineStr">
-        <is>
-          <t>26-27</t>
-        </is>
-      </c>
+      <c r="S38" s="5" t="inlineStr"/>
       <c r="T38" s="5" t="inlineStr"/>
-      <c r="U38" s="5" t="inlineStr">
-        <is>
-          <t>27-28</t>
-        </is>
-      </c>
+      <c r="U38" s="5" t="inlineStr"/>
       <c r="V38" s="5" t="inlineStr"/>
     </row>
     <row r="39">
@@ -7769,10 +7989,10 @@
         <v>0.985</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>0.1975</v>
+        <v>0.1974</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>0.3758</v>
+        <v>0.3746</v>
       </c>
       <c r="G39" s="5" t="n">
         <v>0.223370431255546</v>
@@ -7856,20 +8076,60 @@
       <c r="F40" s="5" t="inlineStr"/>
       <c r="G40" s="5" t="inlineStr"/>
       <c r="H40" s="5" t="inlineStr"/>
-      <c r="I40" s="5" t="inlineStr"/>
-      <c r="J40" s="5" t="inlineStr"/>
-      <c r="K40" s="5" t="inlineStr"/>
-      <c r="L40" s="5" t="inlineStr"/>
-      <c r="M40" s="5" t="inlineStr"/>
-      <c r="N40" s="5" t="inlineStr"/>
-      <c r="O40" s="5" t="inlineStr"/>
-      <c r="P40" s="5" t="inlineStr"/>
-      <c r="Q40" s="5" t="inlineStr"/>
-      <c r="R40" s="5" t="inlineStr"/>
-      <c r="S40" s="5" t="inlineStr"/>
-      <c r="T40" s="5" t="inlineStr"/>
-      <c r="U40" s="5" t="inlineStr"/>
-      <c r="V40" s="5" t="inlineStr"/>
+      <c r="I40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q40" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R40" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="S40" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T40" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="U40" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V40" s="5" t="n">
+        <v>0.01666666666666667</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
@@ -7892,7 +8152,7 @@
         <v>0.39</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>0.5046</v>
+        <v>0.5008</v>
       </c>
       <c r="G41" s="5" t="n">
         <v>0.23150076097273</v>
@@ -7976,7 +8236,7 @@
         <v>0.394</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>0.5084</v>
+        <v>0.5044</v>
       </c>
       <c r="G42" s="5" t="n">
         <v>0.23150076097273</v>
@@ -8060,24 +8320,68 @@
         <v>0.1745</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>0.0315</v>
-      </c>
-      <c r="G43" s="5" t="inlineStr"/>
-      <c r="H43" s="5" t="inlineStr"/>
-      <c r="I43" s="5" t="inlineStr"/>
-      <c r="J43" s="5" t="inlineStr"/>
-      <c r="K43" s="5" t="inlineStr"/>
-      <c r="L43" s="5" t="inlineStr"/>
-      <c r="M43" s="5" t="inlineStr"/>
-      <c r="N43" s="5" t="inlineStr"/>
-      <c r="O43" s="5" t="inlineStr"/>
-      <c r="P43" s="5" t="inlineStr"/>
-      <c r="Q43" s="5" t="inlineStr"/>
-      <c r="R43" s="5" t="inlineStr"/>
-      <c r="S43" s="5" t="inlineStr"/>
-      <c r="T43" s="5" t="inlineStr"/>
-      <c r="U43" s="5" t="inlineStr"/>
-      <c r="V43" s="5" t="inlineStr"/>
+        <v>0.0309</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>0.224633904533977</v>
+      </c>
+      <c r="H43" s="5" t="n">
+        <v>0.0520360014057779</v>
+      </c>
+      <c r="I43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q43" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R43" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="S43" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T43" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="U43" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V43" s="5" t="n">
+        <v>0.01666666666666667</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
@@ -8100,7 +8404,7 @@
         <v>0.3037</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>0.3572</v>
+        <v>0.3556</v>
       </c>
       <c r="G44" s="5" t="n">
         <v>0.221997464026796</v>
@@ -8184,7 +8488,7 @@
         <v>0.2353</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>0.0665</v>
+        <v>0.0663</v>
       </c>
       <c r="G45" s="5" t="n">
         <v>0.23173278497921</v>
@@ -8268,7 +8572,7 @@
         <v>0.1371</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>0.2328</v>
+        <v>0.2322</v>
       </c>
       <c r="G46" s="5" t="n">
         <v>0.23150076097273</v>
@@ -8350,24 +8654,64 @@
       </c>
       <c r="E47" s="5" t="inlineStr"/>
       <c r="F47" s="5" t="n">
-        <v>0.0425</v>
+        <v>0.0423</v>
       </c>
       <c r="G47" s="5" t="inlineStr"/>
       <c r="H47" s="5" t="inlineStr"/>
-      <c r="I47" s="5" t="inlineStr"/>
-      <c r="J47" s="5" t="inlineStr"/>
-      <c r="K47" s="5" t="inlineStr"/>
-      <c r="L47" s="5" t="inlineStr"/>
-      <c r="M47" s="5" t="inlineStr"/>
-      <c r="N47" s="5" t="inlineStr"/>
-      <c r="O47" s="5" t="inlineStr"/>
-      <c r="P47" s="5" t="inlineStr"/>
-      <c r="Q47" s="5" t="inlineStr"/>
-      <c r="R47" s="5" t="inlineStr"/>
-      <c r="S47" s="5" t="inlineStr"/>
-      <c r="T47" s="5" t="inlineStr"/>
-      <c r="U47" s="5" t="inlineStr"/>
-      <c r="V47" s="5" t="inlineStr"/>
+      <c r="I47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q47" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R47" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="S47" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T47" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="U47" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V47" s="5" t="n">
+        <v>0.02333333333333333</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
@@ -8388,24 +8732,64 @@
       </c>
       <c r="E48" s="5" t="inlineStr"/>
       <c r="F48" s="5" t="n">
-        <v>0.029</v>
+        <v>0.0289</v>
       </c>
       <c r="G48" s="5" t="inlineStr"/>
       <c r="H48" s="5" t="inlineStr"/>
-      <c r="I48" s="5" t="inlineStr"/>
-      <c r="J48" s="5" t="inlineStr"/>
-      <c r="K48" s="5" t="inlineStr"/>
-      <c r="L48" s="5" t="inlineStr"/>
-      <c r="M48" s="5" t="inlineStr"/>
-      <c r="N48" s="5" t="inlineStr"/>
-      <c r="O48" s="5" t="inlineStr"/>
-      <c r="P48" s="5" t="inlineStr"/>
-      <c r="Q48" s="5" t="inlineStr"/>
-      <c r="R48" s="5" t="inlineStr"/>
-      <c r="S48" s="5" t="inlineStr"/>
-      <c r="T48" s="5" t="inlineStr"/>
-      <c r="U48" s="5" t="inlineStr"/>
-      <c r="V48" s="5" t="inlineStr"/>
+      <c r="I48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q48" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R48" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="S48" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T48" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="U48" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V48" s="5" t="n">
+        <v>0.02333333333333333</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
@@ -8425,27 +8809,67 @@
         <v>0.9704</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>0.0306</v>
+        <v>0.0298</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>0.0532</v>
+        <v>0.0529</v>
       </c>
       <c r="G49" s="5" t="inlineStr"/>
       <c r="H49" s="5" t="inlineStr"/>
-      <c r="I49" s="5" t="inlineStr"/>
-      <c r="J49" s="5" t="inlineStr"/>
-      <c r="K49" s="5" t="inlineStr"/>
-      <c r="L49" s="5" t="inlineStr"/>
-      <c r="M49" s="5" t="inlineStr"/>
-      <c r="N49" s="5" t="inlineStr"/>
-      <c r="O49" s="5" t="inlineStr"/>
-      <c r="P49" s="5" t="inlineStr"/>
-      <c r="Q49" s="5" t="inlineStr"/>
-      <c r="R49" s="5" t="inlineStr"/>
-      <c r="S49" s="5" t="inlineStr"/>
-      <c r="T49" s="5" t="inlineStr"/>
-      <c r="U49" s="5" t="inlineStr"/>
-      <c r="V49" s="5" t="inlineStr"/>
+      <c r="I49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q49" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R49" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="S49" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T49" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="U49" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V49" s="5" t="n">
+        <v>0.01666666666666667</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
@@ -8465,27 +8889,67 @@
         <v>0.987</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.0024</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>0.0011</v>
+        <v>0</v>
       </c>
       <c r="G50" s="5" t="inlineStr"/>
       <c r="H50" s="5" t="inlineStr"/>
-      <c r="I50" s="5" t="inlineStr"/>
-      <c r="J50" s="5" t="inlineStr"/>
-      <c r="K50" s="5" t="inlineStr"/>
-      <c r="L50" s="5" t="inlineStr"/>
-      <c r="M50" s="5" t="inlineStr"/>
-      <c r="N50" s="5" t="inlineStr"/>
-      <c r="O50" s="5" t="inlineStr"/>
-      <c r="P50" s="5" t="inlineStr"/>
-      <c r="Q50" s="5" t="inlineStr"/>
-      <c r="R50" s="5" t="inlineStr"/>
-      <c r="S50" s="5" t="inlineStr"/>
-      <c r="T50" s="5" t="inlineStr"/>
-      <c r="U50" s="5" t="inlineStr"/>
-      <c r="V50" s="5" t="inlineStr"/>
+      <c r="I50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q50" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R50" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="S50" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T50" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="U50" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V50" s="5" t="n">
+        <v>0.01666666666666667</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
@@ -8505,27 +8969,67 @@
         <v>0.9442</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>0.0141</v>
+        <v>0.0114</v>
       </c>
       <c r="F51" s="5" t="n">
-        <v>0.0766</v>
+        <v>0.07630000000000001</v>
       </c>
       <c r="G51" s="5" t="inlineStr"/>
       <c r="H51" s="5" t="inlineStr"/>
-      <c r="I51" s="5" t="inlineStr"/>
-      <c r="J51" s="5" t="inlineStr"/>
-      <c r="K51" s="5" t="inlineStr"/>
-      <c r="L51" s="5" t="inlineStr"/>
-      <c r="M51" s="5" t="inlineStr"/>
-      <c r="N51" s="5" t="inlineStr"/>
-      <c r="O51" s="5" t="inlineStr"/>
-      <c r="P51" s="5" t="inlineStr"/>
-      <c r="Q51" s="5" t="inlineStr"/>
-      <c r="R51" s="5" t="inlineStr"/>
-      <c r="S51" s="5" t="inlineStr"/>
-      <c r="T51" s="5" t="inlineStr"/>
-      <c r="U51" s="5" t="inlineStr"/>
-      <c r="V51" s="5" t="inlineStr"/>
+      <c r="I51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q51" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R51" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="S51" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T51" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="U51" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V51" s="5" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
@@ -8552,20 +9056,60 @@
       </c>
       <c r="G52" s="5" t="inlineStr"/>
       <c r="H52" s="5" t="inlineStr"/>
-      <c r="I52" s="5" t="inlineStr"/>
-      <c r="J52" s="5" t="inlineStr"/>
-      <c r="K52" s="5" t="inlineStr"/>
-      <c r="L52" s="5" t="inlineStr"/>
-      <c r="M52" s="5" t="inlineStr"/>
-      <c r="N52" s="5" t="inlineStr"/>
-      <c r="O52" s="5" t="inlineStr"/>
-      <c r="P52" s="5" t="inlineStr"/>
-      <c r="Q52" s="5" t="inlineStr"/>
-      <c r="R52" s="5" t="inlineStr"/>
-      <c r="S52" s="5" t="inlineStr"/>
-      <c r="T52" s="5" t="inlineStr"/>
-      <c r="U52" s="5" t="inlineStr"/>
-      <c r="V52" s="5" t="inlineStr"/>
+      <c r="I52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Q52" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R52" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="S52" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T52" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="U52" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V52" s="5" t="n">
+        <v>0.02666666666666667</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
@@ -8623,27 +9167,67 @@
         <v>0.9396</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>0.0425</v>
+        <v>0.0395</v>
       </c>
       <c r="F54" s="5" t="n">
         <v>0.0189</v>
       </c>
       <c r="G54" s="5" t="inlineStr"/>
       <c r="H54" s="5" t="inlineStr"/>
-      <c r="I54" s="5" t="inlineStr"/>
-      <c r="J54" s="5" t="inlineStr"/>
-      <c r="K54" s="5" t="inlineStr"/>
-      <c r="L54" s="5" t="inlineStr"/>
-      <c r="M54" s="5" t="inlineStr"/>
-      <c r="N54" s="5" t="inlineStr"/>
-      <c r="O54" s="5" t="inlineStr"/>
-      <c r="P54" s="5" t="inlineStr"/>
-      <c r="Q54" s="5" t="inlineStr"/>
-      <c r="R54" s="5" t="inlineStr"/>
-      <c r="S54" s="5" t="inlineStr"/>
-      <c r="T54" s="5" t="inlineStr"/>
-      <c r="U54" s="5" t="inlineStr"/>
-      <c r="V54" s="5" t="inlineStr"/>
+      <c r="I54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="M54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="O54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q54" s="5" t="inlineStr">
+        <is>
+          <t>25-26</t>
+        </is>
+      </c>
+      <c r="R54" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="S54" s="5" t="inlineStr">
+        <is>
+          <t>26-27</t>
+        </is>
+      </c>
+      <c r="T54" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="U54" s="5" t="inlineStr">
+        <is>
+          <t>27-28</t>
+        </is>
+      </c>
+      <c r="V54" s="5" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
@@ -8664,7 +9248,7 @@
       </c>
       <c r="E55" s="5" t="inlineStr"/>
       <c r="F55" s="5" t="n">
-        <v>0.0039</v>
+        <v>0.0038</v>
       </c>
       <c r="G55" s="5" t="inlineStr"/>
       <c r="H55" s="5" t="inlineStr"/>

--- a/outputs/QLD_curtailment.xlsx
+++ b/outputs/QLD_curtailment.xlsx
@@ -721,7 +721,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>per-DUID</t>
+          <t>location</t>
         </is>
       </c>
       <c r="P3" s="5" t="n">
@@ -849,7 +849,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>per-DUID</t>
+          <t>location</t>
         </is>
       </c>
       <c r="P5" s="5" t="n">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>per-DUID</t>
+          <t>location</t>
         </is>
       </c>
       <c r="P8" s="5" t="n">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>per-DUID</t>
+          <t>location</t>
         </is>
       </c>
       <c r="P9" s="5" t="n">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>per-DUID</t>
+          <t>location</t>
         </is>
       </c>
       <c r="P10" s="5" t="n">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>per-DUID</t>
+          <t>location</t>
         </is>
       </c>
       <c r="P11" s="5" t="n">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>per-DUID</t>
+          <t>location</t>
         </is>
       </c>
       <c r="P12" s="5" t="n">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>per-DUID</t>
+          <t>location</t>
         </is>
       </c>
       <c r="P13" s="5" t="n">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>per-DUID</t>
+          <t>location</t>
         </is>
       </c>
       <c r="P14" s="5" t="n">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>per-DUID</t>
+          <t>location</t>
         </is>
       </c>
       <c r="P15" s="5" t="n">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>per-DUID</t>
+          <t>location</t>
         </is>
       </c>
       <c r="P16" s="5" t="n">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>per-DUID</t>
+          <t>location</t>
         </is>
       </c>
       <c r="P17" s="5" t="n">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>per-DUID</t>
+          <t>location</t>
         </is>
       </c>
       <c r="P19" s="5" t="n">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>per-DUID</t>
+          <t>location</t>
         </is>
       </c>
       <c r="P20" s="5" t="n">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>per-DUID</t>
+          <t>location</t>
         </is>
       </c>
       <c r="P21" s="5" t="n">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>per-DUID</t>
+          <t>location</t>
         </is>
       </c>
       <c r="P22" s="5" t="n">
@@ -2401,7 +2401,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>per-DUID</t>
+          <t>location</t>
         </is>
       </c>
       <c r="P23" s="5" t="n">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>per-DUID</t>
+          <t>location</t>
         </is>
       </c>
       <c r="P24" s="5" t="n">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>per-DUID</t>
+          <t>location</t>
         </is>
       </c>
       <c r="P25" s="5" t="n">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>per-DUID</t>
+          <t>location</t>
         </is>
       </c>
       <c r="P26" s="5" t="n">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>per-DUID</t>
+          <t>location</t>
         </is>
       </c>
       <c r="P27" s="5" t="n">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>per-DUID</t>
+          <t>location</t>
         </is>
       </c>
       <c r="P28" s="5" t="n">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>per-DUID</t>
+          <t>location</t>
         </is>
       </c>
       <c r="P30" s="5" t="n">
@@ -3158,7 +3158,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>per-DUID</t>
+          <t>location</t>
         </is>
       </c>
       <c r="P32" s="5" t="n">
@@ -3253,7 +3253,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>per-DUID</t>
+          <t>location</t>
         </is>
       </c>
       <c r="P33" s="5" t="n">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>per-DUID</t>
+          <t>location</t>
         </is>
       </c>
       <c r="P34" s="5" t="n">
@@ -3443,7 +3443,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>per-DUID</t>
+          <t>location</t>
         </is>
       </c>
       <c r="P35" s="5" t="n">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>per-DUID</t>
+          <t>location</t>
         </is>
       </c>
       <c r="P36" s="5" t="n">
@@ -3633,7 +3633,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>per-DUID</t>
+          <t>location</t>
         </is>
       </c>
       <c r="P37" s="5" t="n">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>per-DUID</t>
+          <t>location</t>
         </is>
       </c>
       <c r="P38" s="5" t="n">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>per-DUID</t>
+          <t>location</t>
         </is>
       </c>
       <c r="P39" s="5" t="n">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>per-DUID</t>
+          <t>location</t>
         </is>
       </c>
       <c r="P41" s="5" t="n">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>per-DUID</t>
+          <t>location</t>
         </is>
       </c>
       <c r="P42" s="5" t="n">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>per-DUID</t>
+          <t>location</t>
         </is>
       </c>
       <c r="P44" s="5" t="n">
@@ -4349,7 +4349,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>per-DUID</t>
+          <t>location</t>
         </is>
       </c>
       <c r="P45" s="5" t="n">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>per-DUID</t>
+          <t>location</t>
         </is>
       </c>
       <c r="P46" s="5" t="n">

--- a/outputs/QLD_curtailment.xlsx
+++ b/outputs/QLD_curtailment.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y57"/>
+  <dimension ref="A1:AG57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -484,6 +484,14 @@
     <col width="12" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="12" customWidth="1" min="28" max="28"/>
+    <col width="12" customWidth="1" min="29" max="29"/>
+    <col width="12" customWidth="1" min="30" max="30"/>
+    <col width="12" customWidth="1" min="31" max="31"/>
+    <col width="12" customWidth="1" min="32" max="32"/>
+    <col width="12" customWidth="1" min="33" max="33"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -610,6 +618,46 @@
       <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Offl Avg</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>2026 ISP REZ</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>2026 ISP REZ match</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>2026 ISP Step Change Transm Curt 2029-30</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>2026 ISP Step Change Transm Curt 2039-40</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>2026 ISP Step Change Transm Curt 2049-50</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>2026 ISP Step Change Econ Spill 2029-30</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>2026 ISP Step Change Econ Spill 2039-40</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>2026 ISP Step Change Econ Spill 2049-50</t>
         </is>
       </c>
     </row>
@@ -663,6 +711,14 @@
       <c r="W2" s="6" t="inlineStr"/>
       <c r="X2" s="6" t="inlineStr"/>
       <c r="Y2" s="6" t="inlineStr"/>
+      <c r="Z2" s="2" t="inlineStr"/>
+      <c r="AA2" s="2" t="inlineStr"/>
+      <c r="AB2" s="6" t="inlineStr"/>
+      <c r="AC2" s="6" t="inlineStr"/>
+      <c r="AD2" s="6" t="inlineStr"/>
+      <c r="AE2" s="6" t="inlineStr"/>
+      <c r="AF2" s="6" t="inlineStr"/>
+      <c r="AG2" s="6" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -738,6 +794,14 @@
       <c r="W3" s="6" t="inlineStr"/>
       <c r="X3" s="6" t="inlineStr"/>
       <c r="Y3" s="6" t="inlineStr"/>
+      <c r="Z3" s="2" t="inlineStr"/>
+      <c r="AA3" s="2" t="inlineStr"/>
+      <c r="AB3" s="6" t="inlineStr"/>
+      <c r="AC3" s="6" t="inlineStr"/>
+      <c r="AD3" s="6" t="inlineStr"/>
+      <c r="AE3" s="6" t="inlineStr"/>
+      <c r="AF3" s="6" t="inlineStr"/>
+      <c r="AG3" s="6" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -787,6 +851,14 @@
       <c r="W4" s="6" t="inlineStr"/>
       <c r="X4" s="6" t="inlineStr"/>
       <c r="Y4" s="6" t="inlineStr"/>
+      <c r="Z4" s="2" t="inlineStr"/>
+      <c r="AA4" s="2" t="inlineStr"/>
+      <c r="AB4" s="6" t="inlineStr"/>
+      <c r="AC4" s="6" t="inlineStr"/>
+      <c r="AD4" s="6" t="inlineStr"/>
+      <c r="AE4" s="6" t="inlineStr"/>
+      <c r="AF4" s="6" t="inlineStr"/>
+      <c r="AG4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -881,6 +953,34 @@
       </c>
       <c r="Y5" s="6" t="n">
         <v>0.01666666666666667</v>
+      </c>
+      <c r="Z5" s="2" t="inlineStr">
+        <is>
+          <t>Darling Downs</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AB5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AF5" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AG5" s="6" t="n">
+        <v>0.09</v>
       </c>
     </row>
     <row r="6">
@@ -939,6 +1039,14 @@
       <c r="W6" s="6" t="inlineStr"/>
       <c r="X6" s="6" t="inlineStr"/>
       <c r="Y6" s="6" t="inlineStr"/>
+      <c r="Z6" s="2" t="inlineStr"/>
+      <c r="AA6" s="2" t="inlineStr"/>
+      <c r="AB6" s="6" t="inlineStr"/>
+      <c r="AC6" s="6" t="inlineStr"/>
+      <c r="AD6" s="6" t="inlineStr"/>
+      <c r="AE6" s="6" t="inlineStr"/>
+      <c r="AF6" s="6" t="inlineStr"/>
+      <c r="AG6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -996,6 +1104,14 @@
       <c r="W7" s="6" t="inlineStr"/>
       <c r="X7" s="6" t="inlineStr"/>
       <c r="Y7" s="6" t="inlineStr"/>
+      <c r="Z7" s="2" t="inlineStr"/>
+      <c r="AA7" s="2" t="inlineStr"/>
+      <c r="AB7" s="6" t="inlineStr"/>
+      <c r="AC7" s="6" t="inlineStr"/>
+      <c r="AD7" s="6" t="inlineStr"/>
+      <c r="AE7" s="6" t="inlineStr"/>
+      <c r="AF7" s="6" t="inlineStr"/>
+      <c r="AG7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1091,6 +1207,34 @@
       <c r="Y8" s="6" t="n">
         <v>0.04666666666666667</v>
       </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t>Wide Bay</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AB8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AF8" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AG8" s="6" t="n">
+        <v>0.13</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1186,6 +1330,34 @@
       <c r="Y9" s="6" t="n">
         <v>0.03</v>
       </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>Northern Queensland</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AB9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AG9" s="6" t="n">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1281,6 +1453,18 @@
       <c r="Y10" s="6" t="n">
         <v>0.02333333333333333</v>
       </c>
+      <c r="Z10" s="2" t="inlineStr"/>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>no one-to-one match</t>
+        </is>
+      </c>
+      <c r="AB10" s="6" t="inlineStr"/>
+      <c r="AC10" s="6" t="inlineStr"/>
+      <c r="AD10" s="6" t="inlineStr"/>
+      <c r="AE10" s="6" t="inlineStr"/>
+      <c r="AF10" s="6" t="inlineStr"/>
+      <c r="AG10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1376,6 +1560,18 @@
       <c r="Y11" s="6" t="n">
         <v>0.02333333333333333</v>
       </c>
+      <c r="Z11" s="2" t="inlineStr"/>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>no one-to-one match</t>
+        </is>
+      </c>
+      <c r="AB11" s="6" t="inlineStr"/>
+      <c r="AC11" s="6" t="inlineStr"/>
+      <c r="AD11" s="6" t="inlineStr"/>
+      <c r="AE11" s="6" t="inlineStr"/>
+      <c r="AF11" s="6" t="inlineStr"/>
+      <c r="AG11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1471,6 +1667,34 @@
       <c r="Y12" s="6" t="n">
         <v>0.01666666666666667</v>
       </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>Darling Downs</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AB12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AF12" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AG12" s="6" t="n">
+        <v>0.09</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1566,6 +1790,34 @@
       <c r="Y13" s="6" t="n">
         <v>0.01666666666666667</v>
       </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>Darling Downs</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AB13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AF13" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AG13" s="6" t="n">
+        <v>0.09</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1661,6 +1913,18 @@
       <c r="Y14" s="6" t="n">
         <v>0.02333333333333333</v>
       </c>
+      <c r="Z14" s="2" t="inlineStr"/>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>no one-to-one match</t>
+        </is>
+      </c>
+      <c r="AB14" s="6" t="inlineStr"/>
+      <c r="AC14" s="6" t="inlineStr"/>
+      <c r="AD14" s="6" t="inlineStr"/>
+      <c r="AE14" s="6" t="inlineStr"/>
+      <c r="AF14" s="6" t="inlineStr"/>
+      <c r="AG14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1755,6 +2019,34 @@
       </c>
       <c r="Y15" s="6" t="n">
         <v>0.01666666666666667</v>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>Darling Downs</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AB15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AF15" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AG15" s="6" t="n">
+        <v>0.09</v>
       </c>
     </row>
     <row r="16">
@@ -1835,6 +2127,14 @@
       <c r="W16" s="6" t="inlineStr"/>
       <c r="X16" s="6" t="inlineStr"/>
       <c r="Y16" s="6" t="inlineStr"/>
+      <c r="Z16" s="2" t="inlineStr"/>
+      <c r="AA16" s="2" t="inlineStr"/>
+      <c r="AB16" s="6" t="inlineStr"/>
+      <c r="AC16" s="6" t="inlineStr"/>
+      <c r="AD16" s="6" t="inlineStr"/>
+      <c r="AE16" s="6" t="inlineStr"/>
+      <c r="AF16" s="6" t="inlineStr"/>
+      <c r="AG16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1929,6 +2229,34 @@
       </c>
       <c r="Y17" s="6" t="n">
         <v>0.01666666666666667</v>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>Darling Downs</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AB17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AF17" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AG17" s="6" t="n">
+        <v>0.09</v>
       </c>
     </row>
     <row r="18">
@@ -1979,6 +2307,14 @@
       <c r="W18" s="6" t="inlineStr"/>
       <c r="X18" s="6" t="inlineStr"/>
       <c r="Y18" s="6" t="inlineStr"/>
+      <c r="Z18" s="2" t="inlineStr"/>
+      <c r="AA18" s="2" t="inlineStr"/>
+      <c r="AB18" s="6" t="inlineStr"/>
+      <c r="AC18" s="6" t="inlineStr"/>
+      <c r="AD18" s="6" t="inlineStr"/>
+      <c r="AE18" s="6" t="inlineStr"/>
+      <c r="AF18" s="6" t="inlineStr"/>
+      <c r="AG18" s="6" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -2074,6 +2410,18 @@
       <c r="Y19" s="6" t="n">
         <v>0.02333333333333333</v>
       </c>
+      <c r="Z19" s="2" t="inlineStr"/>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>no one-to-one match</t>
+        </is>
+      </c>
+      <c r="AB19" s="6" t="inlineStr"/>
+      <c r="AC19" s="6" t="inlineStr"/>
+      <c r="AD19" s="6" t="inlineStr"/>
+      <c r="AE19" s="6" t="inlineStr"/>
+      <c r="AF19" s="6" t="inlineStr"/>
+      <c r="AG19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -2169,6 +2517,34 @@
       <c r="Y20" s="6" t="n">
         <v>0.03</v>
       </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>Northern Queensland</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AB20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AG20" s="6" t="n">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -2264,6 +2640,18 @@
       <c r="Y21" s="6" t="n">
         <v>0.02333333333333333</v>
       </c>
+      <c r="Z21" s="2" t="inlineStr"/>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>no one-to-one match</t>
+        </is>
+      </c>
+      <c r="AB21" s="6" t="inlineStr"/>
+      <c r="AC21" s="6" t="inlineStr"/>
+      <c r="AD21" s="6" t="inlineStr"/>
+      <c r="AE21" s="6" t="inlineStr"/>
+      <c r="AF21" s="6" t="inlineStr"/>
+      <c r="AG21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -2339,6 +2727,14 @@
       <c r="W22" s="6" t="inlineStr"/>
       <c r="X22" s="6" t="inlineStr"/>
       <c r="Y22" s="6" t="inlineStr"/>
+      <c r="Z22" s="2" t="inlineStr"/>
+      <c r="AA22" s="2" t="inlineStr"/>
+      <c r="AB22" s="6" t="inlineStr"/>
+      <c r="AC22" s="6" t="inlineStr"/>
+      <c r="AD22" s="6" t="inlineStr"/>
+      <c r="AE22" s="6" t="inlineStr"/>
+      <c r="AF22" s="6" t="inlineStr"/>
+      <c r="AG22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -2434,6 +2830,34 @@
       <c r="Y23" s="6" t="n">
         <v>0.02666666666666667</v>
       </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>Hughenden Hub</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+      <c r="AB23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AF23" s="6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AG23" s="6" t="n">
+        <v>0.06</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -2528,6 +2952,34 @@
       </c>
       <c r="Y24" s="6" t="n">
         <v>0.02666666666666667</v>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>Hughenden Hub</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+      <c r="AB24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AF24" s="6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AG24" s="6" t="n">
+        <v>0.06</v>
       </c>
     </row>
     <row r="25">
@@ -2606,6 +3058,14 @@
       <c r="W25" s="6" t="inlineStr"/>
       <c r="X25" s="6" t="inlineStr"/>
       <c r="Y25" s="6" t="inlineStr"/>
+      <c r="Z25" s="2" t="inlineStr"/>
+      <c r="AA25" s="2" t="inlineStr"/>
+      <c r="AB25" s="6" t="inlineStr"/>
+      <c r="AC25" s="6" t="inlineStr"/>
+      <c r="AD25" s="6" t="inlineStr"/>
+      <c r="AE25" s="6" t="inlineStr"/>
+      <c r="AF25" s="6" t="inlineStr"/>
+      <c r="AG25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2701,6 +3161,18 @@
       <c r="Y26" s="6" t="n">
         <v>0.02333333333333333</v>
       </c>
+      <c r="Z26" s="2" t="inlineStr"/>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>no one-to-one match</t>
+        </is>
+      </c>
+      <c r="AB26" s="6" t="inlineStr"/>
+      <c r="AC26" s="6" t="inlineStr"/>
+      <c r="AD26" s="6" t="inlineStr"/>
+      <c r="AE26" s="6" t="inlineStr"/>
+      <c r="AF26" s="6" t="inlineStr"/>
+      <c r="AG26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2776,6 +3248,14 @@
       <c r="W27" s="6" t="inlineStr"/>
       <c r="X27" s="6" t="inlineStr"/>
       <c r="Y27" s="6" t="inlineStr"/>
+      <c r="Z27" s="2" t="inlineStr"/>
+      <c r="AA27" s="2" t="inlineStr"/>
+      <c r="AB27" s="6" t="inlineStr"/>
+      <c r="AC27" s="6" t="inlineStr"/>
+      <c r="AD27" s="6" t="inlineStr"/>
+      <c r="AE27" s="6" t="inlineStr"/>
+      <c r="AF27" s="6" t="inlineStr"/>
+      <c r="AG27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2870,6 +3350,34 @@
       </c>
       <c r="Y28" s="6" t="n">
         <v>0.01666666666666667</v>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>Darling Downs</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AB28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AF28" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AG28" s="6" t="n">
+        <v>0.09</v>
       </c>
     </row>
     <row r="29">
@@ -2952,6 +3460,18 @@
       <c r="Y29" s="6" t="n">
         <v>0.02333333333333333</v>
       </c>
+      <c r="Z29" s="2" t="inlineStr"/>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>no one-to-one match</t>
+        </is>
+      </c>
+      <c r="AB29" s="6" t="inlineStr"/>
+      <c r="AC29" s="6" t="inlineStr"/>
+      <c r="AD29" s="6" t="inlineStr"/>
+      <c r="AE29" s="6" t="inlineStr"/>
+      <c r="AF29" s="6" t="inlineStr"/>
+      <c r="AG29" s="6" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -3046,6 +3566,34 @@
       </c>
       <c r="Y30" s="6" t="n">
         <v>0.02333333333333333</v>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>Fitzroy</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AB30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AF30" s="6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AG30" s="6" t="n">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -3096,6 +3644,14 @@
       <c r="W31" s="6" t="inlineStr"/>
       <c r="X31" s="6" t="inlineStr"/>
       <c r="Y31" s="6" t="inlineStr"/>
+      <c r="Z31" s="2" t="inlineStr"/>
+      <c r="AA31" s="2" t="inlineStr"/>
+      <c r="AB31" s="6" t="inlineStr"/>
+      <c r="AC31" s="6" t="inlineStr"/>
+      <c r="AD31" s="6" t="inlineStr"/>
+      <c r="AE31" s="6" t="inlineStr"/>
+      <c r="AF31" s="6" t="inlineStr"/>
+      <c r="AG31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -3191,6 +3747,34 @@
       <c r="Y32" s="6" t="n">
         <v>0.01666666666666667</v>
       </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>Darling Downs</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AB32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AF32" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AG32" s="6" t="n">
+        <v>0.09</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -3286,6 +3870,34 @@
       <c r="Y33" s="6" t="n">
         <v>0.01666666666666667</v>
       </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>Darling Downs</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AB33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AF33" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AG33" s="6" t="n">
+        <v>0.09</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -3381,6 +3993,34 @@
       <c r="Y34" s="6" t="n">
         <v>0.03</v>
       </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>Northern Queensland</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AB34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AG34" s="6" t="n">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -3476,6 +4116,18 @@
       <c r="Y35" s="6" t="n">
         <v>0.02333333333333333</v>
       </c>
+      <c r="Z35" s="2" t="inlineStr"/>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>no one-to-one match</t>
+        </is>
+      </c>
+      <c r="AB35" s="6" t="inlineStr"/>
+      <c r="AC35" s="6" t="inlineStr"/>
+      <c r="AD35" s="6" t="inlineStr"/>
+      <c r="AE35" s="6" t="inlineStr"/>
+      <c r="AF35" s="6" t="inlineStr"/>
+      <c r="AG35" s="6" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -3571,6 +4223,34 @@
       <c r="Y36" s="6" t="n">
         <v>0.03</v>
       </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>Northern Queensland</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AB36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" s="6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AG36" s="6" t="n">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -3665,6 +4345,34 @@
       </c>
       <c r="Y37" s="6" t="n">
         <v>0.04666666666666667</v>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>Wide Bay</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AB37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AF37" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AG37" s="6" t="n">
+        <v>0.13</v>
       </c>
     </row>
     <row r="38">
@@ -3741,6 +4449,14 @@
       <c r="W38" s="6" t="inlineStr"/>
       <c r="X38" s="6" t="inlineStr"/>
       <c r="Y38" s="6" t="inlineStr"/>
+      <c r="Z38" s="2" t="inlineStr"/>
+      <c r="AA38" s="2" t="inlineStr"/>
+      <c r="AB38" s="6" t="inlineStr"/>
+      <c r="AC38" s="6" t="inlineStr"/>
+      <c r="AD38" s="6" t="inlineStr"/>
+      <c r="AE38" s="6" t="inlineStr"/>
+      <c r="AF38" s="6" t="inlineStr"/>
+      <c r="AG38" s="6" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -3835,6 +4551,34 @@
       </c>
       <c r="Y39" s="6" t="n">
         <v>0.01666666666666667</v>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>Darling Downs</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AB39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AF39" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AG39" s="6" t="n">
+        <v>0.09</v>
       </c>
     </row>
     <row r="40">
@@ -3913,6 +4657,34 @@
       <c r="Y40" s="6" t="n">
         <v>0.01666666666666667</v>
       </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>Darling Downs</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AB40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE40" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AF40" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AG40" s="6" t="n">
+        <v>0.09</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -4008,6 +4780,34 @@
       <c r="Y41" s="6" t="n">
         <v>0.01666666666666667</v>
       </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>Darling Downs</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AB41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE41" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AF41" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AG41" s="6" t="n">
+        <v>0.09</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -4103,6 +4903,34 @@
       <c r="Y42" s="6" t="n">
         <v>0.01666666666666667</v>
       </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>Darling Downs</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AB42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE42" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AF42" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AG42" s="6" t="n">
+        <v>0.09</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -4192,6 +5020,34 @@
       <c r="Y43" s="6" t="n">
         <v>0.01666666666666667</v>
       </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>Darling Downs</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AB43" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC43" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD43" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE43" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AF43" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AG43" s="6" t="n">
+        <v>0.09</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -4287,6 +5143,18 @@
       <c r="Y44" s="6" t="n">
         <v>0.02333333333333333</v>
       </c>
+      <c r="Z44" s="2" t="inlineStr"/>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>no one-to-one match</t>
+        </is>
+      </c>
+      <c r="AB44" s="6" t="inlineStr"/>
+      <c r="AC44" s="6" t="inlineStr"/>
+      <c r="AD44" s="6" t="inlineStr"/>
+      <c r="AE44" s="6" t="inlineStr"/>
+      <c r="AF44" s="6" t="inlineStr"/>
+      <c r="AG44" s="6" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -4382,6 +5250,34 @@
       <c r="Y45" s="6" t="n">
         <v>0.04666666666666667</v>
       </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>Wide Bay</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AB45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE45" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AF45" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AG45" s="6" t="n">
+        <v>0.13</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -4476,6 +5372,34 @@
       </c>
       <c r="Y46" s="6" t="n">
         <v>0.01666666666666667</v>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>Darling Downs</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AB46" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC46" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD46" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE46" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AF46" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AG46" s="6" t="n">
+        <v>0.09</v>
       </c>
     </row>
     <row r="47">
@@ -4556,6 +5480,18 @@
       <c r="Y47" s="6" t="n">
         <v>0.02333333333333333</v>
       </c>
+      <c r="Z47" s="2" t="inlineStr"/>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>no one-to-one match</t>
+        </is>
+      </c>
+      <c r="AB47" s="6" t="inlineStr"/>
+      <c r="AC47" s="6" t="inlineStr"/>
+      <c r="AD47" s="6" t="inlineStr"/>
+      <c r="AE47" s="6" t="inlineStr"/>
+      <c r="AF47" s="6" t="inlineStr"/>
+      <c r="AG47" s="6" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -4635,6 +5571,18 @@
       <c r="Y48" s="6" t="n">
         <v>0.02333333333333333</v>
       </c>
+      <c r="Z48" s="2" t="inlineStr"/>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>no one-to-one match</t>
+        </is>
+      </c>
+      <c r="AB48" s="6" t="inlineStr"/>
+      <c r="AC48" s="6" t="inlineStr"/>
+      <c r="AD48" s="6" t="inlineStr"/>
+      <c r="AE48" s="6" t="inlineStr"/>
+      <c r="AF48" s="6" t="inlineStr"/>
+      <c r="AG48" s="6" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -4716,6 +5664,34 @@
       <c r="Y49" s="6" t="n">
         <v>0.01666666666666667</v>
       </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>Darling Downs</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AB49" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC49" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD49" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE49" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AF49" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AG49" s="6" t="n">
+        <v>0.09</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -4797,6 +5773,34 @@
       <c r="Y50" s="6" t="n">
         <v>0.01666666666666667</v>
       </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>Darling Downs</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AB50" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC50" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD50" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE50" s="6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AF50" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AG50" s="6" t="n">
+        <v>0.09</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -4878,6 +5882,34 @@
       <c r="Y51" s="6" t="n">
         <v>0.02</v>
       </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>Far North Queensland</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AB51" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC51" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD51" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AE51" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF51" s="6" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AG51" s="6" t="n">
+        <v>0.16</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -4958,6 +5990,34 @@
       </c>
       <c r="Y52" s="6" t="n">
         <v>0.02666666666666667</v>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>Hughenden Hub</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>renamed</t>
+        </is>
+      </c>
+      <c r="AB52" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC52" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD52" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE52" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AF52" s="6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AG52" s="6" t="n">
+        <v>0.06</v>
       </c>
     </row>
     <row r="53">
@@ -5022,6 +6082,14 @@
       <c r="W53" s="6" t="inlineStr"/>
       <c r="X53" s="6" t="inlineStr"/>
       <c r="Y53" s="6" t="inlineStr"/>
+      <c r="Z53" s="2" t="inlineStr"/>
+      <c r="AA53" s="2" t="inlineStr"/>
+      <c r="AB53" s="6" t="inlineStr"/>
+      <c r="AC53" s="6" t="inlineStr"/>
+      <c r="AD53" s="6" t="inlineStr"/>
+      <c r="AE53" s="6" t="inlineStr"/>
+      <c r="AF53" s="6" t="inlineStr"/>
+      <c r="AG53" s="6" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -5102,6 +6170,34 @@
       </c>
       <c r="Y54" s="6" t="n">
         <v>0.02</v>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>Far North Queensland</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AB54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD54" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AE54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF54" s="6" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AG54" s="6" t="n">
+        <v>0.16</v>
       </c>
     </row>
     <row r="55">
@@ -5154,6 +6250,14 @@
       <c r="W55" s="6" t="inlineStr"/>
       <c r="X55" s="6" t="inlineStr"/>
       <c r="Y55" s="6" t="inlineStr"/>
+      <c r="Z55" s="2" t="inlineStr"/>
+      <c r="AA55" s="2" t="inlineStr"/>
+      <c r="AB55" s="6" t="inlineStr"/>
+      <c r="AC55" s="6" t="inlineStr"/>
+      <c r="AD55" s="6" t="inlineStr"/>
+      <c r="AE55" s="6" t="inlineStr"/>
+      <c r="AF55" s="6" t="inlineStr"/>
+      <c r="AG55" s="6" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -5203,6 +6307,14 @@
       <c r="W56" s="6" t="inlineStr"/>
       <c r="X56" s="6" t="inlineStr"/>
       <c r="Y56" s="6" t="inlineStr"/>
+      <c r="Z56" s="2" t="inlineStr"/>
+      <c r="AA56" s="2" t="inlineStr"/>
+      <c r="AB56" s="6" t="inlineStr"/>
+      <c r="AC56" s="6" t="inlineStr"/>
+      <c r="AD56" s="6" t="inlineStr"/>
+      <c r="AE56" s="6" t="inlineStr"/>
+      <c r="AF56" s="6" t="inlineStr"/>
+      <c r="AG56" s="6" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -5252,6 +6364,14 @@
       <c r="W57" s="6" t="inlineStr"/>
       <c r="X57" s="6" t="inlineStr"/>
       <c r="Y57" s="6" t="inlineStr"/>
+      <c r="Z57" s="2" t="inlineStr"/>
+      <c r="AA57" s="2" t="inlineStr"/>
+      <c r="AB57" s="6" t="inlineStr"/>
+      <c r="AC57" s="6" t="inlineStr"/>
+      <c r="AD57" s="6" t="inlineStr"/>
+      <c r="AE57" s="6" t="inlineStr"/>
+      <c r="AF57" s="6" t="inlineStr"/>
+      <c r="AG57" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5264,7 +6384,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V57"/>
+  <dimension ref="A1:AB57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5289,6 +6409,12 @@
     <col width="14" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
+    <col width="14" customWidth="1" min="27" max="27"/>
+    <col width="14" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5400,6 +6526,36 @@
       <c r="V1" s="7" t="inlineStr">
         <is>
           <t>ISP_OFFLOADING_AVG</t>
+        </is>
+      </c>
+      <c r="W1" s="7" t="inlineStr">
+        <is>
+          <t>ISPA3_TRANSMISSION_Y1</t>
+        </is>
+      </c>
+      <c r="X1" s="7" t="inlineStr">
+        <is>
+          <t>ISPA3_TRANSMISSION_Y2</t>
+        </is>
+      </c>
+      <c r="Y1" s="7" t="inlineStr">
+        <is>
+          <t>ISPA3_TRANSMISSION_Y3</t>
+        </is>
+      </c>
+      <c r="Z1" s="7" t="inlineStr">
+        <is>
+          <t>ISPA3_SPILL_Y1</t>
+        </is>
+      </c>
+      <c r="AA1" s="7" t="inlineStr">
+        <is>
+          <t>ISPA3_SPILL_Y2</t>
+        </is>
+      </c>
+      <c r="AB1" s="7" t="inlineStr">
+        <is>
+          <t>ISPA3_SPILL_Y3</t>
         </is>
       </c>
     </row>
@@ -5440,6 +6596,12 @@
       <c r="T2" s="5" t="inlineStr"/>
       <c r="U2" s="5" t="inlineStr"/>
       <c r="V2" s="5" t="inlineStr"/>
+      <c r="W2" s="5" t="inlineStr"/>
+      <c r="X2" s="5" t="inlineStr"/>
+      <c r="Y2" s="5" t="inlineStr"/>
+      <c r="Z2" s="5" t="inlineStr"/>
+      <c r="AA2" s="5" t="inlineStr"/>
+      <c r="AB2" s="5" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
@@ -5480,6 +6642,12 @@
       <c r="T3" s="5" t="inlineStr"/>
       <c r="U3" s="5" t="inlineStr"/>
       <c r="V3" s="5" t="inlineStr"/>
+      <c r="W3" s="5" t="inlineStr"/>
+      <c r="X3" s="5" t="inlineStr"/>
+      <c r="Y3" s="5" t="inlineStr"/>
+      <c r="Z3" s="5" t="inlineStr"/>
+      <c r="AA3" s="5" t="inlineStr"/>
+      <c r="AB3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
@@ -5516,6 +6684,12 @@
       <c r="T4" s="5" t="inlineStr"/>
       <c r="U4" s="5" t="inlineStr"/>
       <c r="V4" s="5" t="inlineStr"/>
+      <c r="W4" s="5" t="inlineStr"/>
+      <c r="X4" s="5" t="inlineStr"/>
+      <c r="Y4" s="5" t="inlineStr"/>
+      <c r="Z4" s="5" t="inlineStr"/>
+      <c r="AA4" s="5" t="inlineStr"/>
+      <c r="AB4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
@@ -5599,6 +6773,24 @@
       </c>
       <c r="V5" s="5" t="n">
         <v>0.01666666666666667</v>
+      </c>
+      <c r="W5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AA5" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AB5" s="5" t="n">
+        <v>0.09</v>
       </c>
     </row>
     <row r="6">
@@ -5640,6 +6832,12 @@
       <c r="T6" s="5" t="inlineStr"/>
       <c r="U6" s="5" t="inlineStr"/>
       <c r="V6" s="5" t="inlineStr"/>
+      <c r="W6" s="5" t="inlineStr"/>
+      <c r="X6" s="5" t="inlineStr"/>
+      <c r="Y6" s="5" t="inlineStr"/>
+      <c r="Z6" s="5" t="inlineStr"/>
+      <c r="AA6" s="5" t="inlineStr"/>
+      <c r="AB6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
@@ -5680,6 +6878,12 @@
       <c r="T7" s="5" t="inlineStr"/>
       <c r="U7" s="5" t="inlineStr"/>
       <c r="V7" s="5" t="inlineStr"/>
+      <c r="W7" s="5" t="inlineStr"/>
+      <c r="X7" s="5" t="inlineStr"/>
+      <c r="Y7" s="5" t="inlineStr"/>
+      <c r="Z7" s="5" t="inlineStr"/>
+      <c r="AA7" s="5" t="inlineStr"/>
+      <c r="AB7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
@@ -5764,6 +6968,24 @@
       <c r="V8" s="5" t="n">
         <v>0.04666666666666667</v>
       </c>
+      <c r="W8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AA8" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB8" s="5" t="n">
+        <v>0.13</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
@@ -5848,6 +7070,24 @@
       <c r="V9" s="5" t="n">
         <v>0.03</v>
       </c>
+      <c r="W9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AB9" s="5" t="n">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
@@ -5932,6 +7172,12 @@
       <c r="V10" s="5" t="n">
         <v>0.02333333333333333</v>
       </c>
+      <c r="W10" s="5" t="inlineStr"/>
+      <c r="X10" s="5" t="inlineStr"/>
+      <c r="Y10" s="5" t="inlineStr"/>
+      <c r="Z10" s="5" t="inlineStr"/>
+      <c r="AA10" s="5" t="inlineStr"/>
+      <c r="AB10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
@@ -6016,6 +7262,12 @@
       <c r="V11" s="5" t="n">
         <v>0.02333333333333333</v>
       </c>
+      <c r="W11" s="5" t="inlineStr"/>
+      <c r="X11" s="5" t="inlineStr"/>
+      <c r="Y11" s="5" t="inlineStr"/>
+      <c r="Z11" s="5" t="inlineStr"/>
+      <c r="AA11" s="5" t="inlineStr"/>
+      <c r="AB11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
@@ -6100,6 +7352,24 @@
       <c r="V12" s="5" t="n">
         <v>0.01666666666666667</v>
       </c>
+      <c r="W12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AA12" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AB12" s="5" t="n">
+        <v>0.09</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
@@ -6184,6 +7454,24 @@
       <c r="V13" s="5" t="n">
         <v>0.01666666666666667</v>
       </c>
+      <c r="W13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AA13" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AB13" s="5" t="n">
+        <v>0.09</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
@@ -6268,6 +7556,12 @@
       <c r="V14" s="5" t="n">
         <v>0.02333333333333333</v>
       </c>
+      <c r="W14" s="5" t="inlineStr"/>
+      <c r="X14" s="5" t="inlineStr"/>
+      <c r="Y14" s="5" t="inlineStr"/>
+      <c r="Z14" s="5" t="inlineStr"/>
+      <c r="AA14" s="5" t="inlineStr"/>
+      <c r="AB14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
@@ -6351,6 +7645,24 @@
       </c>
       <c r="V15" s="5" t="n">
         <v>0.01666666666666667</v>
+      </c>
+      <c r="W15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AA15" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AB15" s="5" t="n">
+        <v>0.09</v>
       </c>
     </row>
     <row r="16">
@@ -6396,6 +7708,12 @@
       <c r="T16" s="5" t="inlineStr"/>
       <c r="U16" s="5" t="inlineStr"/>
       <c r="V16" s="5" t="inlineStr"/>
+      <c r="W16" s="5" t="inlineStr"/>
+      <c r="X16" s="5" t="inlineStr"/>
+      <c r="Y16" s="5" t="inlineStr"/>
+      <c r="Z16" s="5" t="inlineStr"/>
+      <c r="AA16" s="5" t="inlineStr"/>
+      <c r="AB16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
@@ -6479,6 +7797,24 @@
       </c>
       <c r="V17" s="5" t="n">
         <v>0.01666666666666667</v>
+      </c>
+      <c r="W17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AA17" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AB17" s="5" t="n">
+        <v>0.09</v>
       </c>
     </row>
     <row r="18">
@@ -6516,6 +7852,12 @@
       <c r="T18" s="5" t="inlineStr"/>
       <c r="U18" s="5" t="inlineStr"/>
       <c r="V18" s="5" t="inlineStr"/>
+      <c r="W18" s="5" t="inlineStr"/>
+      <c r="X18" s="5" t="inlineStr"/>
+      <c r="Y18" s="5" t="inlineStr"/>
+      <c r="Z18" s="5" t="inlineStr"/>
+      <c r="AA18" s="5" t="inlineStr"/>
+      <c r="AB18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
@@ -6600,6 +7942,12 @@
       <c r="V19" s="5" t="n">
         <v>0.02333333333333333</v>
       </c>
+      <c r="W19" s="5" t="inlineStr"/>
+      <c r="X19" s="5" t="inlineStr"/>
+      <c r="Y19" s="5" t="inlineStr"/>
+      <c r="Z19" s="5" t="inlineStr"/>
+      <c r="AA19" s="5" t="inlineStr"/>
+      <c r="AB19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
@@ -6684,6 +8032,24 @@
       <c r="V20" s="5" t="n">
         <v>0.03</v>
       </c>
+      <c r="W20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AB20" s="5" t="n">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
@@ -6768,6 +8134,12 @@
       <c r="V21" s="5" t="n">
         <v>0.02333333333333333</v>
       </c>
+      <c r="W21" s="5" t="inlineStr"/>
+      <c r="X21" s="5" t="inlineStr"/>
+      <c r="Y21" s="5" t="inlineStr"/>
+      <c r="Z21" s="5" t="inlineStr"/>
+      <c r="AA21" s="5" t="inlineStr"/>
+      <c r="AB21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
@@ -6808,6 +8180,12 @@
       <c r="T22" s="5" t="inlineStr"/>
       <c r="U22" s="5" t="inlineStr"/>
       <c r="V22" s="5" t="inlineStr"/>
+      <c r="W22" s="5" t="inlineStr"/>
+      <c r="X22" s="5" t="inlineStr"/>
+      <c r="Y22" s="5" t="inlineStr"/>
+      <c r="Z22" s="5" t="inlineStr"/>
+      <c r="AA22" s="5" t="inlineStr"/>
+      <c r="AB22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
@@ -6892,6 +8270,24 @@
       <c r="V23" s="5" t="n">
         <v>0.02666666666666667</v>
       </c>
+      <c r="W23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AA23" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AB23" s="5" t="n">
+        <v>0.06</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
@@ -6975,6 +8371,24 @@
       </c>
       <c r="V24" s="5" t="n">
         <v>0.02666666666666667</v>
+      </c>
+      <c r="W24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AA24" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AB24" s="5" t="n">
+        <v>0.06</v>
       </c>
     </row>
     <row r="25">
@@ -7018,6 +8432,12 @@
       <c r="T25" s="5" t="inlineStr"/>
       <c r="U25" s="5" t="inlineStr"/>
       <c r="V25" s="5" t="inlineStr"/>
+      <c r="W25" s="5" t="inlineStr"/>
+      <c r="X25" s="5" t="inlineStr"/>
+      <c r="Y25" s="5" t="inlineStr"/>
+      <c r="Z25" s="5" t="inlineStr"/>
+      <c r="AA25" s="5" t="inlineStr"/>
+      <c r="AB25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
@@ -7102,6 +8522,12 @@
       <c r="V26" s="5" t="n">
         <v>0.02333333333333333</v>
       </c>
+      <c r="W26" s="5" t="inlineStr"/>
+      <c r="X26" s="5" t="inlineStr"/>
+      <c r="Y26" s="5" t="inlineStr"/>
+      <c r="Z26" s="5" t="inlineStr"/>
+      <c r="AA26" s="5" t="inlineStr"/>
+      <c r="AB26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
@@ -7142,6 +8568,12 @@
       <c r="T27" s="5" t="inlineStr"/>
       <c r="U27" s="5" t="inlineStr"/>
       <c r="V27" s="5" t="inlineStr"/>
+      <c r="W27" s="5" t="inlineStr"/>
+      <c r="X27" s="5" t="inlineStr"/>
+      <c r="Y27" s="5" t="inlineStr"/>
+      <c r="Z27" s="5" t="inlineStr"/>
+      <c r="AA27" s="5" t="inlineStr"/>
+      <c r="AB27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
@@ -7226,6 +8658,24 @@
       <c r="V28" s="5" t="n">
         <v>0.01666666666666667</v>
       </c>
+      <c r="W28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AA28" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AB28" s="5" t="n">
+        <v>0.09</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
@@ -7306,6 +8756,12 @@
       <c r="V29" s="5" t="n">
         <v>0.02333333333333333</v>
       </c>
+      <c r="W29" s="5" t="inlineStr"/>
+      <c r="X29" s="5" t="inlineStr"/>
+      <c r="Y29" s="5" t="inlineStr"/>
+      <c r="Z29" s="5" t="inlineStr"/>
+      <c r="AA29" s="5" t="inlineStr"/>
+      <c r="AB29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
@@ -7389,6 +8845,24 @@
       </c>
       <c r="V30" s="5" t="n">
         <v>0.02333333333333333</v>
+      </c>
+      <c r="W30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AA30" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AB30" s="5" t="n">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -7426,6 +8900,12 @@
       <c r="T31" s="5" t="inlineStr"/>
       <c r="U31" s="5" t="inlineStr"/>
       <c r="V31" s="5" t="inlineStr"/>
+      <c r="W31" s="5" t="inlineStr"/>
+      <c r="X31" s="5" t="inlineStr"/>
+      <c r="Y31" s="5" t="inlineStr"/>
+      <c r="Z31" s="5" t="inlineStr"/>
+      <c r="AA31" s="5" t="inlineStr"/>
+      <c r="AB31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
@@ -7510,6 +8990,24 @@
       <c r="V32" s="5" t="n">
         <v>0.01666666666666667</v>
       </c>
+      <c r="W32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AA32" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AB32" s="5" t="n">
+        <v>0.09</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
@@ -7594,6 +9092,24 @@
       <c r="V33" s="5" t="n">
         <v>0.01666666666666667</v>
       </c>
+      <c r="W33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AA33" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AB33" s="5" t="n">
+        <v>0.09</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
@@ -7678,6 +9194,24 @@
       <c r="V34" s="5" t="n">
         <v>0.03</v>
       </c>
+      <c r="W34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AB34" s="5" t="n">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
@@ -7762,6 +9296,12 @@
       <c r="V35" s="5" t="n">
         <v>0.02333333333333333</v>
       </c>
+      <c r="W35" s="5" t="inlineStr"/>
+      <c r="X35" s="5" t="inlineStr"/>
+      <c r="Y35" s="5" t="inlineStr"/>
+      <c r="Z35" s="5" t="inlineStr"/>
+      <c r="AA35" s="5" t="inlineStr"/>
+      <c r="AB35" s="5" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
@@ -7846,6 +9386,24 @@
       <c r="V36" s="5" t="n">
         <v>0.03</v>
       </c>
+      <c r="W36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AB36" s="5" t="n">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
@@ -7929,6 +9487,24 @@
       </c>
       <c r="V37" s="5" t="n">
         <v>0.04666666666666667</v>
+      </c>
+      <c r="W37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AA37" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB37" s="5" t="n">
+        <v>0.13</v>
       </c>
     </row>
     <row r="38">
@@ -7970,6 +9546,12 @@
       <c r="T38" s="5" t="inlineStr"/>
       <c r="U38" s="5" t="inlineStr"/>
       <c r="V38" s="5" t="inlineStr"/>
+      <c r="W38" s="5" t="inlineStr"/>
+      <c r="X38" s="5" t="inlineStr"/>
+      <c r="Y38" s="5" t="inlineStr"/>
+      <c r="Z38" s="5" t="inlineStr"/>
+      <c r="AA38" s="5" t="inlineStr"/>
+      <c r="AB38" s="5" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
@@ -8053,6 +9635,24 @@
       </c>
       <c r="V39" s="5" t="n">
         <v>0.01666666666666667</v>
+      </c>
+      <c r="W39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AA39" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AB39" s="5" t="n">
+        <v>0.09</v>
       </c>
     </row>
     <row r="40">
@@ -8130,6 +9730,24 @@
       <c r="V40" s="5" t="n">
         <v>0.01666666666666667</v>
       </c>
+      <c r="W40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AA40" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AB40" s="5" t="n">
+        <v>0.09</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
@@ -8214,6 +9832,24 @@
       <c r="V41" s="5" t="n">
         <v>0.01666666666666667</v>
       </c>
+      <c r="W41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z41" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AA41" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AB41" s="5" t="n">
+        <v>0.09</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
@@ -8298,6 +9934,24 @@
       <c r="V42" s="5" t="n">
         <v>0.01666666666666667</v>
       </c>
+      <c r="W42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AA42" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AB42" s="5" t="n">
+        <v>0.09</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
@@ -8382,6 +10036,24 @@
       <c r="V43" s="5" t="n">
         <v>0.01666666666666667</v>
       </c>
+      <c r="W43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z43" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AA43" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AB43" s="5" t="n">
+        <v>0.09</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
@@ -8466,6 +10138,12 @@
       <c r="V44" s="5" t="n">
         <v>0.02333333333333333</v>
       </c>
+      <c r="W44" s="5" t="inlineStr"/>
+      <c r="X44" s="5" t="inlineStr"/>
+      <c r="Y44" s="5" t="inlineStr"/>
+      <c r="Z44" s="5" t="inlineStr"/>
+      <c r="AA44" s="5" t="inlineStr"/>
+      <c r="AB44" s="5" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
@@ -8550,6 +10228,24 @@
       <c r="V45" s="5" t="n">
         <v>0.04666666666666667</v>
       </c>
+      <c r="W45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z45" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AA45" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB45" s="5" t="n">
+        <v>0.13</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
@@ -8634,6 +10330,24 @@
       <c r="V46" s="5" t="n">
         <v>0.01666666666666667</v>
       </c>
+      <c r="W46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z46" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AA46" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AB46" s="5" t="n">
+        <v>0.09</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
@@ -8712,6 +10426,12 @@
       <c r="V47" s="5" t="n">
         <v>0.02333333333333333</v>
       </c>
+      <c r="W47" s="5" t="inlineStr"/>
+      <c r="X47" s="5" t="inlineStr"/>
+      <c r="Y47" s="5" t="inlineStr"/>
+      <c r="Z47" s="5" t="inlineStr"/>
+      <c r="AA47" s="5" t="inlineStr"/>
+      <c r="AB47" s="5" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
@@ -8790,6 +10510,12 @@
       <c r="V48" s="5" t="n">
         <v>0.02333333333333333</v>
       </c>
+      <c r="W48" s="5" t="inlineStr"/>
+      <c r="X48" s="5" t="inlineStr"/>
+      <c r="Y48" s="5" t="inlineStr"/>
+      <c r="Z48" s="5" t="inlineStr"/>
+      <c r="AA48" s="5" t="inlineStr"/>
+      <c r="AB48" s="5" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
@@ -8870,6 +10596,24 @@
       <c r="V49" s="5" t="n">
         <v>0.01666666666666667</v>
       </c>
+      <c r="W49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z49" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AA49" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AB49" s="5" t="n">
+        <v>0.09</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
@@ -8950,6 +10694,24 @@
       <c r="V50" s="5" t="n">
         <v>0.01666666666666667</v>
       </c>
+      <c r="W50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z50" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AA50" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AB50" s="5" t="n">
+        <v>0.09</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
@@ -9030,6 +10792,24 @@
       <c r="V51" s="5" t="n">
         <v>0.02</v>
       </c>
+      <c r="W51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Z51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AB51" s="5" t="n">
+        <v>0.16</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
@@ -9109,6 +10889,24 @@
       </c>
       <c r="V52" s="5" t="n">
         <v>0.02666666666666667</v>
+      </c>
+      <c r="W52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z52" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AA52" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AB52" s="5" t="n">
+        <v>0.06</v>
       </c>
     </row>
     <row r="53">
@@ -9148,6 +10946,12 @@
       <c r="T53" s="5" t="inlineStr"/>
       <c r="U53" s="5" t="inlineStr"/>
       <c r="V53" s="5" t="inlineStr"/>
+      <c r="W53" s="5" t="inlineStr"/>
+      <c r="X53" s="5" t="inlineStr"/>
+      <c r="Y53" s="5" t="inlineStr"/>
+      <c r="Z53" s="5" t="inlineStr"/>
+      <c r="AA53" s="5" t="inlineStr"/>
+      <c r="AB53" s="5" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
@@ -9227,6 +11031,24 @@
       </c>
       <c r="V54" s="5" t="n">
         <v>0.02</v>
+      </c>
+      <c r="W54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y54" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Z54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA54" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AB54" s="5" t="n">
+        <v>0.16</v>
       </c>
     </row>
     <row r="55">
@@ -9266,6 +11088,12 @@
       <c r="T55" s="5" t="inlineStr"/>
       <c r="U55" s="5" t="inlineStr"/>
       <c r="V55" s="5" t="inlineStr"/>
+      <c r="W55" s="5" t="inlineStr"/>
+      <c r="X55" s="5" t="inlineStr"/>
+      <c r="Y55" s="5" t="inlineStr"/>
+      <c r="Z55" s="5" t="inlineStr"/>
+      <c r="AA55" s="5" t="inlineStr"/>
+      <c r="AB55" s="5" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
@@ -9302,6 +11130,12 @@
       <c r="T56" s="5" t="inlineStr"/>
       <c r="U56" s="5" t="inlineStr"/>
       <c r="V56" s="5" t="inlineStr"/>
+      <c r="W56" s="5" t="inlineStr"/>
+      <c r="X56" s="5" t="inlineStr"/>
+      <c r="Y56" s="5" t="inlineStr"/>
+      <c r="Z56" s="5" t="inlineStr"/>
+      <c r="AA56" s="5" t="inlineStr"/>
+      <c r="AB56" s="5" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
@@ -9338,6 +11172,12 @@
       <c r="T57" s="5" t="inlineStr"/>
       <c r="U57" s="5" t="inlineStr"/>
       <c r="V57" s="5" t="inlineStr"/>
+      <c r="W57" s="5" t="inlineStr"/>
+      <c r="X57" s="5" t="inlineStr"/>
+      <c r="Y57" s="5" t="inlineStr"/>
+      <c r="Z57" s="5" t="inlineStr"/>
+      <c r="AA57" s="5" t="inlineStr"/>
+      <c r="AB57" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C2:C57">
@@ -9580,6 +11420,78 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="W2:W57">
+    <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X2:X57">
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y2:Y57">
+    <cfRule type="colorScale" priority="23">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z2:Z57">
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA2:AA57">
+    <cfRule type="colorScale" priority="25">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB2:AB57">
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outputs/QLD_curtailment.xlsx
+++ b/outputs/QLD_curtailment.xlsx
@@ -692,7 +692,7 @@
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="5" t="inlineStr"/>
       <c r="L2" s="5" t="n">
-        <v>0.1335</v>
+        <v>0.1347</v>
       </c>
       <c r="M2" s="5" t="inlineStr"/>
       <c r="N2" s="5" t="inlineStr"/>
@@ -1287,7 +1287,7 @@
         <v>0.1872</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>0.31</v>
+        <v>0.3111</v>
       </c>
       <c r="M9" s="5" t="n">
         <v>0.219557634008624</v>
@@ -1410,7 +1410,7 @@
         <v>0.0158</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>0.0764</v>
+        <v>0.0762</v>
       </c>
       <c r="M10" s="5" t="n">
         <v>0.22576156415161</v>
@@ -1517,7 +1517,7 @@
         <v>0.0018</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>0.0354</v>
+        <v>0.0363</v>
       </c>
       <c r="M11" s="5" t="n">
         <v>0.221997464026796</v>
@@ -1747,7 +1747,7 @@
         <v>0.01</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>0.0108</v>
+        <v>0.0113</v>
       </c>
       <c r="M13" s="5" t="n">
         <v>0.224633904533977</v>
@@ -1870,7 +1870,7 @@
         <v>0.0376</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>0.2096</v>
+        <v>0.2118</v>
       </c>
       <c r="M14" s="5" t="n">
         <v>0.221997464026796</v>
@@ -1977,7 +1977,7 @@
         <v>0.0581</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>0.1269</v>
+        <v>0.1276</v>
       </c>
       <c r="M15" s="5" t="n">
         <v>0.224633904533977</v>
@@ -2187,7 +2187,7 @@
         <v>0.1929</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>0.3486</v>
+        <v>0.3502</v>
       </c>
       <c r="M17" s="5" t="n">
         <v>0.224633904533977</v>
@@ -2367,7 +2367,7 @@
         <v>0.07389999999999999</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>0.2526</v>
+        <v>0.253</v>
       </c>
       <c r="M19" s="5" t="n">
         <v>0.221997464026796</v>
@@ -2474,7 +2474,7 @@
         <v>0.0871</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>0.0367</v>
+        <v>0.0371</v>
       </c>
       <c r="M20" s="5" t="n">
         <v>0.219557634008624</v>
@@ -2597,7 +2597,7 @@
         <v>0.2149</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>0.3349</v>
+        <v>0.3352</v>
       </c>
       <c r="M21" s="5" t="n">
         <v>0.221997464026796</v>
@@ -2787,7 +2787,7 @@
         <v>0.0902</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>0.0738</v>
+        <v>0.0737</v>
       </c>
       <c r="M23" s="5" t="n">
         <v>0.219557634008624</v>
@@ -2910,7 +2910,7 @@
         <v>0.2351</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>0.3459</v>
+        <v>0.3449</v>
       </c>
       <c r="M24" s="5" t="n">
         <v>0.219557634008624</v>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="K25" s="5" t="inlineStr"/>
       <c r="L25" s="5" t="n">
-        <v>0.2694</v>
+        <v>0.2691</v>
       </c>
       <c r="M25" s="5" t="n">
         <v>0.233985863287972</v>
@@ -3118,7 +3118,7 @@
         <v>0.1022</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>0.0369</v>
+        <v>0.037</v>
       </c>
       <c r="M26" s="5" t="n">
         <v>0.22576156415161</v>
@@ -3308,7 +3308,7 @@
         <v>0.1155</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>0.3663</v>
+        <v>0.367</v>
       </c>
       <c r="M28" s="5" t="n">
         <v>0.23150076097273</v>
@@ -3425,7 +3425,7 @@
         <v>0.02</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>0.259</v>
+        <v>0.2582</v>
       </c>
       <c r="M29" s="5" t="inlineStr"/>
       <c r="N29" s="5" t="inlineStr"/>
@@ -3704,7 +3704,7 @@
         <v>0.3341</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>0.3606</v>
+        <v>0.3613</v>
       </c>
       <c r="M32" s="5" t="n">
         <v>0.23150076097273</v>
@@ -3827,7 +3827,7 @@
         <v>0.0953</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>0.2702</v>
+        <v>0.2713</v>
       </c>
       <c r="M33" s="5" t="n">
         <v>0.23150076097273</v>
@@ -4073,7 +4073,7 @@
         <v>0.0786</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>0.2287</v>
+        <v>0.2296</v>
       </c>
       <c r="M35" s="5" t="n">
         <v>0.22576156415161</v>
@@ -4180,7 +4180,7 @@
         <v>0.1003</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>0.2371</v>
+        <v>0.2384</v>
       </c>
       <c r="M36" s="5" t="n">
         <v>0.219325121104852</v>
@@ -4303,7 +4303,7 @@
         <v>0.1189</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>0.2924</v>
+        <v>0.2925</v>
       </c>
       <c r="M37" s="5" t="n">
         <v>0.218738210926131</v>
@@ -4509,7 +4509,7 @@
         <v>0.1974</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>0.3746</v>
+        <v>0.3756</v>
       </c>
       <c r="M39" s="5" t="n">
         <v>0.223370431255546</v>
@@ -4737,7 +4737,7 @@
         <v>0.39</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>0.5008</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="M41" s="5" t="n">
         <v>0.23150076097273</v>
@@ -4860,7 +4860,7 @@
         <v>0.394</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>0.5044</v>
+        <v>0.504</v>
       </c>
       <c r="M42" s="5" t="n">
         <v>0.23150076097273</v>
@@ -4977,7 +4977,7 @@
         <v>0.1745</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>0.0309</v>
+        <v>0.032</v>
       </c>
       <c r="M43" s="5" t="n">
         <v>0.224633904533977</v>
@@ -5207,7 +5207,7 @@
         <v>0.2353</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>0.0663</v>
+        <v>0.0669</v>
       </c>
       <c r="M45" s="5" t="n">
         <v>0.23173278497921</v>
@@ -5330,7 +5330,7 @@
         <v>0.1371</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>0.2322</v>
+        <v>0.2337</v>
       </c>
       <c r="M46" s="5" t="n">
         <v>0.23150076097273</v>
@@ -5629,7 +5629,7 @@
         <v>0.0298</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>0.0529</v>
+        <v>0.0533</v>
       </c>
       <c r="M49" s="5" t="inlineStr"/>
       <c r="N49" s="5" t="inlineStr"/>
@@ -5847,7 +5847,7 @@
         <v>0.0114</v>
       </c>
       <c r="L51" s="5" t="n">
-        <v>0.07630000000000001</v>
+        <v>0.077</v>
       </c>
       <c r="M51" s="5" t="inlineStr"/>
       <c r="N51" s="5" t="inlineStr"/>
@@ -6136,7 +6136,7 @@
         <v>0.0395</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>0.0189</v>
+        <v>0.019</v>
       </c>
       <c r="M54" s="5" t="inlineStr"/>
       <c r="N54" s="5" t="inlineStr"/>
@@ -6231,7 +6231,7 @@
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="5" t="inlineStr"/>
       <c r="L55" s="5" t="n">
-        <v>0.0038</v>
+        <v>0.0039</v>
       </c>
       <c r="M55" s="5" t="inlineStr"/>
       <c r="N55" s="5" t="inlineStr"/>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="E2" s="5" t="inlineStr"/>
       <c r="F2" s="5" t="n">
-        <v>0.1335</v>
+        <v>0.1347</v>
       </c>
       <c r="G2" s="5" t="inlineStr"/>
       <c r="H2" s="5" t="inlineStr"/>
@@ -7008,7 +7008,7 @@
         <v>0.1872</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.31</v>
+        <v>0.3111</v>
       </c>
       <c r="G9" s="5" t="n">
         <v>0.219557634008624</v>
@@ -7110,7 +7110,7 @@
         <v>0.0158</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.0764</v>
+        <v>0.0762</v>
       </c>
       <c r="G10" s="5" t="n">
         <v>0.22576156415161</v>
@@ -7200,7 +7200,7 @@
         <v>0.0018</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.0354</v>
+        <v>0.0363</v>
       </c>
       <c r="G11" s="5" t="n">
         <v>0.221997464026796</v>
@@ -7392,7 +7392,7 @@
         <v>0.01</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.0108</v>
+        <v>0.0113</v>
       </c>
       <c r="G13" s="5" t="n">
         <v>0.224633904533977</v>
@@ -7494,7 +7494,7 @@
         <v>0.0376</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0.2096</v>
+        <v>0.2118</v>
       </c>
       <c r="G14" s="5" t="n">
         <v>0.221997464026796</v>
@@ -7584,7 +7584,7 @@
         <v>0.0581</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.1269</v>
+        <v>0.1276</v>
       </c>
       <c r="G15" s="5" t="n">
         <v>0.224633904533977</v>
@@ -7736,7 +7736,7 @@
         <v>0.1929</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0.3486</v>
+        <v>0.3502</v>
       </c>
       <c r="G17" s="5" t="n">
         <v>0.224633904533977</v>
@@ -7880,7 +7880,7 @@
         <v>0.07389999999999999</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>0.2526</v>
+        <v>0.253</v>
       </c>
       <c r="G19" s="5" t="n">
         <v>0.221997464026796</v>
@@ -7970,7 +7970,7 @@
         <v>0.0871</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0.0367</v>
+        <v>0.0371</v>
       </c>
       <c r="G20" s="5" t="n">
         <v>0.219557634008624</v>
@@ -8072,7 +8072,7 @@
         <v>0.2149</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0.3349</v>
+        <v>0.3352</v>
       </c>
       <c r="G21" s="5" t="n">
         <v>0.221997464026796</v>
@@ -8208,7 +8208,7 @@
         <v>0.0902</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>0.0738</v>
+        <v>0.0737</v>
       </c>
       <c r="G23" s="5" t="n">
         <v>0.219557634008624</v>
@@ -8310,7 +8310,7 @@
         <v>0.2351</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>0.3459</v>
+        <v>0.3449</v>
       </c>
       <c r="G24" s="5" t="n">
         <v>0.219557634008624</v>
@@ -8410,7 +8410,7 @@
       </c>
       <c r="E25" s="5" t="inlineStr"/>
       <c r="F25" s="5" t="n">
-        <v>0.2694</v>
+        <v>0.2691</v>
       </c>
       <c r="G25" s="5" t="n">
         <v>0.233985863287972</v>
@@ -8460,7 +8460,7 @@
         <v>0.1022</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>0.0369</v>
+        <v>0.037</v>
       </c>
       <c r="G26" s="5" t="n">
         <v>0.22576156415161</v>
@@ -8596,7 +8596,7 @@
         <v>0.1155</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>0.3663</v>
+        <v>0.367</v>
       </c>
       <c r="G28" s="5" t="n">
         <v>0.23150076097273</v>
@@ -8698,7 +8698,7 @@
         <v>0.02</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>0.259</v>
+        <v>0.2582</v>
       </c>
       <c r="G29" s="5" t="inlineStr"/>
       <c r="H29" s="5" t="inlineStr"/>
@@ -8928,7 +8928,7 @@
         <v>0.3341</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>0.3606</v>
+        <v>0.3613</v>
       </c>
       <c r="G32" s="5" t="n">
         <v>0.23150076097273</v>
@@ -9030,7 +9030,7 @@
         <v>0.0953</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>0.2702</v>
+        <v>0.2713</v>
       </c>
       <c r="G33" s="5" t="n">
         <v>0.23150076097273</v>
@@ -9234,7 +9234,7 @@
         <v>0.0786</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>0.2287</v>
+        <v>0.2296</v>
       </c>
       <c r="G35" s="5" t="n">
         <v>0.22576156415161</v>
@@ -9324,7 +9324,7 @@
         <v>0.1003</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>0.2371</v>
+        <v>0.2384</v>
       </c>
       <c r="G36" s="5" t="n">
         <v>0.219325121104852</v>
@@ -9426,7 +9426,7 @@
         <v>0.1189</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>0.2924</v>
+        <v>0.2925</v>
       </c>
       <c r="G37" s="5" t="n">
         <v>0.218738210926131</v>
@@ -9574,7 +9574,7 @@
         <v>0.1974</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>0.3746</v>
+        <v>0.3756</v>
       </c>
       <c r="G39" s="5" t="n">
         <v>0.223370431255546</v>
@@ -9770,7 +9770,7 @@
         <v>0.39</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>0.5008</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="G41" s="5" t="n">
         <v>0.23150076097273</v>
@@ -9872,7 +9872,7 @@
         <v>0.394</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>0.5044</v>
+        <v>0.504</v>
       </c>
       <c r="G42" s="5" t="n">
         <v>0.23150076097273</v>
@@ -9974,7 +9974,7 @@
         <v>0.1745</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>0.0309</v>
+        <v>0.032</v>
       </c>
       <c r="G43" s="5" t="n">
         <v>0.224633904533977</v>
@@ -10166,7 +10166,7 @@
         <v>0.2353</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>0.0663</v>
+        <v>0.0669</v>
       </c>
       <c r="G45" s="5" t="n">
         <v>0.23173278497921</v>
@@ -10268,7 +10268,7 @@
         <v>0.1371</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>0.2322</v>
+        <v>0.2337</v>
       </c>
       <c r="G46" s="5" t="n">
         <v>0.23150076097273</v>
@@ -10538,7 +10538,7 @@
         <v>0.0298</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>0.0529</v>
+        <v>0.0533</v>
       </c>
       <c r="G49" s="5" t="inlineStr"/>
       <c r="H49" s="5" t="inlineStr"/>
@@ -10734,7 +10734,7 @@
         <v>0.0114</v>
       </c>
       <c r="F51" s="5" t="n">
-        <v>0.07630000000000001</v>
+        <v>0.077</v>
       </c>
       <c r="G51" s="5" t="inlineStr"/>
       <c r="H51" s="5" t="inlineStr"/>
@@ -10974,7 +10974,7 @@
         <v>0.0395</v>
       </c>
       <c r="F54" s="5" t="n">
-        <v>0.0189</v>
+        <v>0.019</v>
       </c>
       <c r="G54" s="5" t="inlineStr"/>
       <c r="H54" s="5" t="inlineStr"/>
@@ -11070,7 +11070,7 @@
       </c>
       <c r="E55" s="5" t="inlineStr"/>
       <c r="F55" s="5" t="n">
-        <v>0.0038</v>
+        <v>0.0039</v>
       </c>
       <c r="G55" s="5" t="inlineStr"/>
       <c r="H55" s="5" t="inlineStr"/>
